--- a/豆瓣图书Top250本地数据库.xlsx
+++ b/豆瓣图书Top250本地数据库.xlsx
@@ -413,38 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>book_title</t>
+          <t>书名</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>isbn</t>
+          <t>ISBN</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>pages</t>
+          <t>页数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>内容简介</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>single_comment</t>
+          <t>热门短评内容</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>detail_url</t>
+          <t>详情页URL</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>暂无短评数据</t>
+          <t>未能成功跳转短评页</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>暂无短评数据</t>
+          <t>新版封面，严重剧透。</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2009,464 +2009,508 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>把小说写成这样绝对是开挂了吧，除了连番登场的几十号人物，随处雕琢的大时代的背景也让人叹为观止。对人性的挖掘比起吉田修一还是弱一些，就是纯好看，从第一句开始吸住你逐渐往往里掉。</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>情有可原，罪无可恕。</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>故事中男女主人公从头到尾没有一句对白，经典。</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>张无忌的妈妈也说过 不要轻易相信漂亮女人 她们的演技和城府都是你无法想象的 无删减版本比之前的版本多了关于性的描写 阴茎和乳房等词汇也直接被接纳进来 前十章用来构建人物关系和埋下案件伏笔 从第十章开始抽丝剥茧地隐现真相 枪虾和虾虎鱼（雪穗和桐原）的关系日渐明朗 遗憾的是关于后半段作者的笔锋开始出现倦怠 没有给出很完整明确的指示或者暗示 对于最后整体的真相的揭露也并没有很吃惊 除了娈童之外 其他的因果其实已了然于心</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>邓小平时代</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>9787108041531</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>754</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
 哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
 (展开全部)</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>挽狂澜于既倒，扶大厦之将倾。</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/20424526/</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>邓小平时代</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>9787108041531</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>754</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
 哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
 (展开全部)</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>在书店翻完就成，买回家则如同鸡肋。傅高义写这部书的初衷就是向西方人介绍邓小平和他经历过的大时代，可叹的是，今天我们却要把这样一部写给别人的入门书当作我们了解自我的红宝书。</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/20424526/</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>邓小平时代</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>9787108041531</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>754</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
 哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
 (展开全部)</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>总有人希望这本书能有别出心裁的史料和观点，其实这本书最大的贡献在于理清了从1977年到1992年所有历史事件的脉络</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/20424526/</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>邓小平时代</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>9787108041531</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>754</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
 哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
 (展开全部)</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/20424526/</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>邓小平时代</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>9787108041531</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>754</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
 哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
 (展开全部)</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>按照邓小平的遗愿，他的眼角膜被捐出供眼科研究，内脏被捐出供医学研究，遗体被火化，骨灰盒上覆盖着中国共产党党旗。1997年3月2日，他的骨灰被撒入大海。</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/20424526/</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>小王子</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>9787020042494</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
 小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
 (展开全部)</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>十几岁的时候渴慕着小王子，一天之间可以看四十四次日落。是在多久之后才明白，看四十四次日落的小王子，他有多么难过。</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1084336/</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>小王子</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>9787020042494</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
 小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
 (展开全部)</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>读了好多年，终于读完了，但是实在共鸣不起来，虽然知道那些道理，但真的觉得没什么了不起啊，是我还太幼稚吗？</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1084336/</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>小王子</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>9787020042494</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
 小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
 (展开全部)</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>我的玫瑰花儿，只有四个微不足道的刺，用来抵御这个世界。</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1084336/</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>小王子</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>9787020042494</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
 小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
 (展开全部)</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>说实话 我看不太懂 但还是跟风给个5星吧 以显示我也是有思想有学识之人</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1084336/</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>小王子</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>9787020042494</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
 小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
 (展开全部)</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>虽然我实在幼稚，但我并不怎么喜欢孩童般的纯净，我只爱风浪过后的平静，流水打磨出的清亮，大雪纷飞时的安宁，沧桑看透的纯真，我爱眼冷心热的庄子，人究竟无所逃于天地之间，各适其性，做自己认为有意义的事就好了，无论是统治宇宙还是喝酒点灯，对他们来说，都比爱一朵玫瑰重要，这不是很好的么</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1084336/</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>呐喊</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>鲁迅如果不被赋予那么多政治色彩，单看作品也是一个优秀的毒舌家的</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/1449351/</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>呐喊</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>看他的文章还无法醒悟的人是该有多么可悲</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/1449351/</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>呐喊</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>一个特立独行的人需要金钱来保持他的尊严，否则就只有被毁灭的份，人们是不能容忍一个穷光蛋的异类的。就象一个老姑娘要用钱保持她的高傲，否则就是耻辱。</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/1449351/</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>呐喊</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>这部小说，大体上是描写了辛亥革命前后乡村发生的一系列的故事，其中以鞭子、革命、秀才、假洋鬼子，扮演出一幅中国传统社会的浮世绘。在这里，我们不妨感慨，鲁迅笔下人物的生命力。鲁迅是描写了辛亥革命前后，我们已经革命胜利六十多年，但是假洋鬼子、赵老太爷难道就绝迹了吗？咸与维新，却一切照旧。</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/1449351/</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2537,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>狂人在望着赵家的狗，孔乙己在讲茴字的四种写法，华老栓在拿夏瑜的血馒头，九斤老太在感叹一代不如一代，闰土在隔着厚障壁叫我老爷，圆规杨二嫂在捡东西，阿Q在逗尼姑，耍无赖，闹革命，要困觉，精神胜利法，迅哥在怀念那夜似的豆，那夜似的戏。我们在铁屋子里装睡，想着年轻时做过的许多的梦。</t>
+          <t>鲁迅如果不被赋予那么多政治色彩，单看作品也是一个优秀的毒舌家的</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2505,20 +2549,148 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>看他的文章还无法醒悟的人是该有多么可悲</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>一个特立独行的人需要金钱来保持他的尊严，否则就只有被毁灭的份，人们是不能容忍一个穷光蛋的异类的。就象一个老姑娘要用钱保持她的高傲，否则就是耻辱。</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>这部小说，大体上是描写了辛亥革命前后乡村发生的一系列的故事，其中以鞭子、革命、秀才、假洋鬼子，扮演出一幅中国传统社会的浮世绘。在这里，我们不妨感慨，鲁迅笔下人物的生命力。鲁迅是描写了辛亥革命前后，我们已经革命胜利六十多年，但是假洋鬼子、赵老太爷难道就绝迹了吗？咸与维新，却一切照旧。</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>狂人在望着赵家的狗，孔乙己在讲茴字的四种写法，华老栓在拿夏瑜的血馒头，九斤老太在感叹一代不如一代，闰土在隔着厚障壁叫我老爷，圆规杨二嫂在捡东西，阿Q在逗尼姑，耍无赖，闹革命，要困觉，精神胜利法，迅哥在怀念那夜似的豆，那夜似的戏。我们在铁屋子里装睡，想着年轻时做过的许多的梦。</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>安徒生童话故事集</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>9787020017713</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>550</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
 “为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
@@ -2526,34 +2698,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>比格林好，而且寒假过后的几个月，经常在里面翻出压岁钱</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1046209/</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>安徒生童话故事集</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>9787020017713</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>550</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
 “为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
@@ -2561,34 +2733,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>《海的女儿》是爱情的启蒙。</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1046209/</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>安徒生童话故事集</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>9787020017713</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>550</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
 “为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
@@ -2596,34 +2768,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>如果不是叶君健译的就不要看，书者与译者相得益彰，擦出的精致纯美，无人可及</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1046209/</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>安徒生童话故事集</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>9787020017713</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>550</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
 “为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
@@ -2631,34 +2803,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>写给成人的悲伤童话</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1046209/</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>安徒生童话故事集</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>9787020017713</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>550</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
 “为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
@@ -2666,142 +2838,14 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>小时候看是童话 现在再看的话才发现都是悲剧</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1046209/</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>撒哈拉的故事</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>9787806398791</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>三毛的文字其实没有特别出挑的地方，但是合成一篇，整个却显得真实、清爽。她很好地遵循了白话文“有什么说什么，该怎么说就怎么说”的宗旨，而且她聪明在不在散文中论理，不作生硬的哲思，单纯就事论事，从而反倒能让人身临其境~~印象最深的是她和荷西去偷看别人洗澡灌肠，再如三毛考驾照的那几个考题，好笑极了~~而读到他们遇到三个疯子袭击则心提至喉~~看散文，以前喜欢过余秋雨的辞藻，现在越来越喜欢三毛这类的平淡，平淡是真，写文常常有自炫的诱惑，能抵住诱惑是不容易的。。。【题外】三毛与荷西是般配的一对，如果荷西没有去世地那么早，三毛可能也不会弃世了吧。。。“人”果然是两个人互相支撑在一起才能不倒下的。。。</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/1060068/</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>撒哈拉的故事</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>9787806398791</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>自你之后，再无真正流浪自由的灵魂。</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/1060068/</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>撒哈拉的故事</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>9787806398791</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>再看到 荒山之夜 仍然还是以前的震惊！他们那么随便就经历了一场出生入死，而且完全不在意，人生多么的洒脱啊</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/1060068/</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>撒哈拉的故事</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>9787806398791</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>读过三毛全集，最好的还是这一册。</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/1060068/</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2872,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>你伤害了我的骄傲！</t>
+          <t>三毛的文字其实没有特别出挑的地方，但是合成一篇，整个却显得真实、清爽。她很好地遵循了白话文“有什么说什么，该怎么说就怎么说”的宗旨，而且她聪明在不在散文中论理，不作生硬的哲思，单纯就事论事，从而反倒能让人身临其境~~印象最深的是她和荷西去偷看别人洗澡灌肠，再如三毛考驾照的那几个考题，好笑极了~~而读到他们遇到三个疯子袭击则心提至喉~~看散文，以前喜欢过余秋雨的辞藻，现在越来越喜欢三毛这类的平淡，平淡是真，写文常常有自炫的诱惑，能抵住诱惑是不容易的。。。【题外】三毛与荷西是般配的一对，如果荷西没有去世地那么早，三毛可能也不会弃世了吧。。。“人”果然是两个人互相支撑在一起才能不倒下的。。。</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2840,128 +2884,128 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>天龙八部</t>
+          <t>撒哈拉的故事</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>9787108006721</t>
+          <t>9787806398791</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>经典武学起于春秋，到北宋达到极盛，南宋有所衰落，元末因明教兴盛中兴。明代更有了东方不败等大师。但期间伽利略的出现已预示其衰落。康熙年间出现牛顿，梯云纵灭绝。道光年间出现卡诺，玄冰掌灭绝。尤其是力学定理建立后，内力和轻功全部消失，梯云纵这种只需吐纳练便可自带反重力系统的轻功彻底消失</t>
+          <t>自你之后，再无真正流浪自由的灵魂。</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://book.douban.com/subject/1255625/</t>
+          <t>https://book.douban.com/subject/1060068/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>天龙八部</t>
+          <t>撒哈拉的故事</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>9787108006721</t>
+          <t>9787806398791</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>慕容复是没落皇族子孙，毕生追求皇位，对王语嫣视如草介，段誉是正牌皇帝继承人，却爱美人宁弃江山。你所追的，正是我所弃的，尽道人生的可笑荒谬。</t>
+          <t>再看到 荒山之夜 仍然还是以前的震惊！他们那么随便就经历了一场出生入死，而且完全不在意，人生多么的洒脱啊</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://book.douban.com/subject/1255625/</t>
+          <t>https://book.douban.com/subject/1060068/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>天龙八部</t>
+          <t>撒哈拉的故事</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>9787108006721</t>
+          <t>9787806398791</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>因为众生皆苦，便觉得自己也不是很苦。</t>
+          <t>读过三毛全集，最好的还是这一册。</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://book.douban.com/subject/1255625/</t>
+          <t>https://book.douban.com/subject/1060068/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>天龙八部</t>
+          <t>撒哈拉的故事</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>9787108006721</t>
+          <t>9787806398791</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>金圣叹评《水浒》论武松为天人，萧峰何尝不是天人。看他有阔处，有毒处，有正处，有良处，有快处，有真处，有捷处，有雅处，有大处，有警处，实是金大侠小说中之第一人。</t>
+          <t>你伤害了我的骄傲！</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://book.douban.com/subject/1255625/</t>
+          <t>https://book.douban.com/subject/1060068/</t>
         </is>
       </c>
     </row>
@@ -2988,7 +3032,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>偌大一本书，数百豪杰人物，萧峰一出，全归背景</t>
+          <t>经典武学起于春秋，到北宋达到极盛，南宋有所衰落，元末因明教兴盛中兴。明代更有了东方不败等大师。但期间伽利略的出现已预示其衰落。康熙年间出现牛顿，梯云纵灭绝。道光年间出现卡诺，玄冰掌灭绝。尤其是力学定理建立后，内力和轻功全部消失，梯云纵这种只需吐纳练便可自带反重力系统的轻功彻底消失</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3000,20 +3044,148 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>慕容复是没落皇族子孙，毕生追求皇位，对王语嫣视如草介，段誉是正牌皇帝继承人，却爱美人宁弃江山。你所追的，正是我所弃的，尽道人生的可笑荒谬。</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>因为众生皆苦，便觉得自己也不是很苦。</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>金圣叹评《水浒》论武松为天人，萧峰何尝不是天人。看他有阔处，有毒处，有正处，有良处，有快处，有真处，有捷处，有雅处，有大处，有警处，实是金大侠小说中之第一人。</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>偌大一本书，数百豪杰人物，萧峰一出，全归背景</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>失踪的孩子 : 那不勒斯四部曲4</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>9787020139927</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
 全球畅销近千万册被翻译成40多种语言
@@ -3026,34 +3198,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>理性的培养、逻辑的思维、高雅的阅读等不能让别人爱你，但却能让你坦然接受不被爱。</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/30172069/</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>失踪的孩子 : 那不勒斯四部曲4</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>9787020139927</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
 全球畅销近千万册被翻译成40多种语言
@@ -3066,34 +3238,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>我一度以为二十多岁是一个人最难熬的一段时间，在这段时间里要实现从少年到青年的转换。看了这四本书之后发现人一辈子都在挣扎，只是每个时期面临的困难不同罢了，我们一直都经历着角色的转换。</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/30172069/</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>失踪的孩子 : 那不勒斯四部曲4</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>9787020139927</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
 全球畅销近千万册被翻译成40多种语言
@@ -3106,34 +3278,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>会让你在读完最后一行后想要重新翻开《我的天才女友》的第一页。</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/30172069/</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>失踪的孩子 : 那不勒斯四部曲4</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>9787020139927</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
 全球畅销近千万册被翻译成40多种语言
@@ -3146,34 +3318,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>也许莉拉吸引尼诺的地方，就是尼诺在她身上，开始看到了以为自己也有的东西，但对比之下他发现自己并没有。她拥有才智，但她没有利用它为自己谋福利，而像贵妇一样在挥霍着自己的才智，就好像对她来说，整个世界的财富都是庸俗的。莉拉的才智是免费的，这就是她让尼诺入迷的原因。“她和其他女人不一样，因为她天生就那么桀骜不驯，不会为任何事儿弯腰。”我们所有人都做出让步了，经过考验、失败和成功，这种让步重新塑造了我们。只有莉拉，没有任何人、任何事可以改变她。不仅如此，随着年龄的增长，她和任何人一样变得顽固和难相处，但她的那些品质一直都原封未动，甚至更加坚固。我们恨她的同时，也害怕她，会对她充满敬意。</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/30172069/</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>失踪的孩子 : 那不勒斯四部曲4</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>9787020139927</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
 全球畅销近千万册被翻译成40多种语言
@@ -3186,142 +3358,14 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>读完那不勒斯四部曲的雨夜，人生几十年，像是一场玩笑，像是一次为了记录而存在的表演。</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/30172069/</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>卡拉马佐夫兄弟</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>9787532763696</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>洪荒巨兽，太巨大了。老陀的体量感真不是盖的，契诃夫、布尔加科夫、《百年孤独》、《悉达多》，简直都好像只是从他身上抽下来一根骨头。一边读一边也遗憾：涅朵奇卡没有写完，卡拉马佐夫没有写完，契诃夫死得那么早...</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/25887924/</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>卡拉马佐夫兄弟</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>9787532763696</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>这是一个缺失信仰的年代。这是一个焦虑爆棚的年代。当大家都在忙着读心灵鸡汤，来寻找到人生真谛的时候，推荐你读一读这本《卡拉马佐夫兄弟》，一本被无数大师封神的小说。 这本小说，在文学史上的地位已经毋庸置疑，它极其真实的写出了人性中种种的崇高与丑恶，它像一面镜子，在其中你会看到一个你都不想承认的自己。这本书，是完美的将哲学、神学、心理学融为一体的杰作。 就连最狂傲的，自命为天才的尼采，读完此书也不得不承认：“陀思妥耶夫斯基是我生命中最美好的际遇，他是一个思想深刻的人，他有充分的权利，蔑视我们这些浅薄的德国人。”</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/25887924/</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>卡拉马佐夫兄弟</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>9787532763696</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>那时候我太轻狂，只觉得他太多话，没察觉那是另一种沉默，或者说那是沉默的尽头。</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/25887924/</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>卡拉马佐夫兄弟</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>9787532763696</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>《宗教大法官》一章另添一星，翻译再添一星，这书至少该打七星！</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/25887924/</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3392,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>不知是陀氏自身还是荣如德功劳，语言意蕴丰满，两本大部头看起来很愉快。上海译文这版版式不错，插画精美，如果有精装版就更好了。当时的俄罗斯刚刚破除农奴制，新思潮涌入，宗教却依然占据主导。陀氏虽然拥有一定的倾向性，但理性的光芒已锐不可当。感觉“宗教大法官”和“魔鬼。伊万·费奥多罗维奇的梦魇”两节最为精彩，其中“宗”一节直接逼问上帝，毫不留情揭露宗教，大快人心。相比之下，想到《我的个神啊》这种幼稚的意淫如此为人追捧，只得耻笑。</t>
+          <t>洪荒巨兽，太巨大了。老陀的体量感真不是盖的，契诃夫、布尔加科夫、《百年孤独》、《悉达多》，简直都好像只是从他身上抽下来一根骨头。一边读一边也遗憾：涅朵奇卡没有写完，卡拉马佐夫没有写完，契诃夫死得那么早...</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3360,20 +3404,148 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>这是一个缺失信仰的年代。这是一个焦虑爆棚的年代。当大家都在忙着读心灵鸡汤，来寻找到人生真谛的时候，推荐你读一读这本《卡拉马佐夫兄弟》，一本被无数大师封神的小说。 这本小说，在文学史上的地位已经毋庸置疑，它极其真实的写出了人性中种种的崇高与丑恶，它像一面镜子，在其中你会看到一个你都不想承认的自己。这本书，是完美的将哲学、神学、心理学融为一体的杰作。 就连最狂傲的，自命为天才的尼采，读完此书也不得不承认：“陀思妥耶夫斯基是我生命中最美好的际遇，他是一个思想深刻的人，他有充分的权利，蔑视我们这些浅薄的德国人。”</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>那时候我太轻狂，只觉得他太多话，没察觉那是另一种沉默，或者说那是沉默的尽头。</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>《宗教大法官》一章另添一星，翻译再添一星，这书至少该打七星！</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>不知是陀氏自身还是荣如德功劳，语言意蕴丰满，两本大部头看起来很愉快。上海译文这版版式不错，插画精美，如果有精装版就更好了。当时的俄罗斯刚刚破除农奴制，新思潮涌入，宗教却依然占据主导。陀氏虽然拥有一定的倾向性，但理性的光芒已锐不可当。感觉“宗教大法官”和“魔鬼。伊万·费奥多罗维奇的梦魇”两节最为精彩，其中“宗”一节直接逼问上帝，毫不留情揭露宗教，大快人心。相比之下，想到《我的个神啊》这种幼稚的意淫如此为人追捧，只得耻笑。</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>新名字的故事 : 那不勒斯四部曲2</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>9787020125265</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>只有你身为女人 才会知道这些丑陋的秘密
 两个女人 50年的友谊和战争
@@ -3388,34 +3560,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>我很真诚的讲：作者用极其扎实的故事告诉了女人们，为什么不能太早结婚以及为什么要坚持上学读书……（一本真正的女性主义小说</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/26986954/</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>新名字的故事 : 那不勒斯四部曲2</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>9787020125265</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>只有你身为女人 才会知道这些丑陋的秘密
 两个女人 50年的友谊和战争
@@ -3430,34 +3602,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>你以为那不勒斯很远，但是那种女性才懂的绝望和迷茫是全世界通用的。</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/26986954/</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>新名字的故事 : 那不勒斯四部曲2</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>9787020125265</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>只有你身为女人 才会知道这些丑陋的秘密
 两个女人 50年的友谊和战争
@@ -3472,34 +3644,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>这套小说有一种奇怪的魔力，完全手不释卷，停不下来，会想一口气看掉，沉迷在人物波澜壮阔的情感和命运里。有一种看情节剧的错觉，而且一点也不累人，翻起来又快又兴奋。莉拉的命运啊，真的，最后在工厂里那一幕，哭死了，为她心碎，她的疯狂和大胆，她的天才和倔强。而莱农的心理描写也非常好看，直接而无任何保留，以后她会袒露自己，还是把自己写成故事呢。现在配角的人物形象都开始丰满起来，但是尼诺反倒有点让人爱不起来，在莉拉的光芒下，他显得迟疑而孱弱，反倒是恩佐和莉拉一起学习的画面又一次激动了人心。继续等第三部第四部，想知道莉拉如何继续把控她的命运。</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/26986954/</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>新名字的故事 : 那不勒斯四部曲2</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>9787020125265</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>只有你身为女人 才会知道这些丑陋的秘密
 两个女人 50年的友谊和战争
@@ -3514,34 +3686,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>好吧我也没忍住把这本看完了。我现在最大的困惑其实是：这个作者为什么什么都懂！不光是女人们，男人们的歇斯底里，在她笔下也能驾轻就熟。生活就是如此无望，彼此桎梏，每个人都想要挣脱，可都没有结果，只留下了故事。</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/26986954/</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>新名字的故事 : 那不勒斯四部曲2</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>9787020125265</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>只有你身为女人 才会知道这些丑陋的秘密
 两个女人 50年的友谊和战争
@@ -3556,34 +3728,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>读到一半要气死了，读完了反而释然了，莉拉和莱侬就像两株并生的植物，互相依赖，互相索取，互相想要摆脱对方，又都做不到。不过非常反感作者喜欢在每本书末尾扔炸弹这种做法。</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/26986954/</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>杀死一只知更鸟</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>9787544722766</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
 《杀死一只知更鸟》获1961年普利策奖。
@@ -3597,34 +3769,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>很感人的书，尤其是最后几页。我想以后我要是有孩子了，我要让TA在10岁的时候读这本书，让TA看到人与人的温暖和理解，学会对于“少数人”的包容和同理。这世上很多的罪恶，都来源于多数人对“少数人”的暴力。</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/6781808/</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>杀死一只知更鸟</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>9787544722766</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
 《杀死一只知更鸟》获1961年普利策奖。
@@ -3638,34 +3810,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>她死得无怨无悔，不欠任何人，也不依赖任何东西。她是我见过最勇敢的人。</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/6781808/</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>杀死一只知更鸟</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>9787544722766</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
 《杀死一只知更鸟》获1961年普利策奖。
@@ -3679,34 +3851,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>没有读过这本书的人生跟读过之后的人生，真的很不一样。</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/6781808/</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>杀死一只知更鸟</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>9787544722766</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
 《杀死一只知更鸟》获1961年普利策奖。
@@ -3720,34 +3892,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>偏见不仅会消灭肉体（黑人汤姆之死）也会扼杀灵魂（怪人阿瑟·拉德利一生避世）</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/6781808/</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>杀死一只知更鸟</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>9787544722766</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
 《杀死一只知更鸟》获1961年普利策奖。
@@ -3761,142 +3933,14 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>“除非你穿上一个人的鞋子，像他那样走来走去，否则你永远无法真正了解一个人。”</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/6781808/</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>明朝那些事儿（1-9） : 限量版</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>9787801656087</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>第一次看，还是06年第一本的电子书。后来家里有了本盗版全集，大16开800多页，板砖一样。这两天住院期间带了那本“板砖”重温了一遍，印象最深的是胡宗宪打海盗那段，最大的体会是，人可以没有良心但不能没有理想，没有良心的人未必不能做好事，但没有理想的人，只是苟活世间尔。</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/3674537/</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>明朝那些事儿（1-9） : 限量版</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>9787801656087</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>能勾起你读其他书的书，就是好书。</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/3674537/</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>明朝那些事儿（1-9） : 限量版</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>9787801656087</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>入门佳作，但是作者为了趣味性而牺牲了严谨性。</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/3674537/</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>明朝那些事儿（1-9） : 限量版</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>9787801656087</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>一个寒假看完，不拘一格拆解历史，虽不无主观，但的确很好看；最喜欢2、3集，万国来朝，文治武功，宫闱权斗，兄弟反目，于谦、王阳明伟立光明；中期妖孽盛行，流派林立，皇帝老儿冷眼旁观群臣斗；后期党同伐异，万象争流，妖人牛人猛人一锅粥，270多年的帝国灰飞烟灭，浪滔滔千古风流人物，尽成烟云；官场如职场，厚黑学从来没消失过！</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/3674537/</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3967,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>一部关于厚黑学的血泪史</t>
+          <t>第一次看，还是06年第一本的电子书。后来家里有了本盗版全集，大16开800多页，板砖一样。这两天住院期间带了那本“板砖”重温了一遍，印象最深的是胡宗宪打海盗那段，最大的体会是，人可以没有良心但不能没有理想，没有良心的人未必不能做好事，但没有理想的人，只是苟活世间尔。</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3935,20 +3979,148 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>能勾起你读其他书的书，就是好书。</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>入门佳作，但是作者为了趣味性而牺牲了严谨性。</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>一个寒假看完，不拘一格拆解历史，虽不无主观，但的确很好看；最喜欢2、3集，万国来朝，文治武功，宫闱权斗，兄弟反目，于谦、王阳明伟立光明；中期妖孽盛行，流派林立，皇帝老儿冷眼旁观群臣斗；后期党同伐异，万象争流，妖人牛人猛人一锅粥，270多年的帝国灰飞烟灭，浪滔滔千古风流人物，尽成烟云；官场如职场，厚黑学从来没消失过！</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>一部关于厚黑学的血泪史</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>野草</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
 本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
@@ -3956,34 +4128,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>当我沉默的时候,我觉得充实;我将开口,同时感到空虚。</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1915958/</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>野草</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
 本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
@@ -3991,34 +4163,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>似乎鲁迅经常做噩梦...</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1915958/</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>野草</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
 本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
@@ -4026,34 +4198,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>我不愿彷徨于明暗之间，我不如在黑暗里沉没。</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1915958/</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>野草</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
 本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
@@ -4061,34 +4233,34 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>修行134th，彼时大先生白话文已臻绝顶。这本书是我爹私人藏书中唯一一本鲁迅，我六七岁的时候读过一次，不过必然是有读没有懂，今天读时受到了极大的震撼和感动，昨晚读到手心出汗心绪波动，另外这绝对不是肾虚的表现，我的损友们。最喜欢的是大先生借以自况的复仇者I，于是只剩下广漠的旷野，而他们俩在其间裸着全身，捏着利刃，干枯地立着；以死人似的眼光，赏鉴这路人们的干枯，无血的大戮，而永远沉浸于生命的飞扬的极致的大欢喜中。其次是立论，寥寥几笔白描，爽快淋漓，还有相当几篇感觉没有理解或者没有理解到位，大先生的书，也不是只读一次就可以的</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1915958/</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>野草</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
 本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
@@ -4096,142 +4268,14 @@
 (展开全部)</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>初读，重读，长时间读，掰开揉碎了读，半明半暗地读，不管怎么读都那么有味道，仅是这点有几部散文诗集能做到？</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1915958/</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>沉默的大多数 : 王小波杂文随笔全编</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>9787500627098</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>我对自己的要求很低：我活在世上，无非想要明白些道理，遇见些有趣的事。倘能如我所愿，我的一生就算成功。为此也要去论是非，否则道理不给你明白，有趣的事也不让你遇到。我开始得太晚了，很可能做不成什么，但我总得申明我的态度，所以就有了这本书——为我自己，也代表沉默的大多数。 ——王小波</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/1054685/</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>沉默的大多数 : 王小波杂文随笔全编</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>9787500627098</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>我看现在是冷漠的大多数了</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/1054685/</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>沉默的大多数 : 王小波杂文随笔全编</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>9787500627098</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>与其别人让我闭嘴，不如我自己赶快沉默了去。你的理又不是我的，我跟你辩个五六七八没意思。</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/1054685/</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>沉默的大多数 : 王小波杂文随笔全编</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>9787500627098</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>我们是沉默的大多数，或在内心挣扎，或在脸上写满愤怒，然而结局终究是平庸与顺从。</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>https://book.douban.com/subject/1054685/</t>
         </is>
       </c>
     </row>
@@ -4258,10 +4302,138 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
+          <t>我对自己的要求很低：我活在世上，无非想要明白些道理，遇见些有趣的事。倘能如我所愿，我的一生就算成功。为此也要去论是非，否则道理不给你明白，有趣的事也不让你遇到。我开始得太晚了，很可能做不成什么，但我总得申明我的态度，所以就有了这本书——为我自己，也代表沉默的大多数。 ——王小波</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>我看现在是冷漠的大多数了</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>与其别人让我闭嘴，不如我自己赶快沉默了去。你的理又不是我的，我跟你辩个五六七八没意思。</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>我们是沉默的大多数，或在内心挣扎，或在脸上写满愤怒，然而结局终究是平庸与顺从。</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>看了一半，难以为继。语言风格是揣着聪明装糊涂，可能是时代需要。关键是这聪明在我看来还不够聪明，不过想想，在那个时代，这应当也是冒险了。庆幸自己生在了现在。唯一的收获是，书中说，看杂文看评论的人，永远不能真正了解一门艺术。算是对自己一记警钟。想要广泛涉猎，高谈阔论，却又不曾自己真正深入过什么，算是一种对艺术的亵渎吧。希望自己多一点沉淀。</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>https://book.douban.com/subject/1054685/</t>
         </is>

--- a/豆瓣图书Top250本地数据库.xlsx
+++ b/豆瓣图书Top250本地数据库.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4439,6 +4439,4113 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>盛衰之理，本为天命。然而人心就是如此。眼见得他起高楼，于是便不忍心见他楼塌了。见过他鼎盛的时候，再看他的衰败就无比心酸。而更加可悲的是，目睹这场哗变的你，本就是这戏中之人。</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>第一次看《红楼梦》，是小学五年级。因所有人都说，这是部名著，于是，期末考后，怀着极大的敬意与耐心，准备好好下番苦功夫。不曾想，从头到尾，一点不打绊儿地，没花多长时间，就囫囵吞枣地顺利看完，幼小心灵还因此生出些疑问：怎么一点儿不象名著呀，即不难懂，也不深刻，不就是些家长里短的故事集锦吗！ 留下印象的，不是爱情纠葛，不是阶级矛盾，不是白茫茫一片真干净，而是当时粗糙日常生活中，一些根本无法想象的精美事物：比如，一些菜品，要经过如此多复杂细致的步骤，才能一点点做出；比如，一些庭院宅子，院名的起法，树木的搭配，房子的色彩，有那么多讲究；比如，一些好听的布料名，一些古怪材质的饰品，一些用途不明的摆设；再比如，闲谈，对诗，饮茶……才知道，原来人可以这样生活，可以这样打发时间，而不被视为浪费生命，也无需心下内疚，有些无法理解，又有点儿想入非非。 这或许是文学的另一个用处，让人从踏实细节处，活生生触摸到一个时代的体温。只是后来，每当我跟人说起，《红楼梦》对我来说，就是故事会，就是菜谱与家居指南时，十个会有九个半露出惊讶表情，让我觉得自己，可真没文化！</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>亲戚是干什么用的大全</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>长这么大，到今天才把这部奇书读完。觉得并没有那么多微言大义，倒是曹雪芹的文笔实在了得，对人的那些细腻情感拿捏得十分到位。特别想说的一点是，坚决认为林黛玉不能算是什么完美的理想主义者，她非但不完美，而且是毛病最大的一个。所有的问题又都归结于三个字——看不开！</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>一个呼吁：那些清穿小说的主人公你们风花雪月以后就不能顺道送曹雪芹个打印机么？</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>自然记得从小学到高中的暑假，坐在空调房间的地板上，一边吃西瓜一边沉浸在魔法世界的时光，记得高中时熬夜刷题的间隙，吃一碗泡面，看一会死亡圣器，枯燥的晚上也充满幻想。再见，我曾经心心念念想去的霍格沃兹。</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>至今还记得，读第一本哈利波特的时候，是站在厨房的灯下一口气读完的。</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>伴随了我整个童年成长的经典小说。现下唯一美中不足的应该就是马爱农和马爱新在圣器那一本翻译的时候不停的引用了本山大叔的小品名句“你太有才了”！</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>想说的都在这儿了。 作者：凉白（来自豆瓣） 来源：https://www.douban.com/doubanapp/dispatch/review/8504335 《哈利.波特-(珍藏版)(全七册)》的豆瓣书评:【“死亡不过是另一场伟大的冒险”】</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>长大了才知道哈利波特不仅仅只是儿童读物</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>这是我看过最吓人的一本书。不是可怕而是深深的恐惧。</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>“让人说话天不会塌下来，有话就说，有屁就放，是香是臭，让群众讨论嘛”。 我不信豆瓣审核连教员的话也删。</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>如果尖锐的批评完全消失，温和的批评将会变得刺耳。如果温和的批评也不被允许，沉默将被认为居心叵测。如果沉默也不再允许，赞扬不够卖力将是一种罪行。如果只允许一种声音存在，那么，唯一存在的那个声音就是谎言。－－－摘自油管</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>有种深刻入骨的悲凉。</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>太阳底下无新事，温斯顿在看得见看不见巨大机器前变成了“消失的老鼠”。没有完美的制度，当你感觉到它是完美的时候，它便开始吞噬你了。电幕面前，2+2必须等于5。</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>大刘，你打开了一扇门，门外的世界一片黑暗，这黑暗中蕴藏的故事，永远讲不完。</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>这么个硬核的科幻是怎么装下了程心这朵白莲花婆娘的…</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>书是好书，纸是烂纸，热爱刘慈欣的读者，请不要买这套</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>他们说，读完这套书以后，再抬头看星空感觉就不一样了。嗯，是这样的。</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>一定要和圣母做闺蜜，这样才能有光速飞船坐~</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>每个人都是孤独地出生，在这世间恍惚几十年并不漫长的日子转眼就远去了，然后再孤独地死去。 生命注定是个悲剧，因为我们从没有融入世界，世界永远是身外之物。如果有幸，能在茫茫人海寻得一个身体与灵魂都与自己万分契合的人，与之存在一种可以称之为爱情的联系，然后一起承受生命中不可逃离不可消除的深沉的宿命的孤独。可是这般的幸运艰深难得。有的已失去了爱的能力，有的爱得深沉却无处安放，有的死在这爱里……在所有的爱里，孤独有增无减。 生命只是一场幻梦。</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>看第3遍开始越来越让我惊艳的已不是马尔克斯而是译者了。太牛逼了！这样的文字就算是母语创作也属上乘。尤其倒数第二代布恩迪亚在飓风中破译羊皮卷的全书结尾，笔触磅礴，美到让人惊怖。</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>为什么我觉得不好看呢？是不是我没文化看不懂啊！</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>开始很吃力，越读越上瘾。 惊人得叙事与潮水版的叙事，野兽般撕开真理得外衣。 原来那句经典的开场白，源自这本书。从四姑娘的第一本书，也就开始了他的抄袭生涯。</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>一口气读完但却没有能力评价。</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>有一天我梦醒了，窗外是氤氲不化的雾气，我走到窗边，原来是夜里下了雪，空气一片苍茫，我又想起思嘉，在那场大雾中迷路，恐慌，奔跑，喘息，寻找，家。而瑞德已决意放弃一切。包括她。但我也不是十五岁的我了。那时我见她玫瑰红睡袍，一杯白兰地，手法娴熟，一饮而尽。我怎么学得会像她喝酒这般痛饮人生。可我知道什么是痛。</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>我认为本书唯一值得称赞的人是梅兰妮，一个真正的勇士、一个坚毅的妻子、一个称职的妈妈、一个挚友。</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>其实每个女子在少女时期内心都有一个艾希礼，走到最后才会明白原来自己爱的是班瑞德</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>差不多半年的时间间隙里重看了一遍。快结束时，巴特勒问斯嘉丽多大了，她答28。我突然被狠狠震惊到，两次看书，几次看电影，都觉得看了他们蓬蓬勃勃跌跌荡荡沧海桑田的一辈子，可她才28！</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>我能说“tomorrow is another day.” 这句话对我人生影响很大吗？</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>25岁生日这天把房思琪交付印厂，简体版2018年1月25号上市。做这本书的过程经历了很多，简体版的授权很不容易，感谢游击文化对我们的信任和配合。简体版也得到了他们的认可，除了几处极个别的涉台词语外极少删减，性描写也基本保留，奕含写的克制而干净，实无删改之必要。感谢出版社老师对这本书的爱护，尊重了作者文字。感谢李银河戴锦华张悦然詹宏志蒋方舟等老师的郑重推荐。感谢很多人，为了房思琪和更多读者的相遇。这本书值得也应该被更多人看到，是我的初衷，也是我的目标。 ps2020.07房思琪精装版出版，把在出版两年多里收到的建议做了用心调整。</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>她懂得很多，说话也很深刻，但却有一种单纯感。我不知道她是怎么做到的，她是深刻和单纯的糅合体。她访谈时说：在读这本书的时候，你能感受到痛，那是真实的；你能感受到美，那也是真实的。我都感受到了，甚至能够感受到她被折磨而无法解脱的心情，这是林奕含留给我们的遗言。</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>北影阿廖沙、侯亮平【被】销声匿迹；恋童癖许豪杰恢复微信公号实名，并反咬一口将不肯透露举报人信息的豆瓣告上法庭；北航博士罗茜茜时隔十二年实名举报教授陈小武曾对她及多名女生性骚扰——这些，是你朝反性暴力的实时进程，我们的#me too#远未成声势。这本书的出版告诉我们：不，你并没有选择，你不再可以假装世界上没有人以强暴小女孩为乐；假装从未有小女孩遭受强暴；假装房思琪从不存在。因为这本书属于“文学”，但不单单属于文学，它是一个承受残暴性伤害的女生，为自己提前写就的悼文；因为强暴，是人类社会有史以来最大的屠杀。读着林奕含的文字，一再想要哀叹“可惜”。但可惜这个词太傲慢、太冷酷了，终归是活人对她文学天才的掂量，对可能存在的所谓文学成就or损失的收支核算。而她经受的苦痛黑洞，这些，根本不足以抵偿。</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>简体版终于体面问世了：「一切文学，余爱以血书者。」</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>整个阅读过程太需要心理承受力了，林奕含真的很会写，也是真的很懂得人间的丑陋，只是这份懂得代价太大了，全是血与泪，和无数个不眠之夜的自我拷问、自我厌弃、自我洗脑，在真实与自我安慰之间做艰难的选择。书前书后那些评论是没有心肝吗？面对这种文字还他妈在讲创作技巧、比喻太多、用笔太工？每看到一句这样的话，都觉得千千万万个房思琪的苦白受了，都觉得人间不值得。希望每个无意间和自己厌弃的人产生了关联、无意间发生共谋、陷入到难以挣脱的亲密关系的人，都能迈过自厌和自恨，不用否定自己的感情，诚实本身就是一种力量，面对、接受、挣脱、成长。</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>再也分不清猪的脸和人的脸</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>「凡動物一律平等，但是有些動物比別的動物更加平等。」</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>短短112页，却细致地展现了极权如何产生发展控制农场的一切。觉得恐惧的地方在于记忆如何被轻易的篡改，有什么是可以确信的？</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>比天气预报准多了</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>长篇大论还真不如故事一则</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>这书我看得特慢，只要出现一个地名我就想在谷歌地形图上给找出来，然后细细从战略层面揣摩用兵之道。特别是街亭之战，光在地图上找到街亭这个屯兵的小谷道就花了不少功夫，刚开始始终想不明白这个离汉中十万八千里的地方到底哪儿重要，后来研究了下才知道古时天水通长安的道路并非沿渭水河谷顺流而下，而是走官陇古道，街亭正处于古道的咽喉之处，蜀丢街亭就意味着把背后留给了魏国，腹背受敌，命都难保。总之这本书值得对着地形图细细揣摩，尤其是诸葛亮六出祁山那段。</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>这曾经是我在小学时反复阅读的一部经典。我极爱她，甚至愿意写下每一个人的名字，并且愿意为了这部小说而去读裴注三国志。一部《三国演义》，可以说是我的文学启蒙，并且让我读繁体毫无问题..别人喜爱诸葛亮，我独独对吕布、陈宫和貂蝉感到惋惜，并且唾弃张文远，这个只顾保命的伪君子..我当时相信是因为诸侯先死，所以才被极尽抹灭的：当时谁还相信这是小说呢？</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>“书生轻议冢中人，冢中笑尔书生气！”</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>我是三国控，不解释。最喜欢的一部古典文学。</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>四大名著中最先看的一本书。不过当时在看时，倒不是跟着传统盲目崇拜起刘备关羽来，而是对被作者百般贬低的人物产生研究兴趣，如周瑜并不心胸狭窄，鲁肃并不平庸，草船“接”箭的是孙权，被关兴杀死的潘璋和孔明同年去世，袁绍深得民心，吕蒙“士别三日”，另外张飞有文采……</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>译得很好。重看一遍越发觉得BBC的《神探夏洛克》改编的真是好啊真是巧啊</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>个人感觉，福尔摩斯只是作为侦探小说的鼻祖之一的地位，但感觉远没有阿婆（阿加莎克里斯蒂）的书来的让人出乎意料，令人回味无穷。</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>这个应该是我人生中第一套书。。。。刚会认字，还不知道“犹他州”（印象深刻）为何物的时候，就在看男主角们搞基了，情何以堪。。。</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>已经读了不知多少遍但真的读一辈子都读不厌</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>为什么妈妈要把它借人？现在好了，只剩一本了！给人家弄丢了。</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>挽狂澜于既倒，扶大厦之将倾。</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>在书店翻完就成，买回家则如同鸡肋。傅高义写这部书的初衷就是向西方人介绍邓小平和他经历过的大时代，可叹的是，今天我们却要把这样一部写给别人的入门书当作我们了解自我的红宝书。</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>总有人希望这本书能有别出心裁的史料和观点，其实这本书最大的贡献在于理清了从1977年到1992年所有历史事件的脉络</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>按照邓小平的遗愿，他的眼角膜被捐出供眼科研究，内脏被捐出供医学研究，遗体被火化，骨灰盒上覆盖着中国共产党党旗。1997年3月2日，他的骨灰被撒入大海。</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>十几岁的时候渴慕着小王子，一天之间可以看四十四次日落。是在多久之后才明白，看四十四次日落的小王子，他有多么难过。</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>读了好多年，终于读完了，但是实在共鸣不起来，虽然知道那些道理，但真的觉得没什么了不起啊，是我还太幼稚吗？</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>我的玫瑰花儿，只有四个微不足道的刺，用来抵御这个世界。</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>说实话 我看不太懂 但还是跟风给个5星吧 以显示我也是有思想有学识之人</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>虽然我实在幼稚，但我并不怎么喜欢孩童般的纯净，我只爱风浪过后的平静，流水打磨出的清亮，大雪纷飞时的安宁，沧桑看透的纯真，我爱眼冷心热的庄子，人究竟无所逃于天地之间，各适其性，做自己认为有意义的事就好了，无论是统治宇宙还是喝酒点灯，对他们来说，都比爱一朵玫瑰重要，这不是很好的么</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>鲁迅如果不被赋予那么多政治色彩，单看作品也是一个优秀的毒舌家的</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>看他的文章还无法醒悟的人是该有多么可悲</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>一个特立独行的人需要金钱来保持他的尊严，否则就只有被毁灭的份，人们是不能容忍一个穷光蛋的异类的。就象一个老姑娘要用钱保持她的高傲，否则就是耻辱。</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>这部小说，大体上是描写了辛亥革命前后乡村发生的一系列的故事，其中以鞭子、革命、秀才、假洋鬼子，扮演出一幅中国传统社会的浮世绘。在这里，我们不妨感慨，鲁迅笔下人物的生命力。鲁迅是描写了辛亥革命前后，我们已经革命胜利六十多年，但是假洋鬼子、赵老太爷难道就绝迹了吗？咸与维新，却一切照旧。</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>狂人在望着赵家的狗，孔乙己在讲茴字的四种写法，华老栓在拿夏瑜的血馒头，九斤老太在感叹一代不如一代，闰土在隔着厚障壁叫我老爷，圆规杨二嫂在捡东西，阿Q在逗尼姑，耍无赖，闹革命，要困觉，精神胜利法，迅哥在怀念那夜似的豆，那夜似的戏。我们在铁屋子里装睡，想着年轻时做过的许多的梦。</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>比格林好，而且寒假过后的几个月，经常在里面翻出压岁钱</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>《海的女儿》是爱情的启蒙。</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>如果不是叶君健译的就不要看，书者与译者相得益彰，擦出的精致纯美，无人可及</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>写给成人的悲伤童话</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>小时候看是童话 现在再看的话才发现都是悲剧</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>三毛的文字其实没有特别出挑的地方，但是合成一篇，整个却显得真实、清爽。她很好地遵循了白话文“有什么说什么，该怎么说就怎么说”的宗旨，而且她聪明在不在散文中论理，不作生硬的哲思，单纯就事论事，从而反倒能让人身临其境~~印象最深的是她和荷西去偷看别人洗澡灌肠，再如三毛考驾照的那几个考题，好笑极了~~而读到他们遇到三个疯子袭击则心提至喉~~看散文，以前喜欢过余秋雨的辞藻，现在越来越喜欢三毛这类的平淡，平淡是真，写文常常有自炫的诱惑，能抵住诱惑是不容易的。。。【题外】三毛与荷西是般配的一对，如果荷西没有去世地那么早，三毛可能也不会弃世了吧。。。“人”果然是两个人互相支撑在一起才能不倒下的。。。</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>自你之后，再无真正流浪自由的灵魂。</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>再看到 荒山之夜 仍然还是以前的震惊！他们那么随便就经历了一场出生入死，而且完全不在意，人生多么的洒脱啊</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>读过三毛全集，最好的还是这一册。</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>你伤害了我的骄傲！</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>经典武学起于春秋，到北宋达到极盛，南宋有所衰落，元末因明教兴盛中兴。明代更有了东方不败等大师。但期间伽利略的出现已预示其衰落。康熙年间出现牛顿，梯云纵灭绝。道光年间出现卡诺，玄冰掌灭绝。尤其是力学定理建立后，内力和轻功全部消失，梯云纵这种只需吐纳练便可自带反重力系统的轻功彻底消失</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>慕容复是没落皇族子孙，毕生追求皇位，对王语嫣视如草介，段誉是正牌皇帝继承人，却爱美人宁弃江山。你所追的，正是我所弃的，尽道人生的可笑荒谬。</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>因为众生皆苦，便觉得自己也不是很苦。</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>金圣叹评《水浒》论武松为天人，萧峰何尝不是天人。看他有阔处，有毒处，有正处，有良处，有快处，有真处，有捷处，有雅处，有大处，有警处，实是金大侠小说中之第一人。</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>偌大一本书，数百豪杰人物，萧峰一出，全归背景</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>理性的培养、逻辑的思维、高雅的阅读等不能让别人爱你，但却能让你坦然接受不被爱。</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>我一度以为二十多岁是一个人最难熬的一段时间，在这段时间里要实现从少年到青年的转换。看了这四本书之后发现人一辈子都在挣扎，只是每个时期面临的困难不同罢了，我们一直都经历着角色的转换。</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>会让你在读完最后一行后想要重新翻开《我的天才女友》的第一页。</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>也许莉拉吸引尼诺的地方，就是尼诺在她身上，开始看到了以为自己也有的东西，但对比之下他发现自己并没有。她拥有才智，但她没有利用它为自己谋福利，而像贵妇一样在挥霍着自己的才智，就好像对她来说，整个世界的财富都是庸俗的。莉拉的才智是免费的，这就是她让尼诺入迷的原因。“她和其他女人不一样，因为她天生就那么桀骜不驯，不会为任何事儿弯腰。”我们所有人都做出让步了，经过考验、失败和成功，这种让步重新塑造了我们。只有莉拉，没有任何人、任何事可以改变她。不仅如此，随着年龄的增长，她和任何人一样变得顽固和难相处，但她的那些品质一直都原封未动，甚至更加坚固。我们恨她的同时，也害怕她，会对她充满敬意。</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>读完那不勒斯四部曲的雨夜，人生几十年，像是一场玩笑，像是一次为了记录而存在的表演。</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>洪荒巨兽，太巨大了。老陀的体量感真不是盖的，契诃夫、布尔加科夫、《百年孤独》、《悉达多》，简直都好像只是从他身上抽下来一根骨头。一边读一边也遗憾：涅朵奇卡没有写完，卡拉马佐夫没有写完，契诃夫死得那么早...</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>这是一个缺失信仰的年代。这是一个焦虑爆棚的年代。当大家都在忙着读心灵鸡汤，来寻找到人生真谛的时候，推荐你读一读这本《卡拉马佐夫兄弟》，一本被无数大师封神的小说。 这本小说，在文学史上的地位已经毋庸置疑，它极其真实的写出了人性中种种的崇高与丑恶，它像一面镜子，在其中你会看到一个你都不想承认的自己。这本书，是完美的将哲学、神学、心理学融为一体的杰作。 就连最狂傲的，自命为天才的尼采，读完此书也不得不承认：“陀思妥耶夫斯基是我生命中最美好的际遇，他是一个思想深刻的人，他有充分的权利，蔑视我们这些浅薄的德国人。”</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>那时候我太轻狂，只觉得他太多话，没察觉那是另一种沉默，或者说那是沉默的尽头。</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>《宗教大法官》一章另添一星，翻译再添一星，这书至少该打七星！</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>不知是陀氏自身还是荣如德功劳，语言意蕴丰满，两本大部头看起来很愉快。上海译文这版版式不错，插画精美，如果有精装版就更好了。当时的俄罗斯刚刚破除农奴制，新思潮涌入，宗教却依然占据主导。陀氏虽然拥有一定的倾向性，但理性的光芒已锐不可当。感觉“宗教大法官”和“魔鬼。伊万·费奥多罗维奇的梦魇”两节最为精彩，其中“宗”一节直接逼问上帝，毫不留情揭露宗教，大快人心。相比之下，想到《我的个神啊》这种幼稚的意淫如此为人追捧，只得耻笑。</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>我很真诚的讲：作者用极其扎实的故事告诉了女人们，为什么不能太早结婚以及为什么要坚持上学读书……（一本真正的女性主义小说</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>你以为那不勒斯很远，但是那种女性才懂的绝望和迷茫是全世界通用的。</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>这套小说有一种奇怪的魔力，完全手不释卷，停不下来，会想一口气看掉，沉迷在人物波澜壮阔的情感和命运里。有一种看情节剧的错觉，而且一点也不累人，翻起来又快又兴奋。莉拉的命运啊，真的，最后在工厂里那一幕，哭死了，为她心碎，她的疯狂和大胆，她的天才和倔强。而莱农的心理描写也非常好看，直接而无任何保留，以后她会袒露自己，还是把自己写成故事呢。现在配角的人物形象都开始丰满起来，但是尼诺反倒有点让人爱不起来，在莉拉的光芒下，他显得迟疑而孱弱，反倒是恩佐和莉拉一起学习的画面又一次激动了人心。继续等第三部第四部，想知道莉拉如何继续把控她的命运。</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>好吧我也没忍住把这本看完了。我现在最大的困惑其实是：这个作者为什么什么都懂！不光是女人们，男人们的歇斯底里，在她笔下也能驾轻就熟。生活就是如此无望，彼此桎梏，每个人都想要挣脱，可都没有结果，只留下了故事。</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>读到一半要气死了，读完了反而释然了，莉拉和莱侬就像两株并生的植物，互相依赖，互相索取，互相想要摆脱对方，又都做不到。不过非常反感作者喜欢在每本书末尾扔炸弹这种做法。</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>很感人的书，尤其是最后几页。我想以后我要是有孩子了，我要让TA在10岁的时候读这本书，让TA看到人与人的温暖和理解，学会对于“少数人”的包容和同理。这世上很多的罪恶，都来源于多数人对“少数人”的暴力。</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>她死得无怨无悔，不欠任何人，也不依赖任何东西。她是我见过最勇敢的人。</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>没有读过这本书的人生跟读过之后的人生，真的很不一样。</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>偏见不仅会消灭肉体（黑人汤姆之死）也会扼杀灵魂（怪人阿瑟·拉德利一生避世）</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>“除非你穿上一个人的鞋子，像他那样走来走去，否则你永远无法真正了解一个人。”</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>第一次看，还是06年第一本的电子书。后来家里有了本盗版全集，大16开800多页，板砖一样。这两天住院期间带了那本“板砖”重温了一遍，印象最深的是胡宗宪打海盗那段，最大的体会是，人可以没有良心但不能没有理想，没有良心的人未必不能做好事，但没有理想的人，只是苟活世间尔。</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>能勾起你读其他书的书，就是好书。</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>入门佳作，但是作者为了趣味性而牺牲了严谨性。</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>一个寒假看完，不拘一格拆解历史，虽不无主观，但的确很好看；最喜欢2、3集，万国来朝，文治武功，宫闱权斗，兄弟反目，于谦、王阳明伟立光明；中期妖孽盛行，流派林立，皇帝老儿冷眼旁观群臣斗；后期党同伐异，万象争流，妖人牛人猛人一锅粥，270多年的帝国灰飞烟灭，浪滔滔千古风流人物，尽成烟云；官场如职场，厚黑学从来没消失过！</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>一部关于厚黑学的血泪史</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>当我沉默的时候,我觉得充实;我将开口,同时感到空虚。</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>似乎鲁迅经常做噩梦...</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>我不愿彷徨于明暗之间，我不如在黑暗里沉没。</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>修行134th，彼时大先生白话文已臻绝顶。这本书是我爹私人藏书中唯一一本鲁迅，我六七岁的时候读过一次，不过必然是有读没有懂，今天读时受到了极大的震撼和感动，昨晚读到手心出汗心绪波动，另外这绝对不是肾虚的表现，我的损友们。最喜欢的是大先生借以自况的复仇者I，于是只剩下广漠的旷野，而他们俩在其间裸着全身，捏着利刃，干枯地立着；以死人似的眼光，赏鉴这路人们的干枯，无血的大戮，而永远沉浸于生命的飞扬的极致的大欢喜中。其次是立论，寥寥几笔白描，爽快淋漓，还有相当几篇感觉没有理解或者没有理解到位，大先生的书，也不是只读一次就可以的</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>初读，重读，长时间读，掰开揉碎了读，半明半暗地读，不管怎么读都那么有味道，仅是这点有几部散文诗集能做到？</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>我对自己的要求很低：我活在世上，无非想要明白些道理，遇见些有趣的事。倘能如我所愿，我的一生就算成功。为此也要去论是非，否则道理不给你明白，有趣的事也不让你遇到。我开始得太晚了，很可能做不成什么，但我总得申明我的态度，所以就有了这本书——为我自己，也代表沉默的大多数。 ——王小波</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>我看现在是冷漠的大多数了</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>与其别人让我闭嘴，不如我自己赶快沉默了去。你的理又不是我的，我跟你辩个五六七八没意思。</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>我们是沉默的大多数，或在内心挣扎，或在脸上写满愤怒，然而结局终究是平庸与顺从。</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>看了一半，难以为继。语言风格是揣着聪明装糊涂，可能是时代需要。关键是这聪明在我看来还不够聪明，不过想想，在那个时代，这应当也是冒险了。庆幸自己生在了现在。唯一的收获是，书中说，看杂文看评论的人，永远不能真正了解一门艺术。算是对自己一记警钟。想要广泛涉猎，高谈阔论，却又不曾自己真正深入过什么，算是一种对艺术的亵渎吧。希望自己多一点沉淀。</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/豆瓣图书Top250本地数据库.xlsx
+++ b/豆瓣图书Top250本地数据库.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F231"/>
+  <dimension ref="A1:F352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8546,6 +8546,4289 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>盛衰之理，本为天命。然而人心就是如此。眼见得他起高楼，于是便不忍心见他楼塌了。见过他鼎盛的时候，再看他的衰败就无比心酸。而更加可悲的是，目睹这场哗变的你，本就是这戏中之人。</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>第一次看《红楼梦》，是小学五年级。因所有人都说，这是部名著，于是，期末考后，怀着极大的敬意与耐心，准备好好下番苦功夫。不曾想，从头到尾，一点不打绊儿地，没花多长时间，就囫囵吞枣地顺利看完，幼小心灵还因此生出些疑问：怎么一点儿不象名著呀，即不难懂，也不深刻，不就是些家长里短的故事集锦吗！ 留下印象的，不是爱情纠葛，不是阶级矛盾，不是白茫茫一片真干净，而是当时粗糙日常生活中，一些根本无法想象的精美事物：比如，一些菜品，要经过如此多复杂细致的步骤，才能一点点做出；比如，一些庭院宅子，院名的起法，树木的搭配，房子的色彩，有那么多讲究；比如，一些好听的布料名，一些古怪材质的饰品，一些用途不明的摆设；再比如，闲谈，对诗，饮茶……才知道，原来人可以这样生活，可以这样打发时间，而不被视为浪费生命，也无需心下内疚，有些无法理解，又有点儿想入非非。 这或许是文学的另一个用处，让人从踏实细节处，活生生触摸到一个时代的体温。只是后来，每当我跟人说起，《红楼梦》对我来说，就是故事会，就是菜谱与家居指南时，十个会有九个半露出惊讶表情，让我觉得自己，可真没文化！</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>亲戚是干什么用的大全</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>长这么大，到今天才把这部奇书读完。觉得并没有那么多微言大义，倒是曹雪芹的文笔实在了得，对人的那些细腻情感拿捏得十分到位。特别想说的一点是，坚决认为林黛玉不能算是什么完美的理想主义者，她非但不完美，而且是毛病最大的一个。所有的问题又都归结于三个字——看不开！</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>一个呼吁：那些清穿小说的主人公你们风花雪月以后就不能顺道送曹雪芹个打印机么？</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>读《活着》的过程我很平静，除了有庆献血而死的描述让我呼吸急促。在那个年代像福贵式的悲剧小人物多如牛毛，他们愚昧，勤劳，坚强，隐忍，他们被时代的洪流裹挟着无法喘息，唯有努力活下去才能活下去。福贵的悲哀是每一个中国人的悲哀，谁都无法幸免。第一次读余华，他看似沉重冷静的描述却字字见血。</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>读起来太顺畅，经典就是经典</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>看见了人生悲苦，看见了底层人民的乐观和坚强，看见了生命的柔韧，看见了命运和岁月那不动声色的力量。</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>第一次见序这么多的一本书。（但是三星是更复杂的原因，短评里说不清的原因，不是因为序多……）</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>在《活着》中，管去世叫“熟了”。最初是福贵的爹“熟了”，初闻不解，后文说道，人死像熟透的梨，离树而落。梨者，离也。</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>自然记得从小学到高中的暑假，坐在空调房间的地板上，一边吃西瓜一边沉浸在魔法世界的时光，记得高中时熬夜刷题的间隙，吃一碗泡面，看一会死亡圣器，枯燥的晚上也充满幻想。再见，我曾经心心念念想去的霍格沃兹。</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>至今还记得，读第一本哈利波特的时候，是站在厨房的灯下一口气读完的。</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>伴随了我整个童年成长的经典小说。现下唯一美中不足的应该就是马爱农和马爱新在圣器那一本翻译的时候不停的引用了本山大叔的小品名句“你太有才了”！</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>想说的都在这儿了。 作者：凉白（来自豆瓣） 来源：https://www.douban.com/doubanapp/dispatch/review/8504335 《哈利.波特-(珍藏版)(全七册)》的豆瓣书评:【“死亡不过是另一场伟大的冒险”】</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>长大了才知道哈利波特不仅仅只是儿童读物</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>这是我看过最吓人的一本书。不是可怕而是深深的恐惧。</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>“让人说话天不会塌下来，有话就说，有屁就放，是香是臭，让群众讨论嘛”。 我不信豆瓣审核连教员的话也删。</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>如果尖锐的批评完全消失，温和的批评将会变得刺耳。如果温和的批评也不被允许，沉默将被认为居心叵测。如果沉默也不再允许，赞扬不够卖力将是一种罪行。如果只允许一种声音存在，那么，唯一存在的那个声音就是谎言。－－－摘自油管</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>有种深刻入骨的悲凉。</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>太阳底下无新事，温斯顿在看得见看不见巨大机器前变成了“消失的老鼠”。没有完美的制度，当你感觉到它是完美的时候，它便开始吞噬你了。电幕面前，2+2必须等于5。</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>大刘，你打开了一扇门，门外的世界一片黑暗，这黑暗中蕴藏的故事，永远讲不完。</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>这么个硬核的科幻是怎么装下了程心这朵白莲花婆娘的…</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>书是好书，纸是烂纸，热爱刘慈欣的读者，请不要买这套</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>他们说，读完这套书以后，再抬头看星空感觉就不一样了。嗯，是这样的。</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>一定要和圣母做闺蜜，这样才能有光速飞船坐~</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>有一天我梦醒了，窗外是氤氲不化的雾气，我走到窗边，原来是夜里下了雪，空气一片苍茫，我又想起思嘉，在那场大雾中迷路，恐慌，奔跑，喘息，寻找，家。而瑞德已决意放弃一切。包括她。但我也不是十五岁的我了。那时我见她玫瑰红睡袍，一杯白兰地，手法娴熟，一饮而尽。我怎么学得会像她喝酒这般痛饮人生。可我知道什么是痛。</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>我认为本书唯一值得称赞的人是梅兰妮，一个真正的勇士、一个坚毅的妻子、一个称职的妈妈、一个挚友。</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>其实每个女子在少女时期内心都有一个艾希礼，走到最后才会明白原来自己爱的是班瑞德</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>差不多半年的时间间隙里重看了一遍。快结束时，巴特勒问斯嘉丽多大了，她答28。我突然被狠狠震惊到，两次看书，几次看电影，都觉得看了他们蓬蓬勃勃跌跌荡荡沧海桑田的一辈子，可她才28！</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>我能说“tomorrow is another day.” 这句话对我人生影响很大吗？</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>25岁生日这天把房思琪交付印厂，简体版2018年1月25号上市。做这本书的过程经历了很多，简体版的授权很不容易，感谢游击文化对我们的信任和配合。简体版也得到了他们的认可，除了几处极个别的涉台词语外极少删减，性描写也基本保留，奕含写的克制而干净，实无删改之必要。感谢出版社老师对这本书的爱护，尊重了作者文字。感谢李银河戴锦华张悦然詹宏志蒋方舟等老师的郑重推荐。感谢很多人，为了房思琪和更多读者的相遇。这本书值得也应该被更多人看到，是我的初衷，也是我的目标。 ps2020.07房思琪精装版出版，把在出版两年多里收到的建议做了用心调整。</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>她懂得很多，说话也很深刻，但却有一种单纯感。我不知道她是怎么做到的，她是深刻和单纯的糅合体。她访谈时说：在读这本书的时候，你能感受到痛，那是真实的；你能感受到美，那也是真实的。我都感受到了，甚至能够感受到她被折磨而无法解脱的心情，这是林奕含留给我们的遗言。</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>北影阿廖沙、侯亮平【被】销声匿迹；恋童癖许豪杰恢复微信公号实名，并反咬一口将不肯透露举报人信息的豆瓣告上法庭；北航博士罗茜茜时隔十二年实名举报教授陈小武曾对她及多名女生性骚扰——这些，是你朝反性暴力的实时进程，我们的#me too#远未成声势。这本书的出版告诉我们：不，你并没有选择，你不再可以假装世界上没有人以强暴小女孩为乐；假装从未有小女孩遭受强暴；假装房思琪从不存在。因为这本书属于“文学”，但不单单属于文学，它是一个承受残暴性伤害的女生，为自己提前写就的悼文；因为强暴，是人类社会有史以来最大的屠杀。读着林奕含的文字，一再想要哀叹“可惜”。但可惜这个词太傲慢、太冷酷了，终归是活人对她文学天才的掂量，对可能存在的所谓文学成就or损失的收支核算。而她经受的苦痛黑洞，这些，根本不足以抵偿。</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>简体版终于体面问世了：「一切文学，余爱以血书者。」</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>整个阅读过程太需要心理承受力了，林奕含真的很会写，也是真的很懂得人间的丑陋，只是这份懂得代价太大了，全是血与泪，和无数个不眠之夜的自我拷问、自我厌弃、自我洗脑，在真实与自我安慰之间做艰难的选择。书前书后那些评论是没有心肝吗？面对这种文字还他妈在讲创作技巧、比喻太多、用笔太工？每看到一句这样的话，都觉得千千万万个房思琪的苦白受了，都觉得人间不值得。希望每个无意间和自己厌弃的人产生了关联、无意间发生共谋、陷入到难以挣脱的亲密关系的人，都能迈过自厌和自恨，不用否定自己的感情，诚实本身就是一种力量，面对、接受、挣脱、成长。</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>再也分不清猪的脸和人的脸</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>「凡動物一律平等，但是有些動物比別的動物更加平等。」</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>短短112页，却细致地展现了极权如何产生发展控制农场的一切。觉得恐惧的地方在于记忆如何被轻易的篡改，有什么是可以确信的？</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>比天气预报准多了</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>长篇大论还真不如故事一则</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>这书我看得特慢，只要出现一个地名我就想在谷歌地形图上给找出来，然后细细从战略层面揣摩用兵之道。特别是街亭之战，光在地图上找到街亭这个屯兵的小谷道就花了不少功夫，刚开始始终想不明白这个离汉中十万八千里的地方到底哪儿重要，后来研究了下才知道古时天水通长安的道路并非沿渭水河谷顺流而下，而是走官陇古道，街亭正处于古道的咽喉之处，蜀丢街亭就意味着把背后留给了魏国，腹背受敌，命都难保。总之这本书值得对着地形图细细揣摩，尤其是诸葛亮六出祁山那段。</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>这曾经是我在小学时反复阅读的一部经典。我极爱她，甚至愿意写下每一个人的名字，并且愿意为了这部小说而去读裴注三国志。一部《三国演义》，可以说是我的文学启蒙，并且让我读繁体毫无问题..别人喜爱诸葛亮，我独独对吕布、陈宫和貂蝉感到惋惜，并且唾弃张文远，这个只顾保命的伪君子..我当时相信是因为诸侯先死，所以才被极尽抹灭的：当时谁还相信这是小说呢？</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>“书生轻议冢中人，冢中笑尔书生气！”</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>我是三国控，不解释。最喜欢的一部古典文学。</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>四大名著中最先看的一本书。不过当时在看时，倒不是跟着传统盲目崇拜起刘备关羽来，而是对被作者百般贬低的人物产生研究兴趣，如周瑜并不心胸狭窄，鲁肃并不平庸，草船“接”箭的是孙权，被关兴杀死的潘璋和孔明同年去世，袁绍深得民心，吕蒙“士别三日”，另外张飞有文采……</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>译得很好。重看一遍越发觉得BBC的《神探夏洛克》改编的真是好啊真是巧啊</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>个人感觉，福尔摩斯只是作为侦探小说的鼻祖之一的地位，但感觉远没有阿婆（阿加莎克里斯蒂）的书来的让人出乎意料，令人回味无穷。</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>这个应该是我人生中第一套书。。。。刚会认字，还不知道“犹他州”（印象深刻）为何物的时候，就在看男主角们搞基了，情何以堪。。。</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>已经读了不知多少遍但真的读一辈子都读不厌</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>为什么妈妈要把它借人？现在好了，只剩一本了！给人家弄丢了。</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>新版封面，严重剧透。</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>把小说写成这样绝对是开挂了吧，除了连番登场的几十号人物，随处雕琢的大时代的背景也让人叹为观止。对人性的挖掘比起吉田修一还是弱一些，就是纯好看，从第一句开始吸住你逐渐往往里掉。</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>情有可原，罪无可恕。</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>故事中男女主人公从头到尾没有一句对白，经典。</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>张无忌的妈妈也说过 不要轻易相信漂亮女人 她们的演技和城府都是你无法想象的 无删减版本比之前的版本多了关于性的描写 阴茎和乳房等词汇也直接被接纳进来 前十章用来构建人物关系和埋下案件伏笔 从第十章开始抽丝剥茧地隐现真相 枪虾和虾虎鱼（雪穗和桐原）的关系日渐明朗 遗憾的是关于后半段作者的笔锋开始出现倦怠 没有给出很完整明确的指示或者暗示 对于最后整体的真相的揭露也并没有很吃惊 除了娈童之外 其他的因果其实已了然于心</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>挽狂澜于既倒，扶大厦之将倾。</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>在书店翻完就成，买回家则如同鸡肋。傅高义写这部书的初衷就是向西方人介绍邓小平和他经历过的大时代，可叹的是，今天我们却要把这样一部写给别人的入门书当作我们了解自我的红宝书。</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>总有人希望这本书能有别出心裁的史料和观点，其实这本书最大的贡献在于理清了从1977年到1992年所有历史事件的脉络</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>按照邓小平的遗愿，他的眼角膜被捐出供眼科研究，内脏被捐出供医学研究，遗体被火化，骨灰盒上覆盖着中国共产党党旗。1997年3月2日，他的骨灰被撒入大海。</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>十几岁的时候渴慕着小王子，一天之间可以看四十四次日落。是在多久之后才明白，看四十四次日落的小王子，他有多么难过。</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>读了好多年，终于读完了，但是实在共鸣不起来，虽然知道那些道理，但真的觉得没什么了不起啊，是我还太幼稚吗？</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>我的玫瑰花儿，只有四个微不足道的刺，用来抵御这个世界。</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>说实话 我看不太懂 但还是跟风给个5星吧 以显示我也是有思想有学识之人</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>虽然我实在幼稚，但我并不怎么喜欢孩童般的纯净，我只爱风浪过后的平静，流水打磨出的清亮，大雪纷飞时的安宁，沧桑看透的纯真，我爱眼冷心热的庄子，人究竟无所逃于天地之间，各适其性，做自己认为有意义的事就好了，无论是统治宇宙还是喝酒点灯，对他们来说，都比爱一朵玫瑰重要，这不是很好的么</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>鲁迅如果不被赋予那么多政治色彩，单看作品也是一个优秀的毒舌家的</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>看他的文章还无法醒悟的人是该有多么可悲</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>一个特立独行的人需要金钱来保持他的尊严，否则就只有被毁灭的份，人们是不能容忍一个穷光蛋的异类的。就象一个老姑娘要用钱保持她的高傲，否则就是耻辱。</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>这部小说，大体上是描写了辛亥革命前后乡村发生的一系列的故事，其中以鞭子、革命、秀才、假洋鬼子，扮演出一幅中国传统社会的浮世绘。在这里，我们不妨感慨，鲁迅笔下人物的生命力。鲁迅是描写了辛亥革命前后，我们已经革命胜利六十多年，但是假洋鬼子、赵老太爷难道就绝迹了吗？咸与维新，却一切照旧。</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>狂人在望着赵家的狗，孔乙己在讲茴字的四种写法，华老栓在拿夏瑜的血馒头，九斤老太在感叹一代不如一代，闰土在隔着厚障壁叫我老爷，圆规杨二嫂在捡东西，阿Q在逗尼姑，耍无赖，闹革命，要困觉，精神胜利法，迅哥在怀念那夜似的豆，那夜似的戏。我们在铁屋子里装睡，想着年轻时做过的许多的梦。</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>比格林好，而且寒假过后的几个月，经常在里面翻出压岁钱</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>《海的女儿》是爱情的启蒙。</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>如果不是叶君健译的就不要看，书者与译者相得益彰，擦出的精致纯美，无人可及</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>写给成人的悲伤童话</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>小时候看是童话 现在再看的话才发现都是悲剧</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>三毛的文字其实没有特别出挑的地方，但是合成一篇，整个却显得真实、清爽。她很好地遵循了白话文“有什么说什么，该怎么说就怎么说”的宗旨，而且她聪明在不在散文中论理，不作生硬的哲思，单纯就事论事，从而反倒能让人身临其境~~印象最深的是她和荷西去偷看别人洗澡灌肠，再如三毛考驾照的那几个考题，好笑极了~~而读到他们遇到三个疯子袭击则心提至喉~~看散文，以前喜欢过余秋雨的辞藻，现在越来越喜欢三毛这类的平淡，平淡是真，写文常常有自炫的诱惑，能抵住诱惑是不容易的。。。【题外】三毛与荷西是般配的一对，如果荷西没有去世地那么早，三毛可能也不会弃世了吧。。。“人”果然是两个人互相支撑在一起才能不倒下的。。。</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>自你之后，再无真正流浪自由的灵魂。</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>再看到 荒山之夜 仍然还是以前的震惊！他们那么随便就经历了一场出生入死，而且完全不在意，人生多么的洒脱啊</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>读过三毛全集，最好的还是这一册。</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>你伤害了我的骄傲！</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>经典武学起于春秋，到北宋达到极盛，南宋有所衰落，元末因明教兴盛中兴。明代更有了东方不败等大师。但期间伽利略的出现已预示其衰落。康熙年间出现牛顿，梯云纵灭绝。道光年间出现卡诺，玄冰掌灭绝。尤其是力学定理建立后，内力和轻功全部消失，梯云纵这种只需吐纳练便可自带反重力系统的轻功彻底消失</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>慕容复是没落皇族子孙，毕生追求皇位，对王语嫣视如草介，段誉是正牌皇帝继承人，却爱美人宁弃江山。你所追的，正是我所弃的，尽道人生的可笑荒谬。</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>因为众生皆苦，便觉得自己也不是很苦。</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>金圣叹评《水浒》论武松为天人，萧峰何尝不是天人。看他有阔处，有毒处，有正处，有良处，有快处，有真处，有捷处，有雅处，有大处，有警处，实是金大侠小说中之第一人。</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>偌大一本书，数百豪杰人物，萧峰一出，全归背景</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>理性的培养、逻辑的思维、高雅的阅读等不能让别人爱你，但却能让你坦然接受不被爱。</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>我一度以为二十多岁是一个人最难熬的一段时间，在这段时间里要实现从少年到青年的转换。看了这四本书之后发现人一辈子都在挣扎，只是每个时期面临的困难不同罢了，我们一直都经历着角色的转换。</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>会让你在读完最后一行后想要重新翻开《我的天才女友》的第一页。</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>也许莉拉吸引尼诺的地方，就是尼诺在她身上，开始看到了以为自己也有的东西，但对比之下他发现自己并没有。她拥有才智，但她没有利用它为自己谋福利，而像贵妇一样在挥霍着自己的才智，就好像对她来说，整个世界的财富都是庸俗的。莉拉的才智是免费的，这就是她让尼诺入迷的原因。“她和其他女人不一样，因为她天生就那么桀骜不驯，不会为任何事儿弯腰。”我们所有人都做出让步了，经过考验、失败和成功，这种让步重新塑造了我们。只有莉拉，没有任何人、任何事可以改变她。不仅如此，随着年龄的增长，她和任何人一样变得顽固和难相处，但她的那些品质一直都原封未动，甚至更加坚固。我们恨她的同时，也害怕她，会对她充满敬意。</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>读完那不勒斯四部曲的雨夜，人生几十年，像是一场玩笑，像是一次为了记录而存在的表演。</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>洪荒巨兽，太巨大了。老陀的体量感真不是盖的，契诃夫、布尔加科夫、《百年孤独》、《悉达多》，简直都好像只是从他身上抽下来一根骨头。一边读一边也遗憾：涅朵奇卡没有写完，卡拉马佐夫没有写完，契诃夫死得那么早...</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>这是一个缺失信仰的年代。这是一个焦虑爆棚的年代。当大家都在忙着读心灵鸡汤，来寻找到人生真谛的时候，推荐你读一读这本《卡拉马佐夫兄弟》，一本被无数大师封神的小说。 这本小说，在文学史上的地位已经毋庸置疑，它极其真实的写出了人性中种种的崇高与丑恶，它像一面镜子，在其中你会看到一个你都不想承认的自己。这本书，是完美的将哲学、神学、心理学融为一体的杰作。 就连最狂傲的，自命为天才的尼采，读完此书也不得不承认：“陀思妥耶夫斯基是我生命中最美好的际遇，他是一个思想深刻的人，他有充分的权利，蔑视我们这些浅薄的德国人。”</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>那时候我太轻狂，只觉得他太多话，没察觉那是另一种沉默，或者说那是沉默的尽头。</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>《宗教大法官》一章另添一星，翻译再添一星，这书至少该打七星！</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>不知是陀氏自身还是荣如德功劳，语言意蕴丰满，两本大部头看起来很愉快。上海译文这版版式不错，插画精美，如果有精装版就更好了。当时的俄罗斯刚刚破除农奴制，新思潮涌入，宗教却依然占据主导。陀氏虽然拥有一定的倾向性，但理性的光芒已锐不可当。感觉“宗教大法官”和“魔鬼。伊万·费奥多罗维奇的梦魇”两节最为精彩，其中“宗”一节直接逼问上帝，毫不留情揭露宗教，大快人心。相比之下，想到《我的个神啊》这种幼稚的意淫如此为人追捧，只得耻笑。</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>我很真诚的讲：作者用极其扎实的故事告诉了女人们，为什么不能太早结婚以及为什么要坚持上学读书……（一本真正的女性主义小说</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>你以为那不勒斯很远，但是那种女性才懂的绝望和迷茫是全世界通用的。</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>这套小说有一种奇怪的魔力，完全手不释卷，停不下来，会想一口气看掉，沉迷在人物波澜壮阔的情感和命运里。有一种看情节剧的错觉，而且一点也不累人，翻起来又快又兴奋。莉拉的命运啊，真的，最后在工厂里那一幕，哭死了，为她心碎，她的疯狂和大胆，她的天才和倔强。而莱农的心理描写也非常好看，直接而无任何保留，以后她会袒露自己，还是把自己写成故事呢。现在配角的人物形象都开始丰满起来，但是尼诺反倒有点让人爱不起来，在莉拉的光芒下，他显得迟疑而孱弱，反倒是恩佐和莉拉一起学习的画面又一次激动了人心。继续等第三部第四部，想知道莉拉如何继续把控她的命运。</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>好吧我也没忍住把这本看完了。我现在最大的困惑其实是：这个作者为什么什么都懂！不光是女人们，男人们的歇斯底里，在她笔下也能驾轻就熟。生活就是如此无望，彼此桎梏，每个人都想要挣脱，可都没有结果，只留下了故事。</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>读到一半要气死了，读完了反而释然了，莉拉和莱侬就像两株并生的植物，互相依赖，互相索取，互相想要摆脱对方，又都做不到。不过非常反感作者喜欢在每本书末尾扔炸弹这种做法。</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>很感人的书，尤其是最后几页。我想以后我要是有孩子了，我要让TA在10岁的时候读这本书，让TA看到人与人的温暖和理解，学会对于“少数人”的包容和同理。这世上很多的罪恶，都来源于多数人对“少数人”的暴力。</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>她死得无怨无悔，不欠任何人，也不依赖任何东西。她是我见过最勇敢的人。</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>没有读过这本书的人生跟读过之后的人生，真的很不一样。</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>偏见不仅会消灭肉体（黑人汤姆之死）也会扼杀灵魂（怪人阿瑟·拉德利一生避世）</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>“除非你穿上一个人的鞋子，像他那样走来走去，否则你永远无法真正了解一个人。”</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>第一次看，还是06年第一本的电子书。后来家里有了本盗版全集，大16开800多页，板砖一样。这两天住院期间带了那本“板砖”重温了一遍，印象最深的是胡宗宪打海盗那段，最大的体会是，人可以没有良心但不能没有理想，没有良心的人未必不能做好事，但没有理想的人，只是苟活世间尔。</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>能勾起你读其他书的书，就是好书。</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>入门佳作，但是作者为了趣味性而牺牲了严谨性。</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>一个寒假看完，不拘一格拆解历史，虽不无主观，但的确很好看；最喜欢2、3集，万国来朝，文治武功，宫闱权斗，兄弟反目，于谦、王阳明伟立光明；中期妖孽盛行，流派林立，皇帝老儿冷眼旁观群臣斗；后期党同伐异，万象争流，妖人牛人猛人一锅粥，270多年的帝国灰飞烟灭，浪滔滔千古风流人物，尽成烟云；官场如职场，厚黑学从来没消失过！</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>一部关于厚黑学的血泪史</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>当我沉默的时候,我觉得充实;我将开口,同时感到空虚。</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>似乎鲁迅经常做噩梦...</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>我不愿彷徨于明暗之间，我不如在黑暗里沉没。</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>修行134th，彼时大先生白话文已臻绝顶。这本书是我爹私人藏书中唯一一本鲁迅，我六七岁的时候读过一次，不过必然是有读没有懂，今天读时受到了极大的震撼和感动，昨晚读到手心出汗心绪波动，另外这绝对不是肾虚的表现，我的损友们。最喜欢的是大先生借以自况的复仇者I，于是只剩下广漠的旷野，而他们俩在其间裸着全身，捏着利刃，干枯地立着；以死人似的眼光，赏鉴这路人们的干枯，无血的大戮，而永远沉浸于生命的飞扬的极致的大欢喜中。其次是立论，寥寥几笔白描，爽快淋漓，还有相当几篇感觉没有理解或者没有理解到位，大先生的书，也不是只读一次就可以的</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>初读，重读，长时间读，掰开揉碎了读，半明半暗地读，不管怎么读都那么有味道，仅是这点有几部散文诗集能做到？</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>我对自己的要求很低：我活在世上，无非想要明白些道理，遇见些有趣的事。倘能如我所愿，我的一生就算成功。为此也要去论是非，否则道理不给你明白，有趣的事也不让你遇到。我开始得太晚了，很可能做不成什么，但我总得申明我的态度，所以就有了这本书——为我自己，也代表沉默的大多数。 ——王小波</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>我看现在是冷漠的大多数了</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>与其别人让我闭嘴，不如我自己赶快沉默了去。你的理又不是我的，我跟你辩个五六七八没意思。</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>我们是沉默的大多数，或在内心挣扎，或在脸上写满愤怒，然而结局终究是平庸与顺从。</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>看了一半，难以为继。语言风格是揣着聪明装糊涂，可能是时代需要。关键是这聪明在我看来还不够聪明，不过想想，在那个时代，这应当也是冒险了。庆幸自己生在了现在。唯一的收获是，书中说，看杂文看评论的人，永远不能真正了解一门艺术。算是对自己一记警钟。想要广泛涉猎，高谈阔论，却又不曾自己真正深入过什么，算是一种对艺术的亵渎吧。希望自己多一点沉淀。</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/豆瓣图书Top250本地数据库.xlsx
+++ b/豆瓣图书Top250本地数据库.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F352"/>
+  <dimension ref="A1:F465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12829,6 +12829,3977 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>盛衰之理，本为天命。然而人心就是如此。眼见得他起高楼，于是便不忍心见他楼塌了。见过他鼎盛的时候，再看他的衰败就无比心酸。而更加可悲的是，目睹这场哗变的你，本就是这戏中之人。</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>第一次看《红楼梦》，是小学五年级。因所有人都说，这是部名著，于是，期末考后，怀着极大的敬意与耐心，准备好好下番苦功夫。不曾想，从头到尾，一点不打绊儿地，没花多长时间，就囫囵吞枣地顺利看完，幼小心灵还因此生出些疑问：怎么一点儿不象名著呀，即不难懂，也不深刻，不就是些家长里短的故事集锦吗！ 留下印象的，不是爱情纠葛，不是阶级矛盾，不是白茫茫一片真干净，而是当时粗糙日常生活中，一些根本无法想象的精美事物：比如，一些菜品，要经过如此多复杂细致的步骤，才能一点点做出；比如，一些庭院宅子，院名的起法，树木的搭配，房子的色彩，有那么多讲究；比如，一些好听的布料名，一些古怪材质的饰品，一些用途不明的摆设；再比如，闲谈，对诗，饮茶……才知道，原来人可以这样生活，可以这样打发时间，而不被视为浪费生命，也无需心下内疚，有些无法理解，又有点儿想入非非。 这或许是文学的另一个用处，让人从踏实细节处，活生生触摸到一个时代的体温。只是后来，每当我跟人说起，《红楼梦》对我来说，就是故事会，就是菜谱与家居指南时，十个会有九个半露出惊讶表情，让我觉得自己，可真没文化！</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>亲戚是干什么用的大全</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>长这么大，到今天才把这部奇书读完。觉得并没有那么多微言大义，倒是曹雪芹的文笔实在了得，对人的那些细腻情感拿捏得十分到位。特别想说的一点是，坚决认为林黛玉不能算是什么完美的理想主义者，她非但不完美，而且是毛病最大的一个。所有的问题又都归结于三个字——看不开！</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>一个呼吁：那些清穿小说的主人公你们风花雪月以后就不能顺道送曹雪芹个打印机么？</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>自然记得从小学到高中的暑假，坐在空调房间的地板上，一边吃西瓜一边沉浸在魔法世界的时光，记得高中时熬夜刷题的间隙，吃一碗泡面，看一会死亡圣器，枯燥的晚上也充满幻想。再见，我曾经心心念念想去的霍格沃兹。</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>至今还记得，读第一本哈利波特的时候，是站在厨房的灯下一口气读完的。</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>伴随了我整个童年成长的经典小说。现下唯一美中不足的应该就是马爱农和马爱新在圣器那一本翻译的时候不停的引用了本山大叔的小品名句“你太有才了”！</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>想说的都在这儿了。 作者：凉白（来自豆瓣） 来源：https://www.douban.com/doubanapp/dispatch/review/8504335 《哈利.波特-(珍藏版)(全七册)》的豆瓣书评:【“死亡不过是另一场伟大的冒险”】</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>长大了才知道哈利波特不仅仅只是儿童读物</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>这是我看过最吓人的一本书。不是可怕而是深深的恐惧。</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>“让人说话天不会塌下来，有话就说，有屁就放，是香是臭，让群众讨论嘛”。 我不信豆瓣审核连教员的话也删。</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>如果尖锐的批评完全消失，温和的批评将会变得刺耳。如果温和的批评也不被允许，沉默将被认为居心叵测。如果沉默也不再允许，赞扬不够卖力将是一种罪行。如果只允许一种声音存在，那么，唯一存在的那个声音就是谎言。－－－摘自油管</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>有种深刻入骨的悲凉。</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>太阳底下无新事，温斯顿在看得见看不见巨大机器前变成了“消失的老鼠”。没有完美的制度，当你感觉到它是完美的时候，它便开始吞噬你了。电幕面前，2+2必须等于5。</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>大刘，你打开了一扇门，门外的世界一片黑暗，这黑暗中蕴藏的故事，永远讲不完。</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>这么个硬核的科幻是怎么装下了程心这朵白莲花婆娘的…</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>书是好书，纸是烂纸，热爱刘慈欣的读者，请不要买这套</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>他们说，读完这套书以后，再抬头看星空感觉就不一样了。嗯，是这样的。</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>一定要和圣母做闺蜜，这样才能有光速飞船坐~</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>每个人都是孤独地出生，在这世间恍惚几十年并不漫长的日子转眼就远去了，然后再孤独地死去。 生命注定是个悲剧，因为我们从没有融入世界，世界永远是身外之物。如果有幸，能在茫茫人海寻得一个身体与灵魂都与自己万分契合的人，与之存在一种可以称之为爱情的联系，然后一起承受生命中不可逃离不可消除的深沉的宿命的孤独。可是这般的幸运艰深难得。有的已失去了爱的能力，有的爱得深沉却无处安放，有的死在这爱里……在所有的爱里，孤独有增无减。 生命只是一场幻梦。</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>看第3遍开始越来越让我惊艳的已不是马尔克斯而是译者了。太牛逼了！这样的文字就算是母语创作也属上乘。尤其倒数第二代布恩迪亚在飓风中破译羊皮卷的全书结尾，笔触磅礴，美到让人惊怖。</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>为什么我觉得不好看呢？是不是我没文化看不懂啊！</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>开始很吃力，越读越上瘾。 惊人得叙事与潮水版的叙事，野兽般撕开真理得外衣。 原来那句经典的开场白，源自这本书。从四姑娘的第一本书，也就开始了他的抄袭生涯。</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>一口气读完但却没有能力评价。</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>有一天我梦醒了，窗外是氤氲不化的雾气，我走到窗边，原来是夜里下了雪，空气一片苍茫，我又想起思嘉，在那场大雾中迷路，恐慌，奔跑，喘息，寻找，家。而瑞德已决意放弃一切。包括她。但我也不是十五岁的我了。那时我见她玫瑰红睡袍，一杯白兰地，手法娴熟，一饮而尽。我怎么学得会像她喝酒这般痛饮人生。可我知道什么是痛。</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>我认为本书唯一值得称赞的人是梅兰妮，一个真正的勇士、一个坚毅的妻子、一个称职的妈妈、一个挚友。</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>其实每个女子在少女时期内心都有一个艾希礼，走到最后才会明白原来自己爱的是班瑞德</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>差不多半年的时间间隙里重看了一遍。快结束时，巴特勒问斯嘉丽多大了，她答28。我突然被狠狠震惊到，两次看书，几次看电影，都觉得看了他们蓬蓬勃勃跌跌荡荡沧海桑田的一辈子，可她才28！</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>我能说“tomorrow is another day.” 这句话对我人生影响很大吗？</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>25岁生日这天把房思琪交付印厂，简体版2018年1月25号上市。做这本书的过程经历了很多，简体版的授权很不容易，感谢游击文化对我们的信任和配合。简体版也得到了他们的认可，除了几处极个别的涉台词语外极少删减，性描写也基本保留，奕含写的克制而干净，实无删改之必要。感谢出版社老师对这本书的爱护，尊重了作者文字。感谢李银河戴锦华张悦然詹宏志蒋方舟等老师的郑重推荐。感谢很多人，为了房思琪和更多读者的相遇。这本书值得也应该被更多人看到，是我的初衷，也是我的目标。 ps2020.07房思琪精装版出版，把在出版两年多里收到的建议做了用心调整。</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>她懂得很多，说话也很深刻，但却有一种单纯感。我不知道她是怎么做到的，她是深刻和单纯的糅合体。她访谈时说：在读这本书的时候，你能感受到痛，那是真实的；你能感受到美，那也是真实的。我都感受到了，甚至能够感受到她被折磨而无法解脱的心情，这是林奕含留给我们的遗言。</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>北影阿廖沙、侯亮平【被】销声匿迹；恋童癖许豪杰恢复微信公号实名，并反咬一口将不肯透露举报人信息的豆瓣告上法庭；北航博士罗茜茜时隔十二年实名举报教授陈小武曾对她及多名女生性骚扰——这些，是你朝反性暴力的实时进程，我们的#me too#远未成声势。这本书的出版告诉我们：不，你并没有选择，你不再可以假装世界上没有人以强暴小女孩为乐；假装从未有小女孩遭受强暴；假装房思琪从不存在。因为这本书属于“文学”，但不单单属于文学，它是一个承受残暴性伤害的女生，为自己提前写就的悼文；因为强暴，是人类社会有史以来最大的屠杀。读着林奕含的文字，一再想要哀叹“可惜”。但可惜这个词太傲慢、太冷酷了，终归是活人对她文学天才的掂量，对可能存在的所谓文学成就or损失的收支核算。而她经受的苦痛黑洞，这些，根本不足以抵偿。</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>简体版终于体面问世了：「一切文学，余爱以血书者。」</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>整个阅读过程太需要心理承受力了，林奕含真的很会写，也是真的很懂得人间的丑陋，只是这份懂得代价太大了，全是血与泪，和无数个不眠之夜的自我拷问、自我厌弃、自我洗脑，在真实与自我安慰之间做艰难的选择。书前书后那些评论是没有心肝吗？面对这种文字还他妈在讲创作技巧、比喻太多、用笔太工？每看到一句这样的话，都觉得千千万万个房思琪的苦白受了，都觉得人间不值得。希望每个无意间和自己厌弃的人产生了关联、无意间发生共谋、陷入到难以挣脱的亲密关系的人，都能迈过自厌和自恨，不用否定自己的感情，诚实本身就是一种力量，面对、接受、挣脱、成长。</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>再也分不清猪的脸和人的脸</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>「凡動物一律平等，但是有些動物比別的動物更加平等。」</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>短短112页，却细致地展现了极权如何产生发展控制农场的一切。觉得恐惧的地方在于记忆如何被轻易的篡改，有什么是可以确信的？</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>比天气预报准多了</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>长篇大论还真不如故事一则</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>这书我看得特慢，只要出现一个地名我就想在谷歌地形图上给找出来，然后细细从战略层面揣摩用兵之道。特别是街亭之战，光在地图上找到街亭这个屯兵的小谷道就花了不少功夫，刚开始始终想不明白这个离汉中十万八千里的地方到底哪儿重要，后来研究了下才知道古时天水通长安的道路并非沿渭水河谷顺流而下，而是走官陇古道，街亭正处于古道的咽喉之处，蜀丢街亭就意味着把背后留给了魏国，腹背受敌，命都难保。总之这本书值得对着地形图细细揣摩，尤其是诸葛亮六出祁山那段。</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>这曾经是我在小学时反复阅读的一部经典。我极爱她，甚至愿意写下每一个人的名字，并且愿意为了这部小说而去读裴注三国志。一部《三国演义》，可以说是我的文学启蒙，并且让我读繁体毫无问题..别人喜爱诸葛亮，我独独对吕布、陈宫和貂蝉感到惋惜，并且唾弃张文远，这个只顾保命的伪君子..我当时相信是因为诸侯先死，所以才被极尽抹灭的：当时谁还相信这是小说呢？</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>“书生轻议冢中人，冢中笑尔书生气！”</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>我是三国控，不解释。最喜欢的一部古典文学。</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>四大名著中最先看的一本书。不过当时在看时，倒不是跟着传统盲目崇拜起刘备关羽来，而是对被作者百般贬低的人物产生研究兴趣，如周瑜并不心胸狭窄，鲁肃并不平庸，草船“接”箭的是孙权，被关兴杀死的潘璋和孔明同年去世，袁绍深得民心，吕蒙“士别三日”，另外张飞有文采……</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>译得很好。重看一遍越发觉得BBC的《神探夏洛克》改编的真是好啊真是巧啊</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>个人感觉，福尔摩斯只是作为侦探小说的鼻祖之一的地位，但感觉远没有阿婆（阿加莎克里斯蒂）的书来的让人出乎意料，令人回味无穷。</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>这个应该是我人生中第一套书。。。。刚会认字，还不知道“犹他州”（印象深刻）为何物的时候，就在看男主角们搞基了，情何以堪。。。</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>已经读了不知多少遍但真的读一辈子都读不厌</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>为什么妈妈要把它借人？现在好了，只剩一本了！给人家弄丢了。</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>挽狂澜于既倒，扶大厦之将倾。</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>在书店翻完就成，买回家则如同鸡肋。傅高义写这部书的初衷就是向西方人介绍邓小平和他经历过的大时代，可叹的是，今天我们却要把这样一部写给别人的入门书当作我们了解自我的红宝书。</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>总有人希望这本书能有别出心裁的史料和观点，其实这本书最大的贡献在于理清了从1977年到1992年所有历史事件的脉络</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>按照邓小平的遗愿，他的眼角膜被捐出供眼科研究，内脏被捐出供医学研究，遗体被火化，骨灰盒上覆盖着中国共产党党旗。1997年3月2日，他的骨灰被撒入大海。</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>鲁迅如果不被赋予那么多政治色彩，单看作品也是一个优秀的毒舌家的</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>看他的文章还无法醒悟的人是该有多么可悲</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>一个特立独行的人需要金钱来保持他的尊严，否则就只有被毁灭的份，人们是不能容忍一个穷光蛋的异类的。就象一个老姑娘要用钱保持她的高傲，否则就是耻辱。</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>这部小说，大体上是描写了辛亥革命前后乡村发生的一系列的故事，其中以鞭子、革命、秀才、假洋鬼子，扮演出一幅中国传统社会的浮世绘。在这里，我们不妨感慨，鲁迅笔下人物的生命力。鲁迅是描写了辛亥革命前后，我们已经革命胜利六十多年，但是假洋鬼子、赵老太爷难道就绝迹了吗？咸与维新，却一切照旧。</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>狂人在望着赵家的狗，孔乙己在讲茴字的四种写法，华老栓在拿夏瑜的血馒头，九斤老太在感叹一代不如一代，闰土在隔着厚障壁叫我老爷，圆规杨二嫂在捡东西，阿Q在逗尼姑，耍无赖，闹革命，要困觉，精神胜利法，迅哥在怀念那夜似的豆，那夜似的戏。我们在铁屋子里装睡，想着年轻时做过的许多的梦。</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>比格林好，而且寒假过后的几个月，经常在里面翻出压岁钱</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>《海的女儿》是爱情的启蒙。</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>如果不是叶君健译的就不要看，书者与译者相得益彰，擦出的精致纯美，无人可及</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>写给成人的悲伤童话</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>小时候看是童话 现在再看的话才发现都是悲剧</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>三毛的文字其实没有特别出挑的地方，但是合成一篇，整个却显得真实、清爽。她很好地遵循了白话文“有什么说什么，该怎么说就怎么说”的宗旨，而且她聪明在不在散文中论理，不作生硬的哲思，单纯就事论事，从而反倒能让人身临其境~~印象最深的是她和荷西去偷看别人洗澡灌肠，再如三毛考驾照的那几个考题，好笑极了~~而读到他们遇到三个疯子袭击则心提至喉~~看散文，以前喜欢过余秋雨的辞藻，现在越来越喜欢三毛这类的平淡，平淡是真，写文常常有自炫的诱惑，能抵住诱惑是不容易的。。。【题外】三毛与荷西是般配的一对，如果荷西没有去世地那么早，三毛可能也不会弃世了吧。。。“人”果然是两个人互相支撑在一起才能不倒下的。。。</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>自你之后，再无真正流浪自由的灵魂。</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>再看到 荒山之夜 仍然还是以前的震惊！他们那么随便就经历了一场出生入死，而且完全不在意，人生多么的洒脱啊</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>读过三毛全集，最好的还是这一册。</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>你伤害了我的骄傲！</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>经典武学起于春秋，到北宋达到极盛，南宋有所衰落，元末因明教兴盛中兴。明代更有了东方不败等大师。但期间伽利略的出现已预示其衰落。康熙年间出现牛顿，梯云纵灭绝。道光年间出现卡诺，玄冰掌灭绝。尤其是力学定理建立后，内力和轻功全部消失，梯云纵这种只需吐纳练便可自带反重力系统的轻功彻底消失</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>慕容复是没落皇族子孙，毕生追求皇位，对王语嫣视如草介，段誉是正牌皇帝继承人，却爱美人宁弃江山。你所追的，正是我所弃的，尽道人生的可笑荒谬。</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>因为众生皆苦，便觉得自己也不是很苦。</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>金圣叹评《水浒》论武松为天人，萧峰何尝不是天人。看他有阔处，有毒处，有正处，有良处，有快处，有真处，有捷处，有雅处，有大处，有警处，实是金大侠小说中之第一人。</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>偌大一本书，数百豪杰人物，萧峰一出，全归背景</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>理性的培养、逻辑的思维、高雅的阅读等不能让别人爱你，但却能让你坦然接受不被爱。</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>我一度以为二十多岁是一个人最难熬的一段时间，在这段时间里要实现从少年到青年的转换。看了这四本书之后发现人一辈子都在挣扎，只是每个时期面临的困难不同罢了，我们一直都经历着角色的转换。</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>会让你在读完最后一行后想要重新翻开《我的天才女友》的第一页。</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>也许莉拉吸引尼诺的地方，就是尼诺在她身上，开始看到了以为自己也有的东西，但对比之下他发现自己并没有。她拥有才智，但她没有利用它为自己谋福利，而像贵妇一样在挥霍着自己的才智，就好像对她来说，整个世界的财富都是庸俗的。莉拉的才智是免费的，这就是她让尼诺入迷的原因。“她和其他女人不一样，因为她天生就那么桀骜不驯，不会为任何事儿弯腰。”我们所有人都做出让步了，经过考验、失败和成功，这种让步重新塑造了我们。只有莉拉，没有任何人、任何事可以改变她。不仅如此，随着年龄的增长，她和任何人一样变得顽固和难相处，但她的那些品质一直都原封未动，甚至更加坚固。我们恨她的同时，也害怕她，会对她充满敬意。</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>读完那不勒斯四部曲的雨夜，人生几十年，像是一场玩笑，像是一次为了记录而存在的表演。</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>洪荒巨兽，太巨大了。老陀的体量感真不是盖的，契诃夫、布尔加科夫、《百年孤独》、《悉达多》，简直都好像只是从他身上抽下来一根骨头。一边读一边也遗憾：涅朵奇卡没有写完，卡拉马佐夫没有写完，契诃夫死得那么早...</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>这是一个缺失信仰的年代。这是一个焦虑爆棚的年代。当大家都在忙着读心灵鸡汤，来寻找到人生真谛的时候，推荐你读一读这本《卡拉马佐夫兄弟》，一本被无数大师封神的小说。 这本小说，在文学史上的地位已经毋庸置疑，它极其真实的写出了人性中种种的崇高与丑恶，它像一面镜子，在其中你会看到一个你都不想承认的自己。这本书，是完美的将哲学、神学、心理学融为一体的杰作。 就连最狂傲的，自命为天才的尼采，读完此书也不得不承认：“陀思妥耶夫斯基是我生命中最美好的际遇，他是一个思想深刻的人，他有充分的权利，蔑视我们这些浅薄的德国人。”</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>那时候我太轻狂，只觉得他太多话，没察觉那是另一种沉默，或者说那是沉默的尽头。</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>《宗教大法官》一章另添一星，翻译再添一星，这书至少该打七星！</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>不知是陀氏自身还是荣如德功劳，语言意蕴丰满，两本大部头看起来很愉快。上海译文这版版式不错，插画精美，如果有精装版就更好了。当时的俄罗斯刚刚破除农奴制，新思潮涌入，宗教却依然占据主导。陀氏虽然拥有一定的倾向性，但理性的光芒已锐不可当。感觉“宗教大法官”和“魔鬼。伊万·费奥多罗维奇的梦魇”两节最为精彩，其中“宗”一节直接逼问上帝，毫不留情揭露宗教，大快人心。相比之下，想到《我的个神啊》这种幼稚的意淫如此为人追捧，只得耻笑。</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>我很真诚的讲：作者用极其扎实的故事告诉了女人们，为什么不能太早结婚以及为什么要坚持上学读书……（一本真正的女性主义小说</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>你以为那不勒斯很远，但是那种女性才懂的绝望和迷茫是全世界通用的。</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>这套小说有一种奇怪的魔力，完全手不释卷，停不下来，会想一口气看掉，沉迷在人物波澜壮阔的情感和命运里。有一种看情节剧的错觉，而且一点也不累人，翻起来又快又兴奋。莉拉的命运啊，真的，最后在工厂里那一幕，哭死了，为她心碎，她的疯狂和大胆，她的天才和倔强。而莱农的心理描写也非常好看，直接而无任何保留，以后她会袒露自己，还是把自己写成故事呢。现在配角的人物形象都开始丰满起来，但是尼诺反倒有点让人爱不起来，在莉拉的光芒下，他显得迟疑而孱弱，反倒是恩佐和莉拉一起学习的画面又一次激动了人心。继续等第三部第四部，想知道莉拉如何继续把控她的命运。</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>好吧我也没忍住把这本看完了。我现在最大的困惑其实是：这个作者为什么什么都懂！不光是女人们，男人们的歇斯底里，在她笔下也能驾轻就熟。生活就是如此无望，彼此桎梏，每个人都想要挣脱，可都没有结果，只留下了故事。</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>读到一半要气死了，读完了反而释然了，莉拉和莱侬就像两株并生的植物，互相依赖，互相索取，互相想要摆脱对方，又都做不到。不过非常反感作者喜欢在每本书末尾扔炸弹这种做法。</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>很感人的书，尤其是最后几页。我想以后我要是有孩子了，我要让TA在10岁的时候读这本书，让TA看到人与人的温暖和理解，学会对于“少数人”的包容和同理。这世上很多的罪恶，都来源于多数人对“少数人”的暴力。</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>她死得无怨无悔，不欠任何人，也不依赖任何东西。她是我见过最勇敢的人。</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>没有读过这本书的人生跟读过之后的人生，真的很不一样。</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>偏见不仅会消灭肉体（黑人汤姆之死）也会扼杀灵魂（怪人阿瑟·拉德利一生避世）</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>“除非你穿上一个人的鞋子，像他那样走来走去，否则你永远无法真正了解一个人。”</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>第一次看，还是06年第一本的电子书。后来家里有了本盗版全集，大16开800多页，板砖一样。这两天住院期间带了那本“板砖”重温了一遍，印象最深的是胡宗宪打海盗那段，最大的体会是，人可以没有良心但不能没有理想，没有良心的人未必不能做好事，但没有理想的人，只是苟活世间尔。</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>能勾起你读其他书的书，就是好书。</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>入门佳作，但是作者为了趣味性而牺牲了严谨性。</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>一个寒假看完，不拘一格拆解历史，虽不无主观，但的确很好看；最喜欢2、3集，万国来朝，文治武功，宫闱权斗，兄弟反目，于谦、王阳明伟立光明；中期妖孽盛行，流派林立，皇帝老儿冷眼旁观群臣斗；后期党同伐异，万象争流，妖人牛人猛人一锅粥，270多年的帝国灰飞烟灭，浪滔滔千古风流人物，尽成烟云；官场如职场，厚黑学从来没消失过！</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>一部关于厚黑学的血泪史</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>当我沉默的时候,我觉得充实;我将开口,同时感到空虚。</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>似乎鲁迅经常做噩梦...</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>我不愿彷徨于明暗之间，我不如在黑暗里沉没。</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>修行134th，彼时大先生白话文已臻绝顶。这本书是我爹私人藏书中唯一一本鲁迅，我六七岁的时候读过一次，不过必然是有读没有懂，今天读时受到了极大的震撼和感动，昨晚读到手心出汗心绪波动，另外这绝对不是肾虚的表现，我的损友们。最喜欢的是大先生借以自况的复仇者I，于是只剩下广漠的旷野，而他们俩在其间裸着全身，捏着利刃，干枯地立着；以死人似的眼光，赏鉴这路人们的干枯，无血的大戮，而永远沉浸于生命的飞扬的极致的大欢喜中。其次是立论，寥寥几笔白描，爽快淋漓，还有相当几篇感觉没有理解或者没有理解到位，大先生的书，也不是只读一次就可以的</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>初读，重读，长时间读，掰开揉碎了读，半明半暗地读，不管怎么读都那么有味道，仅是这点有几部散文诗集能做到？</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>我对自己的要求很低：我活在世上，无非想要明白些道理，遇见些有趣的事。倘能如我所愿，我的一生就算成功。为此也要去论是非，否则道理不给你明白，有趣的事也不让你遇到。我开始得太晚了，很可能做不成什么，但我总得申明我的态度，所以就有了这本书——为我自己，也代表沉默的大多数。 ——王小波</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>我看现在是冷漠的大多数了</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>与其别人让我闭嘴，不如我自己赶快沉默了去。你的理又不是我的，我跟你辩个五六七八没意思。</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>我们是沉默的大多数，或在内心挣扎，或在脸上写满愤怒，然而结局终究是平庸与顺从。</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>看了一半，难以为继。语言风格是揣着聪明装糊涂，可能是时代需要。关键是这聪明在我看来还不够聪明，不过想想，在那个时代，这应当也是冒险了。庆幸自己生在了现在。唯一的收获是，书中说，看杂文看评论的人，永远不能真正了解一门艺术。算是对自己一记警钟。想要广泛涉猎，高谈阔论，却又不曾自己真正深入过什么，算是一种对艺术的亵渎吧。希望自己多一点沉淀。</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/豆瓣图书Top250本地数据库.xlsx
+++ b/豆瓣图书Top250本地数据库.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F465"/>
+  <dimension ref="A1:F582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16800,6 +16800,4157 @@
         </is>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>盛衰之理，本为天命。然而人心就是如此。眼见得他起高楼，于是便不忍心见他楼塌了。见过他鼎盛的时候，再看他的衰败就无比心酸。而更加可悲的是，目睹这场哗变的你，本就是这戏中之人。</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>第一次看《红楼梦》，是小学五年级。因所有人都说，这是部名著，于是，期末考后，怀着极大的敬意与耐心，准备好好下番苦功夫。不曾想，从头到尾，一点不打绊儿地，没花多长时间，就囫囵吞枣地顺利看完，幼小心灵还因此生出些疑问：怎么一点儿不象名著呀，即不难懂，也不深刻，不就是些家长里短的故事集锦吗！ 留下印象的，不是爱情纠葛，不是阶级矛盾，不是白茫茫一片真干净，而是当时粗糙日常生活中，一些根本无法想象的精美事物：比如，一些菜品，要经过如此多复杂细致的步骤，才能一点点做出；比如，一些庭院宅子，院名的起法，树木的搭配，房子的色彩，有那么多讲究；比如，一些好听的布料名，一些古怪材质的饰品，一些用途不明的摆设；再比如，闲谈，对诗，饮茶……才知道，原来人可以这样生活，可以这样打发时间，而不被视为浪费生命，也无需心下内疚，有些无法理解，又有点儿想入非非。 这或许是文学的另一个用处，让人从踏实细节处，活生生触摸到一个时代的体温。只是后来，每当我跟人说起，《红楼梦》对我来说，就是故事会，就是菜谱与家居指南时，十个会有九个半露出惊讶表情，让我觉得自己，可真没文化！</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>亲戚是干什么用的大全</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>长这么大，到今天才把这部奇书读完。觉得并没有那么多微言大义，倒是曹雪芹的文笔实在了得，对人的那些细腻情感拿捏得十分到位。特别想说的一点是，坚决认为林黛玉不能算是什么完美的理想主义者，她非但不完美，而且是毛病最大的一个。所有的问题又都归结于三个字——看不开！</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>一个呼吁：那些清穿小说的主人公你们风花雪月以后就不能顺道送曹雪芹个打印机么？</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>自然记得从小学到高中的暑假，坐在空调房间的地板上，一边吃西瓜一边沉浸在魔法世界的时光，记得高中时熬夜刷题的间隙，吃一碗泡面，看一会死亡圣器，枯燥的晚上也充满幻想。再见，我曾经心心念念想去的霍格沃兹。</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>至今还记得，读第一本哈利波特的时候，是站在厨房的灯下一口气读完的。</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>伴随了我整个童年成长的经典小说。现下唯一美中不足的应该就是马爱农和马爱新在圣器那一本翻译的时候不停的引用了本山大叔的小品名句“你太有才了”！</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>想说的都在这儿了。 作者：凉白（来自豆瓣） 来源：https://www.douban.com/doubanapp/dispatch/review/8504335 《哈利.波特-(珍藏版)(全七册)》的豆瓣书评:【“死亡不过是另一场伟大的冒险”】</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>长大了才知道哈利波特不仅仅只是儿童读物</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>这是我看过最吓人的一本书。不是可怕而是深深的恐惧。</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>“让人说话天不会塌下来，有话就说，有屁就放，是香是臭，让群众讨论嘛”。 我不信豆瓣审核连教员的话也删。</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>如果尖锐的批评完全消失，温和的批评将会变得刺耳。如果温和的批评也不被允许，沉默将被认为居心叵测。如果沉默也不再允许，赞扬不够卖力将是一种罪行。如果只允许一种声音存在，那么，唯一存在的那个声音就是谎言。－－－摘自油管</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>有种深刻入骨的悲凉。</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>太阳底下无新事，温斯顿在看得见看不见巨大机器前变成了“消失的老鼠”。没有完美的制度，当你感觉到它是完美的时候，它便开始吞噬你了。电幕面前，2+2必须等于5。</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>大刘，你打开了一扇门，门外的世界一片黑暗，这黑暗中蕴藏的故事，永远讲不完。</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>这么个硬核的科幻是怎么装下了程心这朵白莲花婆娘的…</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>书是好书，纸是烂纸，热爱刘慈欣的读者，请不要买这套</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>他们说，读完这套书以后，再抬头看星空感觉就不一样了。嗯，是这样的。</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>一定要和圣母做闺蜜，这样才能有光速飞船坐~</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>有一天我梦醒了，窗外是氤氲不化的雾气，我走到窗边，原来是夜里下了雪，空气一片苍茫，我又想起思嘉，在那场大雾中迷路，恐慌，奔跑，喘息，寻找，家。而瑞德已决意放弃一切。包括她。但我也不是十五岁的我了。那时我见她玫瑰红睡袍，一杯白兰地，手法娴熟，一饮而尽。我怎么学得会像她喝酒这般痛饮人生。可我知道什么是痛。</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>我认为本书唯一值得称赞的人是梅兰妮，一个真正的勇士、一个坚毅的妻子、一个称职的妈妈、一个挚友。</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>其实每个女子在少女时期内心都有一个艾希礼，走到最后才会明白原来自己爱的是班瑞德</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>差不多半年的时间间隙里重看了一遍。快结束时，巴特勒问斯嘉丽多大了，她答28。我突然被狠狠震惊到，两次看书，几次看电影，都觉得看了他们蓬蓬勃勃跌跌荡荡沧海桑田的一辈子，可她才28！</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>我能说“tomorrow is another day.” 这句话对我人生影响很大吗？</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>25岁生日这天把房思琪交付印厂，简体版2018年1月25号上市。做这本书的过程经历了很多，简体版的授权很不容易，感谢游击文化对我们的信任和配合。简体版也得到了他们的认可，除了几处极个别的涉台词语外极少删减，性描写也基本保留，奕含写的克制而干净，实无删改之必要。感谢出版社老师对这本书的爱护，尊重了作者文字。感谢李银河戴锦华张悦然詹宏志蒋方舟等老师的郑重推荐。感谢很多人，为了房思琪和更多读者的相遇。这本书值得也应该被更多人看到，是我的初衷，也是我的目标。 ps2020.07房思琪精装版出版，把在出版两年多里收到的建议做了用心调整。</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>她懂得很多，说话也很深刻，但却有一种单纯感。我不知道她是怎么做到的，她是深刻和单纯的糅合体。她访谈时说：在读这本书的时候，你能感受到痛，那是真实的；你能感受到美，那也是真实的。我都感受到了，甚至能够感受到她被折磨而无法解脱的心情，这是林奕含留给我们的遗言。</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>北影阿廖沙、侯亮平【被】销声匿迹；恋童癖许豪杰恢复微信公号实名，并反咬一口将不肯透露举报人信息的豆瓣告上法庭；北航博士罗茜茜时隔十二年实名举报教授陈小武曾对她及多名女生性骚扰——这些，是你朝反性暴力的实时进程，我们的#me too#远未成声势。这本书的出版告诉我们：不，你并没有选择，你不再可以假装世界上没有人以强暴小女孩为乐；假装从未有小女孩遭受强暴；假装房思琪从不存在。因为这本书属于“文学”，但不单单属于文学，它是一个承受残暴性伤害的女生，为自己提前写就的悼文；因为强暴，是人类社会有史以来最大的屠杀。读着林奕含的文字，一再想要哀叹“可惜”。但可惜这个词太傲慢、太冷酷了，终归是活人对她文学天才的掂量，对可能存在的所谓文学成就or损失的收支核算。而她经受的苦痛黑洞，这些，根本不足以抵偿。</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>简体版终于体面问世了：「一切文学，余爱以血书者。」</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>整个阅读过程太需要心理承受力了，林奕含真的很会写，也是真的很懂得人间的丑陋，只是这份懂得代价太大了，全是血与泪，和无数个不眠之夜的自我拷问、自我厌弃、自我洗脑，在真实与自我安慰之间做艰难的选择。书前书后那些评论是没有心肝吗？面对这种文字还他妈在讲创作技巧、比喻太多、用笔太工？每看到一句这样的话，都觉得千千万万个房思琪的苦白受了，都觉得人间不值得。希望每个无意间和自己厌弃的人产生了关联、无意间发生共谋、陷入到难以挣脱的亲密关系的人，都能迈过自厌和自恨，不用否定自己的感情，诚实本身就是一种力量，面对、接受、挣脱、成长。</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>再也分不清猪的脸和人的脸</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>「凡動物一律平等，但是有些動物比別的動物更加平等。」</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>短短112页，却细致地展现了极权如何产生发展控制农场的一切。觉得恐惧的地方在于记忆如何被轻易的篡改，有什么是可以确信的？</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>比天气预报准多了</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>长篇大论还真不如故事一则</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>这书我看得特慢，只要出现一个地名我就想在谷歌地形图上给找出来，然后细细从战略层面揣摩用兵之道。特别是街亭之战，光在地图上找到街亭这个屯兵的小谷道就花了不少功夫，刚开始始终想不明白这个离汉中十万八千里的地方到底哪儿重要，后来研究了下才知道古时天水通长安的道路并非沿渭水河谷顺流而下，而是走官陇古道，街亭正处于古道的咽喉之处，蜀丢街亭就意味着把背后留给了魏国，腹背受敌，命都难保。总之这本书值得对着地形图细细揣摩，尤其是诸葛亮六出祁山那段。</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>这曾经是我在小学时反复阅读的一部经典。我极爱她，甚至愿意写下每一个人的名字，并且愿意为了这部小说而去读裴注三国志。一部《三国演义》，可以说是我的文学启蒙，并且让我读繁体毫无问题..别人喜爱诸葛亮，我独独对吕布、陈宫和貂蝉感到惋惜，并且唾弃张文远，这个只顾保命的伪君子..我当时相信是因为诸侯先死，所以才被极尽抹灭的：当时谁还相信这是小说呢？</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>“书生轻议冢中人，冢中笑尔书生气！”</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>我是三国控，不解释。最喜欢的一部古典文学。</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>四大名著中最先看的一本书。不过当时在看时，倒不是跟着传统盲目崇拜起刘备关羽来，而是对被作者百般贬低的人物产生研究兴趣，如周瑜并不心胸狭窄，鲁肃并不平庸，草船“接”箭的是孙权，被关兴杀死的潘璋和孔明同年去世，袁绍深得民心，吕蒙“士别三日”，另外张飞有文采……</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>译得很好。重看一遍越发觉得BBC的《神探夏洛克》改编的真是好啊真是巧啊</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>个人感觉，福尔摩斯只是作为侦探小说的鼻祖之一的地位，但感觉远没有阿婆（阿加莎克里斯蒂）的书来的让人出乎意料，令人回味无穷。</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>这个应该是我人生中第一套书。。。。刚会认字，还不知道“犹他州”（印象深刻）为何物的时候，就在看男主角们搞基了，情何以堪。。。</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>已经读了不知多少遍但真的读一辈子都读不厌</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>为什么妈妈要把它借人？现在好了，只剩一本了！给人家弄丢了。</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>新版封面，严重剧透。</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>把小说写成这样绝对是开挂了吧，除了连番登场的几十号人物，随处雕琢的大时代的背景也让人叹为观止。对人性的挖掘比起吉田修一还是弱一些，就是纯好看，从第一句开始吸住你逐渐往往里掉。</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>情有可原，罪无可恕。</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>故事中男女主人公从头到尾没有一句对白，经典。</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>张无忌的妈妈也说过 不要轻易相信漂亮女人 她们的演技和城府都是你无法想象的 无删减版本比之前的版本多了关于性的描写 阴茎和乳房等词汇也直接被接纳进来 前十章用来构建人物关系和埋下案件伏笔 从第十章开始抽丝剥茧地隐现真相 枪虾和虾虎鱼（雪穗和桐原）的关系日渐明朗 遗憾的是关于后半段作者的笔锋开始出现倦怠 没有给出很完整明确的指示或者暗示 对于最后整体的真相的揭露也并没有很吃惊 除了娈童之外 其他的因果其实已了然于心</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>挽狂澜于既倒，扶大厦之将倾。</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>在书店翻完就成，买回家则如同鸡肋。傅高义写这部书的初衷就是向西方人介绍邓小平和他经历过的大时代，可叹的是，今天我们却要把这样一部写给别人的入门书当作我们了解自我的红宝书。</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>总有人希望这本书能有别出心裁的史料和观点，其实这本书最大的贡献在于理清了从1977年到1992年所有历史事件的脉络</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr"/>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>按照邓小平的遗愿，他的眼角膜被捐出供眼科研究，内脏被捐出供医学研究，遗体被火化，骨灰盒上覆盖着中国共产党党旗。1997年3月2日，他的骨灰被撒入大海。</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>十几岁的时候渴慕着小王子，一天之间可以看四十四次日落。是在多久之后才明白，看四十四次日落的小王子，他有多么难过。</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>读了好多年，终于读完了，但是实在共鸣不起来，虽然知道那些道理，但真的觉得没什么了不起啊，是我还太幼稚吗？</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>我的玫瑰花儿，只有四个微不足道的刺，用来抵御这个世界。</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>说实话 我看不太懂 但还是跟风给个5星吧 以显示我也是有思想有学识之人</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>虽然我实在幼稚，但我并不怎么喜欢孩童般的纯净，我只爱风浪过后的平静，流水打磨出的清亮，大雪纷飞时的安宁，沧桑看透的纯真，我爱眼冷心热的庄子，人究竟无所逃于天地之间，各适其性，做自己认为有意义的事就好了，无论是统治宇宙还是喝酒点灯，对他们来说，都比爱一朵玫瑰重要，这不是很好的么</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>鲁迅如果不被赋予那么多政治色彩，单看作品也是一个优秀的毒舌家的</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>看他的文章还无法醒悟的人是该有多么可悲</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>一个特立独行的人需要金钱来保持他的尊严，否则就只有被毁灭的份，人们是不能容忍一个穷光蛋的异类的。就象一个老姑娘要用钱保持她的高傲，否则就是耻辱。</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>这部小说，大体上是描写了辛亥革命前后乡村发生的一系列的故事，其中以鞭子、革命、秀才、假洋鬼子，扮演出一幅中国传统社会的浮世绘。在这里，我们不妨感慨，鲁迅笔下人物的生命力。鲁迅是描写了辛亥革命前后，我们已经革命胜利六十多年，但是假洋鬼子、赵老太爷难道就绝迹了吗？咸与维新，却一切照旧。</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>狂人在望着赵家的狗，孔乙己在讲茴字的四种写法，华老栓在拿夏瑜的血馒头，九斤老太在感叹一代不如一代，闰土在隔着厚障壁叫我老爷，圆规杨二嫂在捡东西，阿Q在逗尼姑，耍无赖，闹革命，要困觉，精神胜利法，迅哥在怀念那夜似的豆，那夜似的戏。我们在铁屋子里装睡，想着年轻时做过的许多的梦。</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>比格林好，而且寒假过后的几个月，经常在里面翻出压岁钱</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>《海的女儿》是爱情的启蒙。</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>如果不是叶君健译的就不要看，书者与译者相得益彰，擦出的精致纯美，无人可及</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>写给成人的悲伤童话</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>小时候看是童话 现在再看的话才发现都是悲剧</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>三毛的文字其实没有特别出挑的地方，但是合成一篇，整个却显得真实、清爽。她很好地遵循了白话文“有什么说什么，该怎么说就怎么说”的宗旨，而且她聪明在不在散文中论理，不作生硬的哲思，单纯就事论事，从而反倒能让人身临其境~~印象最深的是她和荷西去偷看别人洗澡灌肠，再如三毛考驾照的那几个考题，好笑极了~~而读到他们遇到三个疯子袭击则心提至喉~~看散文，以前喜欢过余秋雨的辞藻，现在越来越喜欢三毛这类的平淡，平淡是真，写文常常有自炫的诱惑，能抵住诱惑是不容易的。。。【题外】三毛与荷西是般配的一对，如果荷西没有去世地那么早，三毛可能也不会弃世了吧。。。“人”果然是两个人互相支撑在一起才能不倒下的。。。</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>自你之后，再无真正流浪自由的灵魂。</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>再看到 荒山之夜 仍然还是以前的震惊！他们那么随便就经历了一场出生入死，而且完全不在意，人生多么的洒脱啊</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>读过三毛全集，最好的还是这一册。</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>你伤害了我的骄傲！</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>经典武学起于春秋，到北宋达到极盛，南宋有所衰落，元末因明教兴盛中兴。明代更有了东方不败等大师。但期间伽利略的出现已预示其衰落。康熙年间出现牛顿，梯云纵灭绝。道光年间出现卡诺，玄冰掌灭绝。尤其是力学定理建立后，内力和轻功全部消失，梯云纵这种只需吐纳练便可自带反重力系统的轻功彻底消失</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>慕容复是没落皇族子孙，毕生追求皇位，对王语嫣视如草介，段誉是正牌皇帝继承人，却爱美人宁弃江山。你所追的，正是我所弃的，尽道人生的可笑荒谬。</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>因为众生皆苦，便觉得自己也不是很苦。</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>金圣叹评《水浒》论武松为天人，萧峰何尝不是天人。看他有阔处，有毒处，有正处，有良处，有快处，有真处，有捷处，有雅处，有大处，有警处，实是金大侠小说中之第一人。</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>偌大一本书，数百豪杰人物，萧峰一出，全归背景</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>理性的培养、逻辑的思维、高雅的阅读等不能让别人爱你，但却能让你坦然接受不被爱。</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>我一度以为二十多岁是一个人最难熬的一段时间，在这段时间里要实现从少年到青年的转换。看了这四本书之后发现人一辈子都在挣扎，只是每个时期面临的困难不同罢了，我们一直都经历着角色的转换。</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>会让你在读完最后一行后想要重新翻开《我的天才女友》的第一页。</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>也许莉拉吸引尼诺的地方，就是尼诺在她身上，开始看到了以为自己也有的东西，但对比之下他发现自己并没有。她拥有才智，但她没有利用它为自己谋福利，而像贵妇一样在挥霍着自己的才智，就好像对她来说，整个世界的财富都是庸俗的。莉拉的才智是免费的，这就是她让尼诺入迷的原因。“她和其他女人不一样，因为她天生就那么桀骜不驯，不会为任何事儿弯腰。”我们所有人都做出让步了，经过考验、失败和成功，这种让步重新塑造了我们。只有莉拉，没有任何人、任何事可以改变她。不仅如此，随着年龄的增长，她和任何人一样变得顽固和难相处，但她的那些品质一直都原封未动，甚至更加坚固。我们恨她的同时，也害怕她，会对她充满敬意。</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>读完那不勒斯四部曲的雨夜，人生几十年，像是一场玩笑，像是一次为了记录而存在的表演。</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>洪荒巨兽，太巨大了。老陀的体量感真不是盖的，契诃夫、布尔加科夫、《百年孤独》、《悉达多》，简直都好像只是从他身上抽下来一根骨头。一边读一边也遗憾：涅朵奇卡没有写完，卡拉马佐夫没有写完，契诃夫死得那么早...</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>这是一个缺失信仰的年代。这是一个焦虑爆棚的年代。当大家都在忙着读心灵鸡汤，来寻找到人生真谛的时候，推荐你读一读这本《卡拉马佐夫兄弟》，一本被无数大师封神的小说。 这本小说，在文学史上的地位已经毋庸置疑，它极其真实的写出了人性中种种的崇高与丑恶，它像一面镜子，在其中你会看到一个你都不想承认的自己。这本书，是完美的将哲学、神学、心理学融为一体的杰作。 就连最狂傲的，自命为天才的尼采，读完此书也不得不承认：“陀思妥耶夫斯基是我生命中最美好的际遇，他是一个思想深刻的人，他有充分的权利，蔑视我们这些浅薄的德国人。”</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>那时候我太轻狂，只觉得他太多话，没察觉那是另一种沉默，或者说那是沉默的尽头。</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>《宗教大法官》一章另添一星，翻译再添一星，这书至少该打七星！</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>不知是陀氏自身还是荣如德功劳，语言意蕴丰满，两本大部头看起来很愉快。上海译文这版版式不错，插画精美，如果有精装版就更好了。当时的俄罗斯刚刚破除农奴制，新思潮涌入，宗教却依然占据主导。陀氏虽然拥有一定的倾向性，但理性的光芒已锐不可当。感觉“宗教大法官”和“魔鬼。伊万·费奥多罗维奇的梦魇”两节最为精彩，其中“宗”一节直接逼问上帝，毫不留情揭露宗教，大快人心。相比之下，想到《我的个神啊》这种幼稚的意淫如此为人追捧，只得耻笑。</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>我很真诚的讲：作者用极其扎实的故事告诉了女人们，为什么不能太早结婚以及为什么要坚持上学读书……（一本真正的女性主义小说</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>你以为那不勒斯很远，但是那种女性才懂的绝望和迷茫是全世界通用的。</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>这套小说有一种奇怪的魔力，完全手不释卷，停不下来，会想一口气看掉，沉迷在人物波澜壮阔的情感和命运里。有一种看情节剧的错觉，而且一点也不累人，翻起来又快又兴奋。莉拉的命运啊，真的，最后在工厂里那一幕，哭死了，为她心碎，她的疯狂和大胆，她的天才和倔强。而莱农的心理描写也非常好看，直接而无任何保留，以后她会袒露自己，还是把自己写成故事呢。现在配角的人物形象都开始丰满起来，但是尼诺反倒有点让人爱不起来，在莉拉的光芒下，他显得迟疑而孱弱，反倒是恩佐和莉拉一起学习的画面又一次激动了人心。继续等第三部第四部，想知道莉拉如何继续把控她的命运。</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>好吧我也没忍住把这本看完了。我现在最大的困惑其实是：这个作者为什么什么都懂！不光是女人们，男人们的歇斯底里，在她笔下也能驾轻就熟。生活就是如此无望，彼此桎梏，每个人都想要挣脱，可都没有结果，只留下了故事。</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>读到一半要气死了，读完了反而释然了，莉拉和莱侬就像两株并生的植物，互相依赖，互相索取，互相想要摆脱对方，又都做不到。不过非常反感作者喜欢在每本书末尾扔炸弹这种做法。</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>很感人的书，尤其是最后几页。我想以后我要是有孩子了，我要让TA在10岁的时候读这本书，让TA看到人与人的温暖和理解，学会对于“少数人”的包容和同理。这世上很多的罪恶，都来源于多数人对“少数人”的暴力。</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>她死得无怨无悔，不欠任何人，也不依赖任何东西。她是我见过最勇敢的人。</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>没有读过这本书的人生跟读过之后的人生，真的很不一样。</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>偏见不仅会消灭肉体（黑人汤姆之死）也会扼杀灵魂（怪人阿瑟·拉德利一生避世）</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>“除非你穿上一个人的鞋子，像他那样走来走去，否则你永远无法真正了解一个人。”</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>第一次看，还是06年第一本的电子书。后来家里有了本盗版全集，大16开800多页，板砖一样。这两天住院期间带了那本“板砖”重温了一遍，印象最深的是胡宗宪打海盗那段，最大的体会是，人可以没有良心但不能没有理想，没有良心的人未必不能做好事，但没有理想的人，只是苟活世间尔。</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>能勾起你读其他书的书，就是好书。</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>入门佳作，但是作者为了趣味性而牺牲了严谨性。</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>一个寒假看完，不拘一格拆解历史，虽不无主观，但的确很好看；最喜欢2、3集，万国来朝，文治武功，宫闱权斗，兄弟反目，于谦、王阳明伟立光明；中期妖孽盛行，流派林立，皇帝老儿冷眼旁观群臣斗；后期党同伐异，万象争流，妖人牛人猛人一锅粥，270多年的帝国灰飞烟灭，浪滔滔千古风流人物，尽成烟云；官场如职场，厚黑学从来没消失过！</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>一部关于厚黑学的血泪史</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>当我沉默的时候,我觉得充实;我将开口,同时感到空虚。</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>似乎鲁迅经常做噩梦...</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>我不愿彷徨于明暗之间，我不如在黑暗里沉没。</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>修行134th，彼时大先生白话文已臻绝顶。这本书是我爹私人藏书中唯一一本鲁迅，我六七岁的时候读过一次，不过必然是有读没有懂，今天读时受到了极大的震撼和感动，昨晚读到手心出汗心绪波动，另外这绝对不是肾虚的表现，我的损友们。最喜欢的是大先生借以自况的复仇者I，于是只剩下广漠的旷野，而他们俩在其间裸着全身，捏着利刃，干枯地立着；以死人似的眼光，赏鉴这路人们的干枯，无血的大戮，而永远沉浸于生命的飞扬的极致的大欢喜中。其次是立论，寥寥几笔白描，爽快淋漓，还有相当几篇感觉没有理解或者没有理解到位，大先生的书，也不是只读一次就可以的</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>初读，重读，长时间读，掰开揉碎了读，半明半暗地读，不管怎么读都那么有味道，仅是这点有几部散文诗集能做到？</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>我对自己的要求很低：我活在世上，无非想要明白些道理，遇见些有趣的事。倘能如我所愿，我的一生就算成功。为此也要去论是非，否则道理不给你明白，有趣的事也不让你遇到。我开始得太晚了，很可能做不成什么，但我总得申明我的态度，所以就有了这本书——为我自己，也代表沉默的大多数。 ——王小波</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>我看现在是冷漠的大多数了</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>与其别人让我闭嘴，不如我自己赶快沉默了去。你的理又不是我的，我跟你辩个五六七八没意思。</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>我们是沉默的大多数，或在内心挣扎，或在脸上写满愤怒，然而结局终究是平庸与顺从。</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>看了一半，难以为继。语言风格是揣着聪明装糊涂，可能是时代需要。关键是这聪明在我看来还不够聪明，不过想想，在那个时代，这应当也是冒险了。庆幸自己生在了现在。唯一的收获是，书中说，看杂文看评论的人，永远不能真正了解一门艺术。算是对自己一记警钟。想要广泛涉猎，高谈阔论，却又不曾自己真正深入过什么，算是一种对艺术的亵渎吧。希望自己多一点沉淀。</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/豆瓣图书Top250本地数据库.xlsx
+++ b/豆瓣图书Top250本地数据库.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4131,6 +4131,4289 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>盛衰之理，本为天命。然而人心就是如此。眼见得他起高楼，于是便不忍心见他楼塌了。见过他鼎盛的时候，再看他的衰败就无比心酸。而更加可悲的是，目睹这场哗变的你，本就是这戏中之人。</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>第一次看《红楼梦》，是小学五年级。因所有人都说，这是部名著，于是，期末考后，怀着极大的敬意与耐心，准备好好下番苦功夫。不曾想，从头到尾，一点不打绊儿地，没花多长时间，就囫囵吞枣地顺利看完，幼小心灵还因此生出些疑问：怎么一点儿不象名著呀，即不难懂，也不深刻，不就是些家长里短的故事集锦吗！ 留下印象的，不是爱情纠葛，不是阶级矛盾，不是白茫茫一片真干净，而是当时粗糙日常生活中，一些根本无法想象的精美事物：比如，一些菜品，要经过如此多复杂细致的步骤，才能一点点做出；比如，一些庭院宅子，院名的起法，树木的搭配，房子的色彩，有那么多讲究；比如，一些好听的布料名，一些古怪材质的饰品，一些用途不明的摆设；再比如，闲谈，对诗，饮茶……才知道，原来人可以这样生活，可以这样打发时间，而不被视为浪费生命，也无需心下内疚，有些无法理解，又有点儿想入非非。 这或许是文学的另一个用处，让人从踏实细节处，活生生触摸到一个时代的体温。只是后来，每当我跟人说起，《红楼梦》对我来说，就是故事会，就是菜谱与家居指南时，十个会有九个半露出惊讶表情，让我觉得自己，可真没文化！</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>亲戚是干什么用的大全</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>长这么大，到今天才把这部奇书读完。觉得并没有那么多微言大义，倒是曹雪芹的文笔实在了得，对人的那些细腻情感拿捏得十分到位。特别想说的一点是，坚决认为林黛玉不能算是什么完美的理想主义者，她非但不完美，而且是毛病最大的一个。所有的问题又都归结于三个字——看不开！</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>一个呼吁：那些清穿小说的主人公你们风花雪月以后就不能顺道送曹雪芹个打印机么？</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>读《活着》的过程我很平静，除了有庆献血而死的描述让我呼吸急促。在那个年代像福贵式的悲剧小人物多如牛毛，他们愚昧，勤劳，坚强，隐忍，他们被时代的洪流裹挟着无法喘息，唯有努力活下去才能活下去。福贵的悲哀是每一个中国人的悲哀，谁都无法幸免。第一次读余华，他看似沉重冷静的描述却字字见血。</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>读起来太顺畅，经典就是经典</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>看见了人生悲苦，看见了底层人民的乐观和坚强，看见了生命的柔韧，看见了命运和岁月那不动声色的力量。</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>第一次见序这么多的一本书。（但是三星是更复杂的原因，短评里说不清的原因，不是因为序多……）</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>在《活着》中，管去世叫“熟了”。最初是福贵的爹“熟了”，初闻不解，后文说道，人死像熟透的梨，离树而落。梨者，离也。</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>自然记得从小学到高中的暑假，坐在空调房间的地板上，一边吃西瓜一边沉浸在魔法世界的时光，记得高中时熬夜刷题的间隙，吃一碗泡面，看一会死亡圣器，枯燥的晚上也充满幻想。再见，我曾经心心念念想去的霍格沃兹。</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>至今还记得，读第一本哈利波特的时候，是站在厨房的灯下一口气读完的。</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>伴随了我整个童年成长的经典小说。现下唯一美中不足的应该就是马爱农和马爱新在圣器那一本翻译的时候不停的引用了本山大叔的小品名句“你太有才了”！</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>想说的都在这儿了。 作者：凉白（来自豆瓣） 来源：https://www.douban.com/doubanapp/dispatch/review/8504335 《哈利.波特-(珍藏版)(全七册)》的豆瓣书评:【“死亡不过是另一场伟大的冒险”】</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>长大了才知道哈利波特不仅仅只是儿童读物</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>这是我看过最吓人的一本书。不是可怕而是深深的恐惧。</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>“让人说话天不会塌下来，有话就说，有屁就放，是香是臭，让群众讨论嘛”。 我不信豆瓣审核连教员的话也删。</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>如果尖锐的批评完全消失，温和的批评将会变得刺耳。如果温和的批评也不被允许，沉默将被认为居心叵测。如果沉默也不再允许，赞扬不够卖力将是一种罪行。如果只允许一种声音存在，那么，唯一存在的那个声音就是谎言。－－－摘自油管</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>有种深刻入骨的悲凉。</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>太阳底下无新事，温斯顿在看得见看不见巨大机器前变成了“消失的老鼠”。没有完美的制度，当你感觉到它是完美的时候，它便开始吞噬你了。电幕面前，2+2必须等于5。</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>大刘，你打开了一扇门，门外的世界一片黑暗，这黑暗中蕴藏的故事，永远讲不完。</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>这么个硬核的科幻是怎么装下了程心这朵白莲花婆娘的…</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>书是好书，纸是烂纸，热爱刘慈欣的读者，请不要买这套</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>他们说，读完这套书以后，再抬头看星空感觉就不一样了。嗯，是这样的。</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>一定要和圣母做闺蜜，这样才能有光速飞船坐~</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>有一天我梦醒了，窗外是氤氲不化的雾气，我走到窗边，原来是夜里下了雪，空气一片苍茫，我又想起思嘉，在那场大雾中迷路，恐慌，奔跑，喘息，寻找，家。而瑞德已决意放弃一切。包括她。但我也不是十五岁的我了。那时我见她玫瑰红睡袍，一杯白兰地，手法娴熟，一饮而尽。我怎么学得会像她喝酒这般痛饮人生。可我知道什么是痛。</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>我认为本书唯一值得称赞的人是梅兰妮，一个真正的勇士、一个坚毅的妻子、一个称职的妈妈、一个挚友。</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>其实每个女子在少女时期内心都有一个艾希礼，走到最后才会明白原来自己爱的是班瑞德</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>差不多半年的时间间隙里重看了一遍。快结束时，巴特勒问斯嘉丽多大了，她答28。我突然被狠狠震惊到，两次看书，几次看电影，都觉得看了他们蓬蓬勃勃跌跌荡荡沧海桑田的一辈子，可她才28！</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>我能说“tomorrow is another day.” 这句话对我人生影响很大吗？</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>25岁生日这天把房思琪交付印厂，简体版2018年1月25号上市。做这本书的过程经历了很多，简体版的授权很不容易，感谢游击文化对我们的信任和配合。简体版也得到了他们的认可，除了几处极个别的涉台词语外极少删减，性描写也基本保留，奕含写的克制而干净，实无删改之必要。感谢出版社老师对这本书的爱护，尊重了作者文字。感谢李银河戴锦华张悦然詹宏志蒋方舟等老师的郑重推荐。感谢很多人，为了房思琪和更多读者的相遇。这本书值得也应该被更多人看到，是我的初衷，也是我的目标。 ps2020.07房思琪精装版出版，把在出版两年多里收到的建议做了用心调整。</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>她懂得很多，说话也很深刻，但却有一种单纯感。我不知道她是怎么做到的，她是深刻和单纯的糅合体。她访谈时说：在读这本书的时候，你能感受到痛，那是真实的；你能感受到美，那也是真实的。我都感受到了，甚至能够感受到她被折磨而无法解脱的心情，这是林奕含留给我们的遗言。</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>北影阿廖沙、侯亮平【被】销声匿迹；恋童癖许豪杰恢复微信公号实名，并反咬一口将不肯透露举报人信息的豆瓣告上法庭；北航博士罗茜茜时隔十二年实名举报教授陈小武曾对她及多名女生性骚扰——这些，是你朝反性暴力的实时进程，我们的#me too#远未成声势。这本书的出版告诉我们：不，你并没有选择，你不再可以假装世界上没有人以强暴小女孩为乐；假装从未有小女孩遭受强暴；假装房思琪从不存在。因为这本书属于“文学”，但不单单属于文学，它是一个承受残暴性伤害的女生，为自己提前写就的悼文；因为强暴，是人类社会有史以来最大的屠杀。读着林奕含的文字，一再想要哀叹“可惜”。但可惜这个词太傲慢、太冷酷了，终归是活人对她文学天才的掂量，对可能存在的所谓文学成就or损失的收支核算。而她经受的苦痛黑洞，这些，根本不足以抵偿。</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>简体版终于体面问世了：「一切文学，余爱以血书者。」</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>整个阅读过程太需要心理承受力了，林奕含真的很会写，也是真的很懂得人间的丑陋，只是这份懂得代价太大了，全是血与泪，和无数个不眠之夜的自我拷问、自我厌弃、自我洗脑，在真实与自我安慰之间做艰难的选择。书前书后那些评论是没有心肝吗？面对这种文字还他妈在讲创作技巧、比喻太多、用笔太工？每看到一句这样的话，都觉得千千万万个房思琪的苦白受了，都觉得人间不值得。希望每个无意间和自己厌弃的人产生了关联、无意间发生共谋、陷入到难以挣脱的亲密关系的人，都能迈过自厌和自恨，不用否定自己的感情，诚实本身就是一种力量，面对、接受、挣脱、成长。</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>再也分不清猪的脸和人的脸</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>「凡動物一律平等，但是有些動物比別的動物更加平等。」</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>短短112页，却细致地展现了极权如何产生发展控制农场的一切。觉得恐惧的地方在于记忆如何被轻易的篡改，有什么是可以确信的？</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>比天气预报准多了</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>长篇大论还真不如故事一则</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>这书我看得特慢，只要出现一个地名我就想在谷歌地形图上给找出来，然后细细从战略层面揣摩用兵之道。特别是街亭之战，光在地图上找到街亭这个屯兵的小谷道就花了不少功夫，刚开始始终想不明白这个离汉中十万八千里的地方到底哪儿重要，后来研究了下才知道古时天水通长安的道路并非沿渭水河谷顺流而下，而是走官陇古道，街亭正处于古道的咽喉之处，蜀丢街亭就意味着把背后留给了魏国，腹背受敌，命都难保。总之这本书值得对着地形图细细揣摩，尤其是诸葛亮六出祁山那段。</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>这曾经是我在小学时反复阅读的一部经典。我极爱她，甚至愿意写下每一个人的名字，并且愿意为了这部小说而去读裴注三国志。一部《三国演义》，可以说是我的文学启蒙，并且让我读繁体毫无问题..别人喜爱诸葛亮，我独独对吕布、陈宫和貂蝉感到惋惜，并且唾弃张文远，这个只顾保命的伪君子..我当时相信是因为诸侯先死，所以才被极尽抹灭的：当时谁还相信这是小说呢？</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>“书生轻议冢中人，冢中笑尔书生气！”</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>我是三国控，不解释。最喜欢的一部古典文学。</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>四大名著中最先看的一本书。不过当时在看时，倒不是跟着传统盲目崇拜起刘备关羽来，而是对被作者百般贬低的人物产生研究兴趣，如周瑜并不心胸狭窄，鲁肃并不平庸，草船“接”箭的是孙权，被关兴杀死的潘璋和孔明同年去世，袁绍深得民心，吕蒙“士别三日”，另外张飞有文采……</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>译得很好。重看一遍越发觉得BBC的《神探夏洛克》改编的真是好啊真是巧啊</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>个人感觉，福尔摩斯只是作为侦探小说的鼻祖之一的地位，但感觉远没有阿婆（阿加莎克里斯蒂）的书来的让人出乎意料，令人回味无穷。</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>这个应该是我人生中第一套书。。。。刚会认字，还不知道“犹他州”（印象深刻）为何物的时候，就在看男主角们搞基了，情何以堪。。。</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>已经读了不知多少遍但真的读一辈子都读不厌</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>为什么妈妈要把它借人？现在好了，只剩一本了！给人家弄丢了。</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>新版封面，严重剧透。</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>把小说写成这样绝对是开挂了吧，除了连番登场的几十号人物，随处雕琢的大时代的背景也让人叹为观止。对人性的挖掘比起吉田修一还是弱一些，就是纯好看，从第一句开始吸住你逐渐往往里掉。</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>情有可原，罪无可恕。</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>故事中男女主人公从头到尾没有一句对白，经典。</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>张无忌的妈妈也说过 不要轻易相信漂亮女人 她们的演技和城府都是你无法想象的 无删减版本比之前的版本多了关于性的描写 阴茎和乳房等词汇也直接被接纳进来 前十章用来构建人物关系和埋下案件伏笔 从第十章开始抽丝剥茧地隐现真相 枪虾和虾虎鱼（雪穗和桐原）的关系日渐明朗 遗憾的是关于后半段作者的笔锋开始出现倦怠 没有给出很完整明确的指示或者暗示 对于最后整体的真相的揭露也并没有很吃惊 除了娈童之外 其他的因果其实已了然于心</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>挽狂澜于既倒，扶大厦之将倾。</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>在书店翻完就成，买回家则如同鸡肋。傅高义写这部书的初衷就是向西方人介绍邓小平和他经历过的大时代，可叹的是，今天我们却要把这样一部写给别人的入门书当作我们了解自我的红宝书。</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>总有人希望这本书能有别出心裁的史料和观点，其实这本书最大的贡献在于理清了从1977年到1992年所有历史事件的脉络</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>按照邓小平的遗愿，他的眼角膜被捐出供眼科研究，内脏被捐出供医学研究，遗体被火化，骨灰盒上覆盖着中国共产党党旗。1997年3月2日，他的骨灰被撒入大海。</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>十几岁的时候渴慕着小王子，一天之间可以看四十四次日落。是在多久之后才明白，看四十四次日落的小王子，他有多么难过。</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>读了好多年，终于读完了，但是实在共鸣不起来，虽然知道那些道理，但真的觉得没什么了不起啊，是我还太幼稚吗？</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>我的玫瑰花儿，只有四个微不足道的刺，用来抵御这个世界。</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>说实话 我看不太懂 但还是跟风给个5星吧 以显示我也是有思想有学识之人</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>虽然我实在幼稚，但我并不怎么喜欢孩童般的纯净，我只爱风浪过后的平静，流水打磨出的清亮，大雪纷飞时的安宁，沧桑看透的纯真，我爱眼冷心热的庄子，人究竟无所逃于天地之间，各适其性，做自己认为有意义的事就好了，无论是统治宇宙还是喝酒点灯，对他们来说，都比爱一朵玫瑰重要，这不是很好的么</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>鲁迅如果不被赋予那么多政治色彩，单看作品也是一个优秀的毒舌家的</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>看他的文章还无法醒悟的人是该有多么可悲</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>一个特立独行的人需要金钱来保持他的尊严，否则就只有被毁灭的份，人们是不能容忍一个穷光蛋的异类的。就象一个老姑娘要用钱保持她的高傲，否则就是耻辱。</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>这部小说，大体上是描写了辛亥革命前后乡村发生的一系列的故事，其中以鞭子、革命、秀才、假洋鬼子，扮演出一幅中国传统社会的浮世绘。在这里，我们不妨感慨，鲁迅笔下人物的生命力。鲁迅是描写了辛亥革命前后，我们已经革命胜利六十多年，但是假洋鬼子、赵老太爷难道就绝迹了吗？咸与维新，却一切照旧。</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>狂人在望着赵家的狗，孔乙己在讲茴字的四种写法，华老栓在拿夏瑜的血馒头，九斤老太在感叹一代不如一代，闰土在隔着厚障壁叫我老爷，圆规杨二嫂在捡东西，阿Q在逗尼姑，耍无赖，闹革命，要困觉，精神胜利法，迅哥在怀念那夜似的豆，那夜似的戏。我们在铁屋子里装睡，想着年轻时做过的许多的梦。</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>比格林好，而且寒假过后的几个月，经常在里面翻出压岁钱</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>《海的女儿》是爱情的启蒙。</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>如果不是叶君健译的就不要看，书者与译者相得益彰，擦出的精致纯美，无人可及</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>写给成人的悲伤童话</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>小时候看是童话 现在再看的话才发现都是悲剧</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>三毛的文字其实没有特别出挑的地方，但是合成一篇，整个却显得真实、清爽。她很好地遵循了白话文“有什么说什么，该怎么说就怎么说”的宗旨，而且她聪明在不在散文中论理，不作生硬的哲思，单纯就事论事，从而反倒能让人身临其境~~印象最深的是她和荷西去偷看别人洗澡灌肠，再如三毛考驾照的那几个考题，好笑极了~~而读到他们遇到三个疯子袭击则心提至喉~~看散文，以前喜欢过余秋雨的辞藻，现在越来越喜欢三毛这类的平淡，平淡是真，写文常常有自炫的诱惑，能抵住诱惑是不容易的。。。【题外】三毛与荷西是般配的一对，如果荷西没有去世地那么早，三毛可能也不会弃世了吧。。。“人”果然是两个人互相支撑在一起才能不倒下的。。。</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>自你之后，再无真正流浪自由的灵魂。</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>再看到 荒山之夜 仍然还是以前的震惊！他们那么随便就经历了一场出生入死，而且完全不在意，人生多么的洒脱啊</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>读过三毛全集，最好的还是这一册。</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>你伤害了我的骄傲！</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>经典武学起于春秋，到北宋达到极盛，南宋有所衰落，元末因明教兴盛中兴。明代更有了东方不败等大师。但期间伽利略的出现已预示其衰落。康熙年间出现牛顿，梯云纵灭绝。道光年间出现卡诺，玄冰掌灭绝。尤其是力学定理建立后，内力和轻功全部消失，梯云纵这种只需吐纳练便可自带反重力系统的轻功彻底消失</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>慕容复是没落皇族子孙，毕生追求皇位，对王语嫣视如草介，段誉是正牌皇帝继承人，却爱美人宁弃江山。你所追的，正是我所弃的，尽道人生的可笑荒谬。</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>因为众生皆苦，便觉得自己也不是很苦。</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>金圣叹评《水浒》论武松为天人，萧峰何尝不是天人。看他有阔处，有毒处，有正处，有良处，有快处，有真处，有捷处，有雅处，有大处，有警处，实是金大侠小说中之第一人。</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>偌大一本书，数百豪杰人物，萧峰一出，全归背景</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>理性的培养、逻辑的思维、高雅的阅读等不能让别人爱你，但却能让你坦然接受不被爱。</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>我一度以为二十多岁是一个人最难熬的一段时间，在这段时间里要实现从少年到青年的转换。看了这四本书之后发现人一辈子都在挣扎，只是每个时期面临的困难不同罢了，我们一直都经历着角色的转换。</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>会让你在读完最后一行后想要重新翻开《我的天才女友》的第一页。</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>也许莉拉吸引尼诺的地方，就是尼诺在她身上，开始看到了以为自己也有的东西，但对比之下他发现自己并没有。她拥有才智，但她没有利用它为自己谋福利，而像贵妇一样在挥霍着自己的才智，就好像对她来说，整个世界的财富都是庸俗的。莉拉的才智是免费的，这就是她让尼诺入迷的原因。“她和其他女人不一样，因为她天生就那么桀骜不驯，不会为任何事儿弯腰。”我们所有人都做出让步了，经过考验、失败和成功，这种让步重新塑造了我们。只有莉拉，没有任何人、任何事可以改变她。不仅如此，随着年龄的增长，她和任何人一样变得顽固和难相处，但她的那些品质一直都原封未动，甚至更加坚固。我们恨她的同时，也害怕她，会对她充满敬意。</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>读完那不勒斯四部曲的雨夜，人生几十年，像是一场玩笑，像是一次为了记录而存在的表演。</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>洪荒巨兽，太巨大了。老陀的体量感真不是盖的，契诃夫、布尔加科夫、《百年孤独》、《悉达多》，简直都好像只是从他身上抽下来一根骨头。一边读一边也遗憾：涅朵奇卡没有写完，卡拉马佐夫没有写完，契诃夫死得那么早...</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>这是一个缺失信仰的年代。这是一个焦虑爆棚的年代。当大家都在忙着读心灵鸡汤，来寻找到人生真谛的时候，推荐你读一读这本《卡拉马佐夫兄弟》，一本被无数大师封神的小说。 这本小说，在文学史上的地位已经毋庸置疑，它极其真实的写出了人性中种种的崇高与丑恶，它像一面镜子，在其中你会看到一个你都不想承认的自己。这本书，是完美的将哲学、神学、心理学融为一体的杰作。 就连最狂傲的，自命为天才的尼采，读完此书也不得不承认：“陀思妥耶夫斯基是我生命中最美好的际遇，他是一个思想深刻的人，他有充分的权利，蔑视我们这些浅薄的德国人。”</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>那时候我太轻狂，只觉得他太多话，没察觉那是另一种沉默，或者说那是沉默的尽头。</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>《宗教大法官》一章另添一星，翻译再添一星，这书至少该打七星！</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>不知是陀氏自身还是荣如德功劳，语言意蕴丰满，两本大部头看起来很愉快。上海译文这版版式不错，插画精美，如果有精装版就更好了。当时的俄罗斯刚刚破除农奴制，新思潮涌入，宗教却依然占据主导。陀氏虽然拥有一定的倾向性，但理性的光芒已锐不可当。感觉“宗教大法官”和“魔鬼。伊万·费奥多罗维奇的梦魇”两节最为精彩，其中“宗”一节直接逼问上帝，毫不留情揭露宗教，大快人心。相比之下，想到《我的个神啊》这种幼稚的意淫如此为人追捧，只得耻笑。</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>我很真诚的讲：作者用极其扎实的故事告诉了女人们，为什么不能太早结婚以及为什么要坚持上学读书……（一本真正的女性主义小说</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>你以为那不勒斯很远，但是那种女性才懂的绝望和迷茫是全世界通用的。</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>这套小说有一种奇怪的魔力，完全手不释卷，停不下来，会想一口气看掉，沉迷在人物波澜壮阔的情感和命运里。有一种看情节剧的错觉，而且一点也不累人，翻起来又快又兴奋。莉拉的命运啊，真的，最后在工厂里那一幕，哭死了，为她心碎，她的疯狂和大胆，她的天才和倔强。而莱农的心理描写也非常好看，直接而无任何保留，以后她会袒露自己，还是把自己写成故事呢。现在配角的人物形象都开始丰满起来，但是尼诺反倒有点让人爱不起来，在莉拉的光芒下，他显得迟疑而孱弱，反倒是恩佐和莉拉一起学习的画面又一次激动了人心。继续等第三部第四部，想知道莉拉如何继续把控她的命运。</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>好吧我也没忍住把这本看完了。我现在最大的困惑其实是：这个作者为什么什么都懂！不光是女人们，男人们的歇斯底里，在她笔下也能驾轻就熟。生活就是如此无望，彼此桎梏，每个人都想要挣脱，可都没有结果，只留下了故事。</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>读到一半要气死了，读完了反而释然了，莉拉和莱侬就像两株并生的植物，互相依赖，互相索取，互相想要摆脱对方，又都做不到。不过非常反感作者喜欢在每本书末尾扔炸弹这种做法。</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>很感人的书，尤其是最后几页。我想以后我要是有孩子了，我要让TA在10岁的时候读这本书，让TA看到人与人的温暖和理解，学会对于“少数人”的包容和同理。这世上很多的罪恶，都来源于多数人对“少数人”的暴力。</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>她死得无怨无悔，不欠任何人，也不依赖任何东西。她是我见过最勇敢的人。</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>没有读过这本书的人生跟读过之后的人生，真的很不一样。</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>偏见不仅会消灭肉体（黑人汤姆之死）也会扼杀灵魂（怪人阿瑟·拉德利一生避世）</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>“除非你穿上一个人的鞋子，像他那样走来走去，否则你永远无法真正了解一个人。”</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>第一次看，还是06年第一本的电子书。后来家里有了本盗版全集，大16开800多页，板砖一样。这两天住院期间带了那本“板砖”重温了一遍，印象最深的是胡宗宪打海盗那段，最大的体会是，人可以没有良心但不能没有理想，没有良心的人未必不能做好事，但没有理想的人，只是苟活世间尔。</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>能勾起你读其他书的书，就是好书。</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>入门佳作，但是作者为了趣味性而牺牲了严谨性。</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>一个寒假看完，不拘一格拆解历史，虽不无主观，但的确很好看；最喜欢2、3集，万国来朝，文治武功，宫闱权斗，兄弟反目，于谦、王阳明伟立光明；中期妖孽盛行，流派林立，皇帝老儿冷眼旁观群臣斗；后期党同伐异，万象争流，妖人牛人猛人一锅粥，270多年的帝国灰飞烟灭，浪滔滔千古风流人物，尽成烟云；官场如职场，厚黑学从来没消失过！</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>一部关于厚黑学的血泪史</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>当我沉默的时候,我觉得充实;我将开口,同时感到空虚。</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>似乎鲁迅经常做噩梦...</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>我不愿彷徨于明暗之间，我不如在黑暗里沉没。</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>修行134th，彼时大先生白话文已臻绝顶。这本书是我爹私人藏书中唯一一本鲁迅，我六七岁的时候读过一次，不过必然是有读没有懂，今天读时受到了极大的震撼和感动，昨晚读到手心出汗心绪波动，另外这绝对不是肾虚的表现，我的损友们。最喜欢的是大先生借以自况的复仇者I，于是只剩下广漠的旷野，而他们俩在其间裸着全身，捏着利刃，干枯地立着；以死人似的眼光，赏鉴这路人们的干枯，无血的大戮，而永远沉浸于生命的飞扬的极致的大欢喜中。其次是立论，寥寥几笔白描，爽快淋漓，还有相当几篇感觉没有理解或者没有理解到位，大先生的书，也不是只读一次就可以的</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>初读，重读，长时间读，掰开揉碎了读，半明半暗地读，不管怎么读都那么有味道，仅是这点有几部散文诗集能做到？</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>我对自己的要求很低：我活在世上，无非想要明白些道理，遇见些有趣的事。倘能如我所愿，我的一生就算成功。为此也要去论是非，否则道理不给你明白，有趣的事也不让你遇到。我开始得太晚了，很可能做不成什么，但我总得申明我的态度，所以就有了这本书——为我自己，也代表沉默的大多数。 ——王小波</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>我看现在是冷漠的大多数了</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>与其别人让我闭嘴，不如我自己赶快沉默了去。你的理又不是我的，我跟你辩个五六七八没意思。</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>我们是沉默的大多数，或在内心挣扎，或在脸上写满愤怒，然而结局终究是平庸与顺从。</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>看了一半，难以为继。语言风格是揣着聪明装糊涂，可能是时代需要。关键是这聪明在我看来还不够聪明，不过想想，在那个时代，这应当也是冒险了。庆幸自己生在了现在。唯一的收获是，书中说，看杂文看评论的人，永远不能真正了解一门艺术。算是对自己一记警钟。想要广泛涉猎，高谈阔论，却又不曾自己真正深入过什么，算是一种对艺术的亵渎吧。希望自己多一点沉淀。</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/豆瓣图书Top250本地数据库.xlsx
+++ b/豆瓣图书Top250本地数据库.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F227"/>
+  <dimension ref="A1:F348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8414,6 +8414,4257 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>盛衰之理，本为天命。然而人心就是如此。眼见得他起高楼，于是便不忍心见他楼塌了。见过他鼎盛的时候，再看他的衰败就无比心酸。而更加可悲的是，目睹这场哗变的你，本就是这戏中之人。</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>第一次看《红楼梦》，是小学五年级。因所有人都说，这是部名著，于是，期末考后，怀着极大的敬意与耐心，准备好好下番苦功夫。不曾想，从头到尾，一点不打绊儿地，没花多长时间，就囫囵吞枣地顺利看完，幼小心灵还因此生出些疑问：怎么一点儿不象名著呀，即不难懂，也不深刻，不就是些家长里短的故事集锦吗！ 留下印象的，不是爱情纠葛，不是阶级矛盾，不是白茫茫一片真干净，而是当时粗糙日常生活中，一些根本无法想象的精美事物：比如，一些菜品，要经过如此多复杂细致的步骤，才能一点点做出；比如，一些庭院宅子，院名的起法，树木的搭配，房子的色彩，有那么多讲究；比如，一些好听的布料名，一些古怪材质的饰品，一些用途不明的摆设；再比如，闲谈，对诗，饮茶……才知道，原来人可以这样生活，可以这样打发时间，而不被视为浪费生命，也无需心下内疚，有些无法理解，又有点儿想入非非。 这或许是文学的另一个用处，让人从踏实细节处，活生生触摸到一个时代的体温。只是后来，每当我跟人说起，《红楼梦》对我来说，就是故事会，就是菜谱与家居指南时，十个会有九个半露出惊讶表情，让我觉得自己，可真没文化！</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>亲戚是干什么用的大全</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>长这么大，到今天才把这部奇书读完。觉得并没有那么多微言大义，倒是曹雪芹的文笔实在了得，对人的那些细腻情感拿捏得十分到位。特别想说的一点是，坚决认为林黛玉不能算是什么完美的理想主义者，她非但不完美，而且是毛病最大的一个。所有的问题又都归结于三个字——看不开！</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>一个呼吁：那些清穿小说的主人公你们风花雪月以后就不能顺道送曹雪芹个打印机么？</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>读《活着》的过程我很平静，除了有庆献血而死的描述让我呼吸急促。在那个年代像福贵式的悲剧小人物多如牛毛，他们愚昧，勤劳，坚强，隐忍，他们被时代的洪流裹挟着无法喘息，唯有努力活下去才能活下去。福贵的悲哀是每一个中国人的悲哀，谁都无法幸免。第一次读余华，他看似沉重冷静的描述却字字见血。</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>读起来太顺畅，经典就是经典</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>看见了人生悲苦，看见了底层人民的乐观和坚强，看见了生命的柔韧，看见了命运和岁月那不动声色的力量。</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>第一次见序这么多的一本书。（但是三星是更复杂的原因，短评里说不清的原因，不是因为序多……）</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>在《活着》中，管去世叫“熟了”。最初是福贵的爹“熟了”，初闻不解，后文说道，人死像熟透的梨，离树而落。梨者，离也。</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>自然记得从小学到高中的暑假，坐在空调房间的地板上，一边吃西瓜一边沉浸在魔法世界的时光，记得高中时熬夜刷题的间隙，吃一碗泡面，看一会死亡圣器，枯燥的晚上也充满幻想。再见，我曾经心心念念想去的霍格沃兹。</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>至今还记得，读第一本哈利波特的时候，是站在厨房的灯下一口气读完的。</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>伴随了我整个童年成长的经典小说。现下唯一美中不足的应该就是马爱农和马爱新在圣器那一本翻译的时候不停的引用了本山大叔的小品名句“你太有才了”！</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>想说的都在这儿了。 作者：凉白（来自豆瓣） 来源：https://www.douban.com/doubanapp/dispatch/review/8504335 《哈利.波特-(珍藏版)(全七册)》的豆瓣书评:【“死亡不过是另一场伟大的冒险”】</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>长大了才知道哈利波特不仅仅只是儿童读物</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>这是我看过最吓人的一本书。不是可怕而是深深的恐惧。</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>“让人说话天不会塌下来，有话就说，有屁就放，是香是臭，让群众讨论嘛”。 我不信豆瓣审核连教员的话也删。</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>如果尖锐的批评完全消失，温和的批评将会变得刺耳。如果温和的批评也不被允许，沉默将被认为居心叵测。如果沉默也不再允许，赞扬不够卖力将是一种罪行。如果只允许一种声音存在，那么，唯一存在的那个声音就是谎言。－－－摘自油管</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>有种深刻入骨的悲凉。</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>太阳底下无新事，温斯顿在看得见看不见巨大机器前变成了“消失的老鼠”。没有完美的制度，当你感觉到它是完美的时候，它便开始吞噬你了。电幕面前，2+2必须等于5。</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>大刘，你打开了一扇门，门外的世界一片黑暗，这黑暗中蕴藏的故事，永远讲不完。</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>这么个硬核的科幻是怎么装下了程心这朵白莲花婆娘的…</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>书是好书，纸是烂纸，热爱刘慈欣的读者，请不要买这套</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>他们说，读完这套书以后，再抬头看星空感觉就不一样了。嗯，是这样的。</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>一定要和圣母做闺蜜，这样才能有光速飞船坐~</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>每个人都是孤独地出生，在这世间恍惚几十年并不漫长的日子转眼就远去了，然后再孤独地死去。 生命注定是个悲剧，因为我们从没有融入世界，世界永远是身外之物。如果有幸，能在茫茫人海寻得一个身体与灵魂都与自己万分契合的人，与之存在一种可以称之为爱情的联系，然后一起承受生命中不可逃离不可消除的深沉的宿命的孤独。可是这般的幸运艰深难得。有的已失去了爱的能力，有的爱得深沉却无处安放，有的死在这爱里……在所有的爱里，孤独有增无减。 生命只是一场幻梦。</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>看第3遍开始越来越让我惊艳的已不是马尔克斯而是译者了。太牛逼了！这样的文字就算是母语创作也属上乘。尤其倒数第二代布恩迪亚在飓风中破译羊皮卷的全书结尾，笔触磅礴，美到让人惊怖。</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>为什么我觉得不好看呢？是不是我没文化看不懂啊！</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>开始很吃力，越读越上瘾。 惊人得叙事与潮水版的叙事，野兽般撕开真理得外衣。 原来那句经典的开场白，源自这本书。从四姑娘的第一本书，也就开始了他的抄袭生涯。</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>一口气读完但却没有能力评价。</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>有一天我梦醒了，窗外是氤氲不化的雾气，我走到窗边，原来是夜里下了雪，空气一片苍茫，我又想起思嘉，在那场大雾中迷路，恐慌，奔跑，喘息，寻找，家。而瑞德已决意放弃一切。包括她。但我也不是十五岁的我了。那时我见她玫瑰红睡袍，一杯白兰地，手法娴熟，一饮而尽。我怎么学得会像她喝酒这般痛饮人生。可我知道什么是痛。</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>我认为本书唯一值得称赞的人是梅兰妮，一个真正的勇士、一个坚毅的妻子、一个称职的妈妈、一个挚友。</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>其实每个女子在少女时期内心都有一个艾希礼，走到最后才会明白原来自己爱的是班瑞德</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>差不多半年的时间间隙里重看了一遍。快结束时，巴特勒问斯嘉丽多大了，她答28。我突然被狠狠震惊到，两次看书，几次看电影，都觉得看了他们蓬蓬勃勃跌跌荡荡沧海桑田的一辈子，可她才28！</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>我能说“tomorrow is another day.” 这句话对我人生影响很大吗？</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>再也分不清猪的脸和人的脸</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>「凡動物一律平等，但是有些動物比別的動物更加平等。」</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>短短112页，却细致地展现了极权如何产生发展控制农场的一切。觉得恐惧的地方在于记忆如何被轻易的篡改，有什么是可以确信的？</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>比天气预报准多了</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>长篇大论还真不如故事一则</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>这书我看得特慢，只要出现一个地名我就想在谷歌地形图上给找出来，然后细细从战略层面揣摩用兵之道。特别是街亭之战，光在地图上找到街亭这个屯兵的小谷道就花了不少功夫，刚开始始终想不明白这个离汉中十万八千里的地方到底哪儿重要，后来研究了下才知道古时天水通长安的道路并非沿渭水河谷顺流而下，而是走官陇古道，街亭正处于古道的咽喉之处，蜀丢街亭就意味着把背后留给了魏国，腹背受敌，命都难保。总之这本书值得对着地形图细细揣摩，尤其是诸葛亮六出祁山那段。</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>这曾经是我在小学时反复阅读的一部经典。我极爱她，甚至愿意写下每一个人的名字，并且愿意为了这部小说而去读裴注三国志。一部《三国演义》，可以说是我的文学启蒙，并且让我读繁体毫无问题..别人喜爱诸葛亮，我独独对吕布、陈宫和貂蝉感到惋惜，并且唾弃张文远，这个只顾保命的伪君子..我当时相信是因为诸侯先死，所以才被极尽抹灭的：当时谁还相信这是小说呢？</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>“书生轻议冢中人，冢中笑尔书生气！”</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>我是三国控，不解释。最喜欢的一部古典文学。</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>四大名著中最先看的一本书。不过当时在看时，倒不是跟着传统盲目崇拜起刘备关羽来，而是对被作者百般贬低的人物产生研究兴趣，如周瑜并不心胸狭窄，鲁肃并不平庸，草船“接”箭的是孙权，被关兴杀死的潘璋和孔明同年去世，袁绍深得民心，吕蒙“士别三日”，另外张飞有文采……</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>译得很好。重看一遍越发觉得BBC的《神探夏洛克》改编的真是好啊真是巧啊</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>个人感觉，福尔摩斯只是作为侦探小说的鼻祖之一的地位，但感觉远没有阿婆（阿加莎克里斯蒂）的书来的让人出乎意料，令人回味无穷。</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>这个应该是我人生中第一套书。。。。刚会认字，还不知道“犹他州”（印象深刻）为何物的时候，就在看男主角们搞基了，情何以堪。。。</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>已经读了不知多少遍但真的读一辈子都读不厌</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>为什么妈妈要把它借人？现在好了，只剩一本了！给人家弄丢了。</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>新版封面，严重剧透。</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>把小说写成这样绝对是开挂了吧，除了连番登场的几十号人物，随处雕琢的大时代的背景也让人叹为观止。对人性的挖掘比起吉田修一还是弱一些，就是纯好看，从第一句开始吸住你逐渐往往里掉。</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>情有可原，罪无可恕。</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>故事中男女主人公从头到尾没有一句对白，经典。</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>张无忌的妈妈也说过 不要轻易相信漂亮女人 她们的演技和城府都是你无法想象的 无删减版本比之前的版本多了关于性的描写 阴茎和乳房等词汇也直接被接纳进来 前十章用来构建人物关系和埋下案件伏笔 从第十章开始抽丝剥茧地隐现真相 枪虾和虾虎鱼（雪穗和桐原）的关系日渐明朗 遗憾的是关于后半段作者的笔锋开始出现倦怠 没有给出很完整明确的指示或者暗示 对于最后整体的真相的揭露也并没有很吃惊 除了娈童之外 其他的因果其实已了然于心</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>挽狂澜于既倒，扶大厦之将倾。</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>在书店翻完就成，买回家则如同鸡肋。傅高义写这部书的初衷就是向西方人介绍邓小平和他经历过的大时代，可叹的是，今天我们却要把这样一部写给别人的入门书当作我们了解自我的红宝书。</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>总有人希望这本书能有别出心裁的史料和观点，其实这本书最大的贡献在于理清了从1977年到1992年所有历史事件的脉络</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>按照邓小平的遗愿，他的眼角膜被捐出供眼科研究，内脏被捐出供医学研究，遗体被火化，骨灰盒上覆盖着中国共产党党旗。1997年3月2日，他的骨灰被撒入大海。</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>十几岁的时候渴慕着小王子，一天之间可以看四十四次日落。是在多久之后才明白，看四十四次日落的小王子，他有多么难过。</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>读了好多年，终于读完了，但是实在共鸣不起来，虽然知道那些道理，但真的觉得没什么了不起啊，是我还太幼稚吗？</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>我的玫瑰花儿，只有四个微不足道的刺，用来抵御这个世界。</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>说实话 我看不太懂 但还是跟风给个5星吧 以显示我也是有思想有学识之人</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>虽然我实在幼稚，但我并不怎么喜欢孩童般的纯净，我只爱风浪过后的平静，流水打磨出的清亮，大雪纷飞时的安宁，沧桑看透的纯真，我爱眼冷心热的庄子，人究竟无所逃于天地之间，各适其性，做自己认为有意义的事就好了，无论是统治宇宙还是喝酒点灯，对他们来说，都比爱一朵玫瑰重要，这不是很好的么</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>鲁迅如果不被赋予那么多政治色彩，单看作品也是一个优秀的毒舌家的</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>看他的文章还无法醒悟的人是该有多么可悲</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>一个特立独行的人需要金钱来保持他的尊严，否则就只有被毁灭的份，人们是不能容忍一个穷光蛋的异类的。就象一个老姑娘要用钱保持她的高傲，否则就是耻辱。</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>这部小说，大体上是描写了辛亥革命前后乡村发生的一系列的故事，其中以鞭子、革命、秀才、假洋鬼子，扮演出一幅中国传统社会的浮世绘。在这里，我们不妨感慨，鲁迅笔下人物的生命力。鲁迅是描写了辛亥革命前后，我们已经革命胜利六十多年，但是假洋鬼子、赵老太爷难道就绝迹了吗？咸与维新，却一切照旧。</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>狂人在望着赵家的狗，孔乙己在讲茴字的四种写法，华老栓在拿夏瑜的血馒头，九斤老太在感叹一代不如一代，闰土在隔着厚障壁叫我老爷，圆规杨二嫂在捡东西，阿Q在逗尼姑，耍无赖，闹革命，要困觉，精神胜利法，迅哥在怀念那夜似的豆，那夜似的戏。我们在铁屋子里装睡，想着年轻时做过的许多的梦。</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>比格林好，而且寒假过后的几个月，经常在里面翻出压岁钱</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>《海的女儿》是爱情的启蒙。</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>如果不是叶君健译的就不要看，书者与译者相得益彰，擦出的精致纯美，无人可及</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>写给成人的悲伤童话</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>小时候看是童话 现在再看的话才发现都是悲剧</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>三毛的文字其实没有特别出挑的地方，但是合成一篇，整个却显得真实、清爽。她很好地遵循了白话文“有什么说什么，该怎么说就怎么说”的宗旨，而且她聪明在不在散文中论理，不作生硬的哲思，单纯就事论事，从而反倒能让人身临其境~~印象最深的是她和荷西去偷看别人洗澡灌肠，再如三毛考驾照的那几个考题，好笑极了~~而读到他们遇到三个疯子袭击则心提至喉~~看散文，以前喜欢过余秋雨的辞藻，现在越来越喜欢三毛这类的平淡，平淡是真，写文常常有自炫的诱惑，能抵住诱惑是不容易的。。。【题外】三毛与荷西是般配的一对，如果荷西没有去世地那么早，三毛可能也不会弃世了吧。。。“人”果然是两个人互相支撑在一起才能不倒下的。。。</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>自你之后，再无真正流浪自由的灵魂。</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>再看到 荒山之夜 仍然还是以前的震惊！他们那么随便就经历了一场出生入死，而且完全不在意，人生多么的洒脱啊</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>读过三毛全集，最好的还是这一册。</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>你伤害了我的骄傲！</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>经典武学起于春秋，到北宋达到极盛，南宋有所衰落，元末因明教兴盛中兴。明代更有了东方不败等大师。但期间伽利略的出现已预示其衰落。康熙年间出现牛顿，梯云纵灭绝。道光年间出现卡诺，玄冰掌灭绝。尤其是力学定理建立后，内力和轻功全部消失，梯云纵这种只需吐纳练便可自带反重力系统的轻功彻底消失</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>慕容复是没落皇族子孙，毕生追求皇位，对王语嫣视如草介，段誉是正牌皇帝继承人，却爱美人宁弃江山。你所追的，正是我所弃的，尽道人生的可笑荒谬。</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>因为众生皆苦，便觉得自己也不是很苦。</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>金圣叹评《水浒》论武松为天人，萧峰何尝不是天人。看他有阔处，有毒处，有正处，有良处，有快处，有真处，有捷处，有雅处，有大处，有警处，实是金大侠小说中之第一人。</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>偌大一本书，数百豪杰人物，萧峰一出，全归背景</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>理性的培养、逻辑的思维、高雅的阅读等不能让别人爱你，但却能让你坦然接受不被爱。</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>我一度以为二十多岁是一个人最难熬的一段时间，在这段时间里要实现从少年到青年的转换。看了这四本书之后发现人一辈子都在挣扎，只是每个时期面临的困难不同罢了，我们一直都经历着角色的转换。</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>会让你在读完最后一行后想要重新翻开《我的天才女友》的第一页。</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>也许莉拉吸引尼诺的地方，就是尼诺在她身上，开始看到了以为自己也有的东西，但对比之下他发现自己并没有。她拥有才智，但她没有利用它为自己谋福利，而像贵妇一样在挥霍着自己的才智，就好像对她来说，整个世界的财富都是庸俗的。莉拉的才智是免费的，这就是她让尼诺入迷的原因。“她和其他女人不一样，因为她天生就那么桀骜不驯，不会为任何事儿弯腰。”我们所有人都做出让步了，经过考验、失败和成功，这种让步重新塑造了我们。只有莉拉，没有任何人、任何事可以改变她。不仅如此，随着年龄的增长，她和任何人一样变得顽固和难相处，但她的那些品质一直都原封未动，甚至更加坚固。我们恨她的同时，也害怕她，会对她充满敬意。</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>读完那不勒斯四部曲的雨夜，人生几十年，像是一场玩笑，像是一次为了记录而存在的表演。</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>洪荒巨兽，太巨大了。老陀的体量感真不是盖的，契诃夫、布尔加科夫、《百年孤独》、《悉达多》，简直都好像只是从他身上抽下来一根骨头。一边读一边也遗憾：涅朵奇卡没有写完，卡拉马佐夫没有写完，契诃夫死得那么早...</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>这是一个缺失信仰的年代。这是一个焦虑爆棚的年代。当大家都在忙着读心灵鸡汤，来寻找到人生真谛的时候，推荐你读一读这本《卡拉马佐夫兄弟》，一本被无数大师封神的小说。 这本小说，在文学史上的地位已经毋庸置疑，它极其真实的写出了人性中种种的崇高与丑恶，它像一面镜子，在其中你会看到一个你都不想承认的自己。这本书，是完美的将哲学、神学、心理学融为一体的杰作。 就连最狂傲的，自命为天才的尼采，读完此书也不得不承认：“陀思妥耶夫斯基是我生命中最美好的际遇，他是一个思想深刻的人，他有充分的权利，蔑视我们这些浅薄的德国人。”</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>那时候我太轻狂，只觉得他太多话，没察觉那是另一种沉默，或者说那是沉默的尽头。</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>《宗教大法官》一章另添一星，翻译再添一星，这书至少该打七星！</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>不知是陀氏自身还是荣如德功劳，语言意蕴丰满，两本大部头看起来很愉快。上海译文这版版式不错，插画精美，如果有精装版就更好了。当时的俄罗斯刚刚破除农奴制，新思潮涌入，宗教却依然占据主导。陀氏虽然拥有一定的倾向性，但理性的光芒已锐不可当。感觉“宗教大法官”和“魔鬼。伊万·费奥多罗维奇的梦魇”两节最为精彩，其中“宗”一节直接逼问上帝，毫不留情揭露宗教，大快人心。相比之下，想到《我的个神啊》这种幼稚的意淫如此为人追捧，只得耻笑。</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>我很真诚的讲：作者用极其扎实的故事告诉了女人们，为什么不能太早结婚以及为什么要坚持上学读书……（一本真正的女性主义小说</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>你以为那不勒斯很远，但是那种女性才懂的绝望和迷茫是全世界通用的。</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>这套小说有一种奇怪的魔力，完全手不释卷，停不下来，会想一口气看掉，沉迷在人物波澜壮阔的情感和命运里。有一种看情节剧的错觉，而且一点也不累人，翻起来又快又兴奋。莉拉的命运啊，真的，最后在工厂里那一幕，哭死了，为她心碎，她的疯狂和大胆，她的天才和倔强。而莱农的心理描写也非常好看，直接而无任何保留，以后她会袒露自己，还是把自己写成故事呢。现在配角的人物形象都开始丰满起来，但是尼诺反倒有点让人爱不起来，在莉拉的光芒下，他显得迟疑而孱弱，反倒是恩佐和莉拉一起学习的画面又一次激动了人心。继续等第三部第四部，想知道莉拉如何继续把控她的命运。</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>好吧我也没忍住把这本看完了。我现在最大的困惑其实是：这个作者为什么什么都懂！不光是女人们，男人们的歇斯底里，在她笔下也能驾轻就熟。生活就是如此无望，彼此桎梏，每个人都想要挣脱，可都没有结果，只留下了故事。</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>读到一半要气死了，读完了反而释然了，莉拉和莱侬就像两株并生的植物，互相依赖，互相索取，互相想要摆脱对方，又都做不到。不过非常反感作者喜欢在每本书末尾扔炸弹这种做法。</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>很感人的书，尤其是最后几页。我想以后我要是有孩子了，我要让TA在10岁的时候读这本书，让TA看到人与人的温暖和理解，学会对于“少数人”的包容和同理。这世上很多的罪恶，都来源于多数人对“少数人”的暴力。</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>她死得无怨无悔，不欠任何人，也不依赖任何东西。她是我见过最勇敢的人。</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>没有读过这本书的人生跟读过之后的人生，真的很不一样。</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>偏见不仅会消灭肉体（黑人汤姆之死）也会扼杀灵魂（怪人阿瑟·拉德利一生避世）</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>“除非你穿上一个人的鞋子，像他那样走来走去，否则你永远无法真正了解一个人。”</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>第一次看，还是06年第一本的电子书。后来家里有了本盗版全集，大16开800多页，板砖一样。这两天住院期间带了那本“板砖”重温了一遍，印象最深的是胡宗宪打海盗那段，最大的体会是，人可以没有良心但不能没有理想，没有良心的人未必不能做好事，但没有理想的人，只是苟活世间尔。</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>能勾起你读其他书的书，就是好书。</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>入门佳作，但是作者为了趣味性而牺牲了严谨性。</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>一个寒假看完，不拘一格拆解历史，虽不无主观，但的确很好看；最喜欢2、3集，万国来朝，文治武功，宫闱权斗，兄弟反目，于谦、王阳明伟立光明；中期妖孽盛行，流派林立，皇帝老儿冷眼旁观群臣斗；后期党同伐异，万象争流，妖人牛人猛人一锅粥，270多年的帝国灰飞烟灭，浪滔滔千古风流人物，尽成烟云；官场如职场，厚黑学从来没消失过！</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>一部关于厚黑学的血泪史</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>当我沉默的时候,我觉得充实;我将开口,同时感到空虚。</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>似乎鲁迅经常做噩梦...</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>我不愿彷徨于明暗之间，我不如在黑暗里沉没。</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>修行134th，彼时大先生白话文已臻绝顶。这本书是我爹私人藏书中唯一一本鲁迅，我六七岁的时候读过一次，不过必然是有读没有懂，今天读时受到了极大的震撼和感动，昨晚读到手心出汗心绪波动，另外这绝对不是肾虚的表现，我的损友们。最喜欢的是大先生借以自况的复仇者I，于是只剩下广漠的旷野，而他们俩在其间裸着全身，捏着利刃，干枯地立着；以死人似的眼光，赏鉴这路人们的干枯，无血的大戮，而永远沉浸于生命的飞扬的极致的大欢喜中。其次是立论，寥寥几笔白描，爽快淋漓，还有相当几篇感觉没有理解或者没有理解到位，大先生的书，也不是只读一次就可以的</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>初读，重读，长时间读，掰开揉碎了读，半明半暗地读，不管怎么读都那么有味道，仅是这点有几部散文诗集能做到？</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>我对自己的要求很低：我活在世上，无非想要明白些道理，遇见些有趣的事。倘能如我所愿，我的一生就算成功。为此也要去论是非，否则道理不给你明白，有趣的事也不让你遇到。我开始得太晚了，很可能做不成什么，但我总得申明我的态度，所以就有了这本书——为我自己，也代表沉默的大多数。 ——王小波</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>我看现在是冷漠的大多数了</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>与其别人让我闭嘴，不如我自己赶快沉默了去。你的理又不是我的，我跟你辩个五六七八没意思。</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>我们是沉默的大多数，或在内心挣扎，或在脸上写满愤怒，然而结局终究是平庸与顺从。</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>看了一半，难以为继。语言风格是揣着聪明装糊涂，可能是时代需要。关键是这聪明在我看来还不够聪明，不过想想，在那个时代，这应当也是冒险了。庆幸自己生在了现在。唯一的收获是，书中说，看杂文看评论的人，永远不能真正了解一门艺术。算是对自己一记警钟。想要广泛涉猎，高谈阔论，却又不曾自己真正深入过什么，算是一种对艺术的亵渎吧。希望自己多一点沉淀。</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/豆瓣图书Top250本地数据库.xlsx
+++ b/豆瓣图书Top250本地数据库.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F348"/>
+  <dimension ref="A1:F465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12665,6 +12665,4117 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>盛衰之理，本为天命。然而人心就是如此。眼见得他起高楼，于是便不忍心见他楼塌了。见过他鼎盛的时候，再看他的衰败就无比心酸。而更加可悲的是，目睹这场哗变的你，本就是这戏中之人。</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>第一次看《红楼梦》，是小学五年级。因所有人都说，这是部名著，于是，期末考后，怀着极大的敬意与耐心，准备好好下番苦功夫。不曾想，从头到尾，一点不打绊儿地，没花多长时间，就囫囵吞枣地顺利看完，幼小心灵还因此生出些疑问：怎么一点儿不象名著呀，即不难懂，也不深刻，不就是些家长里短的故事集锦吗！ 留下印象的，不是爱情纠葛，不是阶级矛盾，不是白茫茫一片真干净，而是当时粗糙日常生活中，一些根本无法想象的精美事物：比如，一些菜品，要经过如此多复杂细致的步骤，才能一点点做出；比如，一些庭院宅子，院名的起法，树木的搭配，房子的色彩，有那么多讲究；比如，一些好听的布料名，一些古怪材质的饰品，一些用途不明的摆设；再比如，闲谈，对诗，饮茶……才知道，原来人可以这样生活，可以这样打发时间，而不被视为浪费生命，也无需心下内疚，有些无法理解，又有点儿想入非非。 这或许是文学的另一个用处，让人从踏实细节处，活生生触摸到一个时代的体温。只是后来，每当我跟人说起，《红楼梦》对我来说，就是故事会，就是菜谱与家居指南时，十个会有九个半露出惊讶表情，让我觉得自己，可真没文化！</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>亲戚是干什么用的大全</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>长这么大，到今天才把这部奇书读完。觉得并没有那么多微言大义，倒是曹雪芹的文笔实在了得，对人的那些细腻情感拿捏得十分到位。特别想说的一点是，坚决认为林黛玉不能算是什么完美的理想主义者，她非但不完美，而且是毛病最大的一个。所有的问题又都归结于三个字——看不开！</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>一个呼吁：那些清穿小说的主人公你们风花雪月以后就不能顺道送曹雪芹个打印机么？</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>读《活着》的过程我很平静，除了有庆献血而死的描述让我呼吸急促。在那个年代像福贵式的悲剧小人物多如牛毛，他们愚昧，勤劳，坚强，隐忍，他们被时代的洪流裹挟着无法喘息，唯有努力活下去才能活下去。福贵的悲哀是每一个中国人的悲哀，谁都无法幸免。第一次读余华，他看似沉重冷静的描述却字字见血。</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>读起来太顺畅，经典就是经典</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>看见了人生悲苦，看见了底层人民的乐观和坚强，看见了生命的柔韧，看见了命运和岁月那不动声色的力量。</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>第一次见序这么多的一本书。（但是三星是更复杂的原因，短评里说不清的原因，不是因为序多……）</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>在《活着》中，管去世叫“熟了”。最初是福贵的爹“熟了”，初闻不解，后文说道，人死像熟透的梨，离树而落。梨者，离也。</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>自然记得从小学到高中的暑假，坐在空调房间的地板上，一边吃西瓜一边沉浸在魔法世界的时光，记得高中时熬夜刷题的间隙，吃一碗泡面，看一会死亡圣器，枯燥的晚上也充满幻想。再见，我曾经心心念念想去的霍格沃兹。</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>至今还记得，读第一本哈利波特的时候，是站在厨房的灯下一口气读完的。</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>伴随了我整个童年成长的经典小说。现下唯一美中不足的应该就是马爱农和马爱新在圣器那一本翻译的时候不停的引用了本山大叔的小品名句“你太有才了”！</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>想说的都在这儿了。 作者：凉白（来自豆瓣） 来源：https://www.douban.com/doubanapp/dispatch/review/8504335 《哈利.波特-(珍藏版)(全七册)》的豆瓣书评:【“死亡不过是另一场伟大的冒险”】</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>长大了才知道哈利波特不仅仅只是儿童读物</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>这是我看过最吓人的一本书。不是可怕而是深深的恐惧。</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>“让人说话天不会塌下来，有话就说，有屁就放，是香是臭，让群众讨论嘛”。 我不信豆瓣审核连教员的话也删。</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>如果尖锐的批评完全消失，温和的批评将会变得刺耳。如果温和的批评也不被允许，沉默将被认为居心叵测。如果沉默也不再允许，赞扬不够卖力将是一种罪行。如果只允许一种声音存在，那么，唯一存在的那个声音就是谎言。－－－摘自油管</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>有种深刻入骨的悲凉。</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>太阳底下无新事，温斯顿在看得见看不见巨大机器前变成了“消失的老鼠”。没有完美的制度，当你感觉到它是完美的时候，它便开始吞噬你了。电幕面前，2+2必须等于5。</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>大刘，你打开了一扇门，门外的世界一片黑暗，这黑暗中蕴藏的故事，永远讲不完。</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>这么个硬核的科幻是怎么装下了程心这朵白莲花婆娘的…</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>书是好书，纸是烂纸，热爱刘慈欣的读者，请不要买这套</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>他们说，读完这套书以后，再抬头看星空感觉就不一样了。嗯，是这样的。</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>一定要和圣母做闺蜜，这样才能有光速飞船坐~</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>有一天我梦醒了，窗外是氤氲不化的雾气，我走到窗边，原来是夜里下了雪，空气一片苍茫，我又想起思嘉，在那场大雾中迷路，恐慌，奔跑，喘息，寻找，家。而瑞德已决意放弃一切。包括她。但我也不是十五岁的我了。那时我见她玫瑰红睡袍，一杯白兰地，手法娴熟，一饮而尽。我怎么学得会像她喝酒这般痛饮人生。可我知道什么是痛。</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>我认为本书唯一值得称赞的人是梅兰妮，一个真正的勇士、一个坚毅的妻子、一个称职的妈妈、一个挚友。</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>其实每个女子在少女时期内心都有一个艾希礼，走到最后才会明白原来自己爱的是班瑞德</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>差不多半年的时间间隙里重看了一遍。快结束时，巴特勒问斯嘉丽多大了，她答28。我突然被狠狠震惊到，两次看书，几次看电影，都觉得看了他们蓬蓬勃勃跌跌荡荡沧海桑田的一辈子，可她才28！</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>我能说“tomorrow is another day.” 这句话对我人生影响很大吗？</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>25岁生日这天把房思琪交付印厂，简体版2018年1月25号上市。做这本书的过程经历了很多，简体版的授权很不容易，感谢游击文化对我们的信任和配合。简体版也得到了他们的认可，除了几处极个别的涉台词语外极少删减，性描写也基本保留，奕含写的克制而干净，实无删改之必要。感谢出版社老师对这本书的爱护，尊重了作者文字。感谢李银河戴锦华张悦然詹宏志蒋方舟等老师的郑重推荐。感谢很多人，为了房思琪和更多读者的相遇。这本书值得也应该被更多人看到，是我的初衷，也是我的目标。 ps2020.07房思琪精装版出版，把在出版两年多里收到的建议做了用心调整。</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>她懂得很多，说话也很深刻，但却有一种单纯感。我不知道她是怎么做到的，她是深刻和单纯的糅合体。她访谈时说：在读这本书的时候，你能感受到痛，那是真实的；你能感受到美，那也是真实的。我都感受到了，甚至能够感受到她被折磨而无法解脱的心情，这是林奕含留给我们的遗言。</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>北影阿廖沙、侯亮平【被】销声匿迹；恋童癖许豪杰恢复微信公号实名，并反咬一口将不肯透露举报人信息的豆瓣告上法庭；北航博士罗茜茜时隔十二年实名举报教授陈小武曾对她及多名女生性骚扰——这些，是你朝反性暴力的实时进程，我们的#me too#远未成声势。这本书的出版告诉我们：不，你并没有选择，你不再可以假装世界上没有人以强暴小女孩为乐；假装从未有小女孩遭受强暴；假装房思琪从不存在。因为这本书属于“文学”，但不单单属于文学，它是一个承受残暴性伤害的女生，为自己提前写就的悼文；因为强暴，是人类社会有史以来最大的屠杀。读着林奕含的文字，一再想要哀叹“可惜”。但可惜这个词太傲慢、太冷酷了，终归是活人对她文学天才的掂量，对可能存在的所谓文学成就or损失的收支核算。而她经受的苦痛黑洞，这些，根本不足以抵偿。</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>简体版终于体面问世了：「一切文学，余爱以血书者。」</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>整个阅读过程太需要心理承受力了，林奕含真的很会写，也是真的很懂得人间的丑陋，只是这份懂得代价太大了，全是血与泪，和无数个不眠之夜的自我拷问、自我厌弃、自我洗脑，在真实与自我安慰之间做艰难的选择。书前书后那些评论是没有心肝吗？面对这种文字还他妈在讲创作技巧、比喻太多、用笔太工？每看到一句这样的话，都觉得千千万万个房思琪的苦白受了，都觉得人间不值得。希望每个无意间和自己厌弃的人产生了关联、无意间发生共谋、陷入到难以挣脱的亲密关系的人，都能迈过自厌和自恨，不用否定自己的感情，诚实本身就是一种力量，面对、接受、挣脱、成长。</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>再也分不清猪的脸和人的脸</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>「凡動物一律平等，但是有些動物比別的動物更加平等。」</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>短短112页，却细致地展现了极权如何产生发展控制农场的一切。觉得恐惧的地方在于记忆如何被轻易的篡改，有什么是可以确信的？</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>比天气预报准多了</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>长篇大论还真不如故事一则</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>这书我看得特慢，只要出现一个地名我就想在谷歌地形图上给找出来，然后细细从战略层面揣摩用兵之道。特别是街亭之战，光在地图上找到街亭这个屯兵的小谷道就花了不少功夫，刚开始始终想不明白这个离汉中十万八千里的地方到底哪儿重要，后来研究了下才知道古时天水通长安的道路并非沿渭水河谷顺流而下，而是走官陇古道，街亭正处于古道的咽喉之处，蜀丢街亭就意味着把背后留给了魏国，腹背受敌，命都难保。总之这本书值得对着地形图细细揣摩，尤其是诸葛亮六出祁山那段。</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>这曾经是我在小学时反复阅读的一部经典。我极爱她，甚至愿意写下每一个人的名字，并且愿意为了这部小说而去读裴注三国志。一部《三国演义》，可以说是我的文学启蒙，并且让我读繁体毫无问题..别人喜爱诸葛亮，我独独对吕布、陈宫和貂蝉感到惋惜，并且唾弃张文远，这个只顾保命的伪君子..我当时相信是因为诸侯先死，所以才被极尽抹灭的：当时谁还相信这是小说呢？</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>“书生轻议冢中人，冢中笑尔书生气！”</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>我是三国控，不解释。最喜欢的一部古典文学。</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>四大名著中最先看的一本书。不过当时在看时，倒不是跟着传统盲目崇拜起刘备关羽来，而是对被作者百般贬低的人物产生研究兴趣，如周瑜并不心胸狭窄，鲁肃并不平庸，草船“接”箭的是孙权，被关兴杀死的潘璋和孔明同年去世，袁绍深得民心，吕蒙“士别三日”，另外张飞有文采……</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>译得很好。重看一遍越发觉得BBC的《神探夏洛克》改编的真是好啊真是巧啊</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>个人感觉，福尔摩斯只是作为侦探小说的鼻祖之一的地位，但感觉远没有阿婆（阿加莎克里斯蒂）的书来的让人出乎意料，令人回味无穷。</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>这个应该是我人生中第一套书。。。。刚会认字，还不知道“犹他州”（印象深刻）为何物的时候，就在看男主角们搞基了，情何以堪。。。</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>已经读了不知多少遍但真的读一辈子都读不厌</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>为什么妈妈要把它借人？现在好了，只剩一本了！给人家弄丢了。</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>挽狂澜于既倒，扶大厦之将倾。</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>在书店翻完就成，买回家则如同鸡肋。傅高义写这部书的初衷就是向西方人介绍邓小平和他经历过的大时代，可叹的是，今天我们却要把这样一部写给别人的入门书当作我们了解自我的红宝书。</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>总有人希望这本书能有别出心裁的史料和观点，其实这本书最大的贡献在于理清了从1977年到1992年所有历史事件的脉络</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>按照邓小平的遗愿，他的眼角膜被捐出供眼科研究，内脏被捐出供医学研究，遗体被火化，骨灰盒上覆盖着中国共产党党旗。1997年3月2日，他的骨灰被撒入大海。</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>十几岁的时候渴慕着小王子，一天之间可以看四十四次日落。是在多久之后才明白，看四十四次日落的小王子，他有多么难过。</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>读了好多年，终于读完了，但是实在共鸣不起来，虽然知道那些道理，但真的觉得没什么了不起啊，是我还太幼稚吗？</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>我的玫瑰花儿，只有四个微不足道的刺，用来抵御这个世界。</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>说实话 我看不太懂 但还是跟风给个5星吧 以显示我也是有思想有学识之人</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>虽然我实在幼稚，但我并不怎么喜欢孩童般的纯净，我只爱风浪过后的平静，流水打磨出的清亮，大雪纷飞时的安宁，沧桑看透的纯真，我爱眼冷心热的庄子，人究竟无所逃于天地之间，各适其性，做自己认为有意义的事就好了，无论是统治宇宙还是喝酒点灯，对他们来说，都比爱一朵玫瑰重要，这不是很好的么</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>鲁迅如果不被赋予那么多政治色彩，单看作品也是一个优秀的毒舌家的</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>看他的文章还无法醒悟的人是该有多么可悲</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>一个特立独行的人需要金钱来保持他的尊严，否则就只有被毁灭的份，人们是不能容忍一个穷光蛋的异类的。就象一个老姑娘要用钱保持她的高傲，否则就是耻辱。</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>这部小说，大体上是描写了辛亥革命前后乡村发生的一系列的故事，其中以鞭子、革命、秀才、假洋鬼子，扮演出一幅中国传统社会的浮世绘。在这里，我们不妨感慨，鲁迅笔下人物的生命力。鲁迅是描写了辛亥革命前后，我们已经革命胜利六十多年，但是假洋鬼子、赵老太爷难道就绝迹了吗？咸与维新，却一切照旧。</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>狂人在望着赵家的狗，孔乙己在讲茴字的四种写法，华老栓在拿夏瑜的血馒头，九斤老太在感叹一代不如一代，闰土在隔着厚障壁叫我老爷，圆规杨二嫂在捡东西，阿Q在逗尼姑，耍无赖，闹革命，要困觉，精神胜利法，迅哥在怀念那夜似的豆，那夜似的戏。我们在铁屋子里装睡，想着年轻时做过的许多的梦。</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>比格林好，而且寒假过后的几个月，经常在里面翻出压岁钱</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>《海的女儿》是爱情的启蒙。</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>如果不是叶君健译的就不要看，书者与译者相得益彰，擦出的精致纯美，无人可及</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>写给成人的悲伤童话</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>小时候看是童话 现在再看的话才发现都是悲剧</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>三毛的文字其实没有特别出挑的地方，但是合成一篇，整个却显得真实、清爽。她很好地遵循了白话文“有什么说什么，该怎么说就怎么说”的宗旨，而且她聪明在不在散文中论理，不作生硬的哲思，单纯就事论事，从而反倒能让人身临其境~~印象最深的是她和荷西去偷看别人洗澡灌肠，再如三毛考驾照的那几个考题，好笑极了~~而读到他们遇到三个疯子袭击则心提至喉~~看散文，以前喜欢过余秋雨的辞藻，现在越来越喜欢三毛这类的平淡，平淡是真，写文常常有自炫的诱惑，能抵住诱惑是不容易的。。。【题外】三毛与荷西是般配的一对，如果荷西没有去世地那么早，三毛可能也不会弃世了吧。。。“人”果然是两个人互相支撑在一起才能不倒下的。。。</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>自你之后，再无真正流浪自由的灵魂。</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>再看到 荒山之夜 仍然还是以前的震惊！他们那么随便就经历了一场出生入死，而且完全不在意，人生多么的洒脱啊</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>读过三毛全集，最好的还是这一册。</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>你伤害了我的骄傲！</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>经典武学起于春秋，到北宋达到极盛，南宋有所衰落，元末因明教兴盛中兴。明代更有了东方不败等大师。但期间伽利略的出现已预示其衰落。康熙年间出现牛顿，梯云纵灭绝。道光年间出现卡诺，玄冰掌灭绝。尤其是力学定理建立后，内力和轻功全部消失，梯云纵这种只需吐纳练便可自带反重力系统的轻功彻底消失</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>慕容复是没落皇族子孙，毕生追求皇位，对王语嫣视如草介，段誉是正牌皇帝继承人，却爱美人宁弃江山。你所追的，正是我所弃的，尽道人生的可笑荒谬。</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>因为众生皆苦，便觉得自己也不是很苦。</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>金圣叹评《水浒》论武松为天人，萧峰何尝不是天人。看他有阔处，有毒处，有正处，有良处，有快处，有真处，有捷处，有雅处，有大处，有警处，实是金大侠小说中之第一人。</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>偌大一本书，数百豪杰人物，萧峰一出，全归背景</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>理性的培养、逻辑的思维、高雅的阅读等不能让别人爱你，但却能让你坦然接受不被爱。</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>我一度以为二十多岁是一个人最难熬的一段时间，在这段时间里要实现从少年到青年的转换。看了这四本书之后发现人一辈子都在挣扎，只是每个时期面临的困难不同罢了，我们一直都经历着角色的转换。</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>会让你在读完最后一行后想要重新翻开《我的天才女友》的第一页。</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>也许莉拉吸引尼诺的地方，就是尼诺在她身上，开始看到了以为自己也有的东西，但对比之下他发现自己并没有。她拥有才智，但她没有利用它为自己谋福利，而像贵妇一样在挥霍着自己的才智，就好像对她来说，整个世界的财富都是庸俗的。莉拉的才智是免费的，这就是她让尼诺入迷的原因。“她和其他女人不一样，因为她天生就那么桀骜不驯，不会为任何事儿弯腰。”我们所有人都做出让步了，经过考验、失败和成功，这种让步重新塑造了我们。只有莉拉，没有任何人、任何事可以改变她。不仅如此，随着年龄的增长，她和任何人一样变得顽固和难相处，但她的那些品质一直都原封未动，甚至更加坚固。我们恨她的同时，也害怕她，会对她充满敬意。</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>读完那不勒斯四部曲的雨夜，人生几十年，像是一场玩笑，像是一次为了记录而存在的表演。</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>洪荒巨兽，太巨大了。老陀的体量感真不是盖的，契诃夫、布尔加科夫、《百年孤独》、《悉达多》，简直都好像只是从他身上抽下来一根骨头。一边读一边也遗憾：涅朵奇卡没有写完，卡拉马佐夫没有写完，契诃夫死得那么早...</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>这是一个缺失信仰的年代。这是一个焦虑爆棚的年代。当大家都在忙着读心灵鸡汤，来寻找到人生真谛的时候，推荐你读一读这本《卡拉马佐夫兄弟》，一本被无数大师封神的小说。 这本小说，在文学史上的地位已经毋庸置疑，它极其真实的写出了人性中种种的崇高与丑恶，它像一面镜子，在其中你会看到一个你都不想承认的自己。这本书，是完美的将哲学、神学、心理学融为一体的杰作。 就连最狂傲的，自命为天才的尼采，读完此书也不得不承认：“陀思妥耶夫斯基是我生命中最美好的际遇，他是一个思想深刻的人，他有充分的权利，蔑视我们这些浅薄的德国人。”</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>那时候我太轻狂，只觉得他太多话，没察觉那是另一种沉默，或者说那是沉默的尽头。</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>《宗教大法官》一章另添一星，翻译再添一星，这书至少该打七星！</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>不知是陀氏自身还是荣如德功劳，语言意蕴丰满，两本大部头看起来很愉快。上海译文这版版式不错，插画精美，如果有精装版就更好了。当时的俄罗斯刚刚破除农奴制，新思潮涌入，宗教却依然占据主导。陀氏虽然拥有一定的倾向性，但理性的光芒已锐不可当。感觉“宗教大法官”和“魔鬼。伊万·费奥多罗维奇的梦魇”两节最为精彩，其中“宗”一节直接逼问上帝，毫不留情揭露宗教，大快人心。相比之下，想到《我的个神啊》这种幼稚的意淫如此为人追捧，只得耻笑。</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>我很真诚的讲：作者用极其扎实的故事告诉了女人们，为什么不能太早结婚以及为什么要坚持上学读书……（一本真正的女性主义小说</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>你以为那不勒斯很远，但是那种女性才懂的绝望和迷茫是全世界通用的。</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>这套小说有一种奇怪的魔力，完全手不释卷，停不下来，会想一口气看掉，沉迷在人物波澜壮阔的情感和命运里。有一种看情节剧的错觉，而且一点也不累人，翻起来又快又兴奋。莉拉的命运啊，真的，最后在工厂里那一幕，哭死了，为她心碎，她的疯狂和大胆，她的天才和倔强。而莱农的心理描写也非常好看，直接而无任何保留，以后她会袒露自己，还是把自己写成故事呢。现在配角的人物形象都开始丰满起来，但是尼诺反倒有点让人爱不起来，在莉拉的光芒下，他显得迟疑而孱弱，反倒是恩佐和莉拉一起学习的画面又一次激动了人心。继续等第三部第四部，想知道莉拉如何继续把控她的命运。</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>好吧我也没忍住把这本看完了。我现在最大的困惑其实是：这个作者为什么什么都懂！不光是女人们，男人们的歇斯底里，在她笔下也能驾轻就熟。生活就是如此无望，彼此桎梏，每个人都想要挣脱，可都没有结果，只留下了故事。</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>读到一半要气死了，读完了反而释然了，莉拉和莱侬就像两株并生的植物，互相依赖，互相索取，互相想要摆脱对方，又都做不到。不过非常反感作者喜欢在每本书末尾扔炸弹这种做法。</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>很感人的书，尤其是最后几页。我想以后我要是有孩子了，我要让TA在10岁的时候读这本书，让TA看到人与人的温暖和理解，学会对于“少数人”的包容和同理。这世上很多的罪恶，都来源于多数人对“少数人”的暴力。</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>她死得无怨无悔，不欠任何人，也不依赖任何东西。她是我见过最勇敢的人。</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>没有读过这本书的人生跟读过之后的人生，真的很不一样。</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>偏见不仅会消灭肉体（黑人汤姆之死）也会扼杀灵魂（怪人阿瑟·拉德利一生避世）</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>“除非你穿上一个人的鞋子，像他那样走来走去，否则你永远无法真正了解一个人。”</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>第一次看，还是06年第一本的电子书。后来家里有了本盗版全集，大16开800多页，板砖一样。这两天住院期间带了那本“板砖”重温了一遍，印象最深的是胡宗宪打海盗那段，最大的体会是，人可以没有良心但不能没有理想，没有良心的人未必不能做好事，但没有理想的人，只是苟活世间尔。</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>能勾起你读其他书的书，就是好书。</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>入门佳作，但是作者为了趣味性而牺牲了严谨性。</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>一个寒假看完，不拘一格拆解历史，虽不无主观，但的确很好看；最喜欢2、3集，万国来朝，文治武功，宫闱权斗，兄弟反目，于谦、王阳明伟立光明；中期妖孽盛行，流派林立，皇帝老儿冷眼旁观群臣斗；后期党同伐异，万象争流，妖人牛人猛人一锅粥，270多年的帝国灰飞烟灭，浪滔滔千古风流人物，尽成烟云；官场如职场，厚黑学从来没消失过！</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>一部关于厚黑学的血泪史</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>当我沉默的时候,我觉得充实;我将开口,同时感到空虚。</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>似乎鲁迅经常做噩梦...</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>我不愿彷徨于明暗之间，我不如在黑暗里沉没。</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>修行134th，彼时大先生白话文已臻绝顶。这本书是我爹私人藏书中唯一一本鲁迅，我六七岁的时候读过一次，不过必然是有读没有懂，今天读时受到了极大的震撼和感动，昨晚读到手心出汗心绪波动，另外这绝对不是肾虚的表现，我的损友们。最喜欢的是大先生借以自况的复仇者I，于是只剩下广漠的旷野，而他们俩在其间裸着全身，捏着利刃，干枯地立着；以死人似的眼光，赏鉴这路人们的干枯，无血的大戮，而永远沉浸于生命的飞扬的极致的大欢喜中。其次是立论，寥寥几笔白描，爽快淋漓，还有相当几篇感觉没有理解或者没有理解到位，大先生的书，也不是只读一次就可以的</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>初读，重读，长时间读，掰开揉碎了读，半明半暗地读，不管怎么读都那么有味道，仅是这点有几部散文诗集能做到？</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>我对自己的要求很低：我活在世上，无非想要明白些道理，遇见些有趣的事。倘能如我所愿，我的一生就算成功。为此也要去论是非，否则道理不给你明白，有趣的事也不让你遇到。我开始得太晚了，很可能做不成什么，但我总得申明我的态度，所以就有了这本书——为我自己，也代表沉默的大多数。 ——王小波</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>我看现在是冷漠的大多数了</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>与其别人让我闭嘴，不如我自己赶快沉默了去。你的理又不是我的，我跟你辩个五六七八没意思。</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>我们是沉默的大多数，或在内心挣扎，或在脸上写满愤怒，然而结局终究是平庸与顺从。</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>看了一半，难以为继。语言风格是揣着聪明装糊涂，可能是时代需要。关键是这聪明在我看来还不够聪明，不过想想，在那个时代，这应当也是冒险了。庆幸自己生在了现在。唯一的收获是，书中说，看杂文看评论的人，永远不能真正了解一门艺术。算是对自己一记警钟。想要广泛涉猎，高谈阔论，却又不曾自己真正深入过什么，算是一种对艺术的亵渎吧。希望自己多一点沉淀。</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/豆瓣图书Top250本地数据库.xlsx
+++ b/豆瓣图书Top250本地数据库.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F465"/>
+  <dimension ref="A1:F578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16776,6 +16776,3997 @@
         </is>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>盛衰之理，本为天命。然而人心就是如此。眼见得他起高楼，于是便不忍心见他楼塌了。见过他鼎盛的时候，再看他的衰败就无比心酸。而更加可悲的是，目睹这场哗变的你，本就是这戏中之人。</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>第一次看《红楼梦》，是小学五年级。因所有人都说，这是部名著，于是，期末考后，怀着极大的敬意与耐心，准备好好下番苦功夫。不曾想，从头到尾，一点不打绊儿地，没花多长时间，就囫囵吞枣地顺利看完，幼小心灵还因此生出些疑问：怎么一点儿不象名著呀，即不难懂，也不深刻，不就是些家长里短的故事集锦吗！ 留下印象的，不是爱情纠葛，不是阶级矛盾，不是白茫茫一片真干净，而是当时粗糙日常生活中，一些根本无法想象的精美事物：比如，一些菜品，要经过如此多复杂细致的步骤，才能一点点做出；比如，一些庭院宅子，院名的起法，树木的搭配，房子的色彩，有那么多讲究；比如，一些好听的布料名，一些古怪材质的饰品，一些用途不明的摆设；再比如，闲谈，对诗，饮茶……才知道，原来人可以这样生活，可以这样打发时间，而不被视为浪费生命，也无需心下内疚，有些无法理解，又有点儿想入非非。 这或许是文学的另一个用处，让人从踏实细节处，活生生触摸到一个时代的体温。只是后来，每当我跟人说起，《红楼梦》对我来说，就是故事会，就是菜谱与家居指南时，十个会有九个半露出惊讶表情，让我觉得自己，可真没文化！</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>亲戚是干什么用的大全</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>长这么大，到今天才把这部奇书读完。觉得并没有那么多微言大义，倒是曹雪芹的文笔实在了得，对人的那些细腻情感拿捏得十分到位。特别想说的一点是，坚决认为林黛玉不能算是什么完美的理想主义者，她非但不完美，而且是毛病最大的一个。所有的问题又都归结于三个字——看不开！</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>9787020002207</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>《红楼梦》是一部百科全书式的长篇小说。以宝黛爱情悲剧为主线，以四大家族的荣辱兴衰为背景，描绘出18世纪中国封建社会的方方面面，以及封建专制下新兴资本主义民主思想的萌动。结构宏大、情节委婉、细节精致，人物形象栩栩如生，声口毕现，堪称中国古代小说中的经 典。
+由红楼梦研究所校注、人民文学出版社出版的《红楼梦》以庚辰（1760）本《脂砚斋重评石头记》为底本，以甲戌（1754）本、已卯（1759）本、蒙古王府本、戚蓼生序本、舒元炜序本、郑振铎藏本、红楼梦稿本、列宁格勒藏本（俄藏本）、程甲本、程乙本等众多版本为参校本，是一个博采众长、非常适合大众阅读的本子；同时，对底本的重要修改，皆出校记，读者可因以了解《红楼梦》的不同版本状况。
+红学所的校注本已印行二十五年，其间1994年曾做过一次修订，又十几年过去，2008年推出修订第三版，体现了新的校注成果和科研成果。...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>一个呼吁：那些清穿小说的主人公你们风花雪月以后就不能顺道送曹雪芹个打印机么？</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1007305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>活着</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>9787506365437</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>《活着(新版)》讲述了农村人福贵悲惨的人生遭遇。福贵本是个阔少爷，可他嗜赌如命，终于赌光了家业，一贫如洗。他的父亲被他活活气死，母亲则在穷困中患了重病，福贵前去求药，却在途中被国民党抓去当壮丁。经过几番波折回到家里，才知道母亲早已去世，妻子家珍含辛茹苦地养大两个儿女。此后更加悲惨的命运一次又一次降临到福贵身上，他的妻子、儿女和孙子相继死去，最后只剩福贵和一头老牛相依为命，但老人依旧活着，仿佛比往日更加洒脱与坚强。
+《活着(新版)》荣获意大利格林扎纳•卡佛文学奖最高奖项（1998年）、台湾《中国时报》10本好书奖（1994年）、香港“博益”15本好书奖（1994年）、第三届世界华文“冰心文学奖”（2002年），入选香港《亚洲周刊》评选的“20世纪中文小说百年百强”、中国百位批评家和文学编辑评选的“20世纪90年代最有影响的10部作品”。</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4913064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>自然记得从小学到高中的暑假，坐在空调房间的地板上，一边吃西瓜一边沉浸在魔法世界的时光，记得高中时熬夜刷题的间隙，吃一碗泡面，看一会死亡圣器，枯燥的晚上也充满幻想。再见，我曾经心心念念想去的霍格沃兹。</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>至今还记得，读第一本哈利波特的时候，是站在厨房的灯下一口气读完的。</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>伴随了我整个童年成长的经典小说。现下唯一美中不足的应该就是马爱农和马爱新在圣器那一本翻译的时候不停的引用了本山大叔的小品名句“你太有才了”！</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>想说的都在这儿了。 作者：凉白（来自豆瓣） 来源：https://www.douban.com/doubanapp/dispatch/review/8504335 《哈利.波特-(珍藏版)(全七册)》的豆瓣书评:【“死亡不过是另一场伟大的冒险”】</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>哈利·波特</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>9787020096695</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>《哈利·波特(共7册)(精)》编著者J.K.罗琳。
+ 《哈利·波特(共7册)(精)》内容提要：2000年的一个深夜，在美国书店的烛光中，穿着黑斗篷，戴着小眼镜的店员开始销售“哈利o波特4”英文版，从此哈利·波特系列图书席卷全球，也是在这一年，简体中文版“哈利o波特”系列图书通过人民文学出版社引进版权登陆中国，作者J.K.罗琳用一种简单的魔法游戏将魔幻的故事传递给了中国乃至全球的青少年读者，与此同时商业电影的改编更是将这部魔幻题材的小说推向了巅峰。
+ 截止到2013年，哈利·波特系列图书累计销量达到200多万套。
+ 此次，人民文学出版社隆重推出《哈利o波特（精装本）》（全七册），此套精装珍藏版《哈利·波特》听取广大资深哈迷的心声，恢复选用陪伴广大哈迷十年之久深入人心的原有封面，并在此基础上提高工艺、完善装帧，配有独具匠心的精美函套，使...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>长大了才知道哈利波特不仅仅只是儿童读物</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/24531956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>这是我看过最吓人的一本书。不是可怕而是深深的恐惧。</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>“让人说话天不会塌下来，有话就说，有屁就放，是香是臭，让群众讨论嘛”。 我不信豆瓣审核连教员的话也删。</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>如果尖锐的批评完全消失，温和的批评将会变得刺耳。如果温和的批评也不被允许，沉默将被认为居心叵测。如果沉默也不再允许，赞扬不够卖力将是一种罪行。如果只允许一种声音存在，那么，唯一存在的那个声音就是谎言。－－－摘自油管</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>有种深刻入骨的悲凉。</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>9787530210291</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>★村上春树以《1Q84》向本书致敬
+★著名学者刘绍铭经典译本内地首次出版
+★62种文字风靡110个国家，全球销量超过5000万册
+★《时代周刊》“最好的100本英语小说”
+★兰登书屋“100本20世纪最佳英语小说”
+★入选英美中学生必读书书目
+1936年以来，我所写的每 一部严肃作品，都是直接或间接地反对极权主义，支持我所理解的民主社会主义。 ——乔治•奥威尔（《我为何写作》）
+《1984》是一部杰出的政治寓言小说，也是一部幻想小说。作品刻画了人类在极权主义社会的生存状态，有若一个永不褪色的警示标签，警醒世人提防这种预想中的黑暗成为现实。历经几十年，其生命力益显强大，被誉为20世纪影响最为深远的文学经典之一。</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>太阳底下无新事，温斯顿在看得见看不见巨大机器前变成了“消失的老鼠”。没有完美的制度，当你感觉到它是完美的时候，它便开始吞噬你了。电幕面前，2+2必须等于5。</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/4820710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>大刘，你打开了一扇门，门外的世界一片黑暗，这黑暗中蕴藏的故事，永远讲不完。</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>这么个硬核的科幻是怎么装下了程心这朵白莲花婆娘的…</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>书是好书，纸是烂纸，热爱刘慈欣的读者，请不要买这套</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>他们说，读完这套书以后，再抬头看星空感觉就不一样了。嗯，是这样的。</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>三体全集 : 地球往事三部曲</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>9787229042066</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>《地球往事·三体》
+文化大革命如火如荼进行的同时，军方探寻外星文明的绝秘计划“红岸工程”取得了突破性进展。但在按下发射键的那一刻，历经劫难的叶文洁没有意识到，她彻底改变了人类的命运。
+地球文明向宇宙发出的第一声啼鸣，以太阳为中心，以光速向宇宙深处飞驰……
+四光年外，“三体文明”正苦苦挣扎——三颗无规则运行的太阳主导下的百余次毁灭与重生逼迫他们逃离母星。而恰在此时，他们接收到了地球发来的信息。
+在运用超技术锁死地球人的基础科学之后，三体人庞大的宇宙舰队开始向地球进发……人类的末日悄然来临。
+《地球往事·黑暗森林》
+三体人在利用魔法般的科技锁死了地球人的科学之后，庞大的宇宙舰队杀气腾腾地直扑太阳系，意欲清除地球文明。
+面对前所未有的危局，经历过无数磨难的地球人组建起同样庞大的太空舰队，同时，利用三体人思维透明的致命缺陷，制订了神秘莫测的“面壁计划”，精选...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>一定要和圣母做闺蜜，这样才能有光速飞船坐~</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6518605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>百年孤独</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>9787544253994</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>《百年孤独》是魔幻现实主义文学的代表作，描写了布恩迪亚家族七代人的传奇故事，以及加勒比海沿岸小镇马孔多的百年兴衰，反映了拉丁美洲一个世纪以来风云变幻的历史。作品融入神话传说、民间故事、宗教典故等神秘因素，巧妙地糅合了现实与虚幻，展现出一个瑰丽的想象世界，成为20世纪最重要的经典文学巨著之一。1982年加西亚•马尔克斯获得诺贝尔文学奖，奠定世界级文学大师的地位，很大程度上乃是凭借《百年孤独》的巨大影响。</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6082808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>有一天我梦醒了，窗外是氤氲不化的雾气，我走到窗边，原来是夜里下了雪，空气一片苍茫，我又想起思嘉，在那场大雾中迷路，恐慌，奔跑，喘息，寻找，家。而瑞德已决意放弃一切。包括她。但我也不是十五岁的我了。那时我见她玫瑰红睡袍，一杯白兰地，手法娴熟，一饮而尽。我怎么学得会像她喝酒这般痛饮人生。可我知道什么是痛。</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>我认为本书唯一值得称赞的人是梅兰妮，一个真正的勇士、一个坚毅的妻子、一个称职的妈妈、一个挚友。</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>其实每个女子在少女时期内心都有一个艾希礼，走到最后才会明白原来自己爱的是班瑞德</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>差不多半年的时间间隙里重看了一遍。快结束时，巴特勒问斯嘉丽多大了，她答28。我突然被狠狠震惊到，两次看书，几次看电影，都觉得看了他们蓬蓬勃勃跌跌荡荡沧海桑田的一辈子，可她才28！</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>9787806570920</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>小说中的故事发生在1861年美国南北战争前夕。生活在南方的少女郝思嘉从小深受南方文化传统的熏陶，可在她的血液里却流淌着野性的叛逆因素。随着战火的蔓廷和生活环境的恶化，郝思嘉的叛逆个性越来越丰满，越鲜明，在一系列的的挫折中她改造了自我，改变了个人甚至整个家族的命运，成为时代时势造就的新女性的形象。
+作品在描绘人物生活与爱情的同时，勾勒出南北双方在政治，经济，文化各个层次的异同，具有浓厚的史诗风格，堪称美国历史转折时期的真实写照，同时也成为历久不衰的爱情经典。</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>我能说“tomorrow is another day.” 这句话对我人生影响很大吗？</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1068920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>房思琪的初恋乐园</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>9787559614636</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>令人心碎却无能为力的真实故事。
+向死而生的文学绝唱 打动万千读者的年度华语小说。
+李银河 戴锦华 骆以军 张悦然 詹宏志 蒋方舟 等多位学者作家社会名人郑重推荐。
+痛苦的际遇是如此难以分享，好险这个世界还有文学。
+我下楼拿作文给李老师改。他掏出来，我被逼到 涂在墙上。老师说了九个字：“不行的话，嘴巴可以吧。”我说了五个字：“不行，我不会。”他就塞进来。那感觉像溺水。可以说话之后，我对老师说：“对不起。”有一种功课做不好的感觉。
+小小的房思琪住在金碧辉煌的人生里，她的脸和她可以想象的将来一样漂亮。补习班语文名师李国华是同一栋高级住宅的邻居。崇拜文学的小房思琪同样崇拜饱读诗书的李老师。
+有一天李老师说，你的程度这么好，不如每个礼拜交一篇作文给我吧，不收你周点费。思琪听话地下楼了。老师在家里等她，桌上没有纸笔。
+思琪的初恋是李老师。因为李老师把她翻面，把...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>暂无短评数据</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/27614904/</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>再也分不清猪的脸和人的脸</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>「凡動物一律平等，但是有些動物比別的動物更加平等。」</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>短短112页，却细致地展现了极权如何产生发展控制农场的一切。觉得恐惧的地方在于记忆如何被轻易的篡改，有什么是可以确信的？</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>比天气预报准多了</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>动物农场</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>9787532741854</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>《动物农场》是奥威尔最优秀的作品之一，是一则入木三分的反乌托的政治讽喻寓言。
+农场的一群动物成功地进行了一场“革命”，将压榨他们的人类东家赶出农场，建立起一个平等的动物社会。然而，动物领袖，那些聪明的猪们最终却篡夺了革命的果实，成为比人类东家更加独裁和极权的统治者。</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>长篇大论还真不如故事一则</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/2035179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>这书我看得特慢，只要出现一个地名我就想在谷歌地形图上给找出来，然后细细从战略层面揣摩用兵之道。特别是街亭之战，光在地图上找到街亭这个屯兵的小谷道就花了不少功夫，刚开始始终想不明白这个离汉中十万八千里的地方到底哪儿重要，后来研究了下才知道古时天水通长安的道路并非沿渭水河谷顺流而下，而是走官陇古道，街亭正处于古道的咽喉之处，蜀丢街亭就意味着把背后留给了魏国，腹背受敌，命都难保。总之这本书值得对着地形图细细揣摩，尤其是诸葛亮六出祁山那段。</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>这曾经是我在小学时反复阅读的一部经典。我极爱她，甚至愿意写下每一个人的名字，并且愿意为了这部小说而去读裴注三国志。一部《三国演义》，可以说是我的文学启蒙，并且让我读繁体毫无问题..别人喜爱诸葛亮，我独独对吕布、陈宫和貂蝉感到惋惜，并且唾弃张文远，这个只顾保命的伪君子..我当时相信是因为诸侯先死，所以才被极尽抹灭的：当时谁还相信这是小说呢？</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>“书生轻议冢中人，冢中笑尔书生气！”</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>我是三国控，不解释。最喜欢的一部古典文学。</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>三国演义（全二册）</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>9787020008728</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>《三国演义》又名《三国志演义》、《三国志通俗演义》，是我国小说史上最著名最杰出的长篇章回体历史小说。 《三国演义》的作者是元末明初人罗贯中，由毛纶，毛宗岗父子批改。在其成书前，“三国故事”已经历了数百年的历史发展过程。在唐代，三国故事已广为流传，连儿童都很熟悉。随着市民文艺的发展，宋代的“说话”艺人，已有专门说三国故事的，当时称为“说三分”。元代出现的《三国志平话》，实际上是从说书人使用的本子，虽较简略粗糙，但已初肯《三国演义》的规模。罗贯中在群众传说和民间艺人创作的基础上，又依据陈寿《三国志》及裴松之注中所征引的资料（还包括《世说新语》及注中的资料），经过巨大的创作劳动，写在了规模宏伟的巨著——《三国志通俗演义》全书24卷，240回。后来经过毛纶，毛宗岗父子批改，形成我们现在所见的《三国演义》120回版 
+ 由于人文出版社选取的毛批版本和...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>四大名著中最先看的一本书。不过当时在看时，倒不是跟着传统盲目崇拜起刘备关羽来，而是对被作者百般贬低的人物产生研究兴趣，如周瑜并不心胸狭窄，鲁肃并不平庸，草船“接”箭的是孙权，被关兴杀死的潘璋和孔明同年去世，袁绍深得民心，吕蒙“士别三日”，另外张飞有文采……</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1019568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>译得很好。重看一遍越发觉得BBC的《神探夏洛克》改编的真是好啊真是巧啊</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>个人感觉，福尔摩斯只是作为侦探小说的鼻祖之一的地位，但感觉远没有阿婆（阿加莎克里斯蒂）的书来的让人出乎意料，令人回味无穷。</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>这个应该是我人生中第一套书。。。。刚会认字，还不知道“犹他州”（印象深刻）为何物的时候，就在看男主角们搞基了，情何以堪。。。</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>已经读了不知多少遍但真的读一辈子都读不厌</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>福尔摩斯探案全集（上中下）</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>9787501408580</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>531；706；583</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>最经典的群众出版社的翻译版本，一经出版，立即风靡成千上万的中国人。离奇的情节，扣人的悬念，世界上最聪明的侦探，人间最诡秘的案情，福尔摩斯不但让罪犯无处藏身，也让你的脑细胞热情激荡，本套书获第一届全国优秀外国文学图书奖。</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>为什么妈妈要把它借人？现在好了，只剩一本了！给人家弄丢了。</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1040211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>新版封面，严重剧透。</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>把小说写成这样绝对是开挂了吧，除了连番登场的几十号人物，随处雕琢的大时代的背景也让人叹为观止。对人性的挖掘比起吉田修一还是弱一些，就是纯好看，从第一句开始吸住你逐渐往往里掉。</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>情有可原，罪无可恕。</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>故事中男女主人公从头到尾没有一句对白，经典。</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>白夜行</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>9787544258609</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>东野圭吾万千书迷心中的无冕之王
+周刊文春推理小说年度BEST10第1名
+本格推理小说年度BEST10第2名
+《白夜行》是东野圭吾迄今口碑最好的长篇杰作，具备经典名著的一切要素：
+一宗离奇命案牵出跨度近20年步步惊心的故事：悲凉的爱情、吊诡的命运、令人发指的犯罪、复杂人性的对决与救赎……
+-------------------------------------------------------------------
+1973年，大阪的一栋废弃建筑中发现一名遭利器刺死的男子。案件扑朔迷离，悬而未决。
+此后20年间，案件滋生出的恶逐渐萌芽生长，绽放出恶之花。案件相关者的人生逐渐被越来越重的阴影笼罩……
+“我的天空里没有太阳，总是黑夜，但并不暗，因为有东西代替了太阳。虽然没有太阳那么明亮，但对我来说已经足够。
+凭借着这份光，我便能把黑夜当成白天。
+我从...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>张无忌的妈妈也说过 不要轻易相信漂亮女人 她们的演技和城府都是你无法想象的 无删减版本比之前的版本多了关于性的描写 阴茎和乳房等词汇也直接被接纳进来 前十章用来构建人物关系和埋下案件伏笔 从第十章开始抽丝剥茧地隐现真相 枪虾和虾虎鱼（雪穗和桐原）的关系日渐明朗 遗憾的是关于后半段作者的笔锋开始出现倦怠 没有给出很完整明确的指示或者暗示 对于最后整体的真相的揭露也并没有很吃惊 除了娈童之外 其他的因果其实已了然于心</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/10554308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>挽狂澜于既倒，扶大厦之将倾。</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>在书店翻完就成，买回家则如同鸡肋。傅高义写这部书的初衷就是向西方人介绍邓小平和他经历过的大时代，可叹的是，今天我们却要把这样一部写给别人的入门书当作我们了解自我的红宝书。</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>总有人希望这本书能有别出心裁的史料和观点，其实这本书最大的贡献在于理清了从1977年到1992年所有历史事件的脉络</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr"/>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>邓小平时代</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>9787108041531</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>邓小平深刻影响了中国历史和世界历史的走向，也改变了每一个当代中国人的命运。解读邓小平的政治生涯及其行为逻辑，就是解读当代中国，解读个人命运背后的历史变局。
+哈佛大学傅高义教授倾十年心力完成的巨著《邓小平时代》，是对邓小平跌宕起伏的一生以及中国惊险崎岖的改革开放之路的全景式描述。作者以丰富的史料、国内外重要的研究成果、档案资料和为数众多的独家访谈为基础，对邓小平个人性格及执政风格进行了深层分析，并对中国改革开放史进行了完整而独到的阐释。全书人物、事件众多，既有对毛泽东、周恩来、邓小平、陈云等人相互关系的细致解读，又有对三中全会、权力过渡、中美建交、政改试水、经济特区、一国两制、九二南巡等重大事件和决策的深入分析。全书持论严谨、脉络清晰、观点鲜明、叙述生动，力图使人物言行符合历史情境，对改革开放的历史进程亦时有独特看法，引人深思，被誉为邓小平研究“纪念碑...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>按照邓小平的遗愿，他的眼角膜被捐出供眼科研究，内脏被捐出供医学研究，遗体被火化，骨灰盒上覆盖着中国共产党党旗。1997年3月2日，他的骨灰被撒入大海。</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/20424526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>十几岁的时候渴慕着小王子，一天之间可以看四十四次日落。是在多久之后才明白，看四十四次日落的小王子，他有多么难过。</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>读了好多年，终于读完了，但是实在共鸣不起来，虽然知道那些道理，但真的觉得没什么了不起啊，是我还太幼稚吗？</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>我的玫瑰花儿，只有四个微不足道的刺，用来抵御这个世界。</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>说实话 我看不太懂 但还是跟风给个5星吧 以显示我也是有思想有学识之人</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>小王子</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>9787020042494</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>小王子是一个超凡脱俗的仙童，他住在一颗只比他大一丁点儿的小行星上。陪伴他的是一朵他非常喜爱的小玫瑰花。但玫瑰花的虚荣心伤害了小王子对她的感情。小王子告别小行星，开始了遨游太空的旅行。他先后访问了六个行星，各种见闻使他陷入忧伤，他感到大人们荒唐可笑、太不正常。只有在其中一个点灯人的星球上，小王子才找到一个可以作为朋友的人。但点灯人的天地又十分狭小，除了点灯人他自己，不能容下第二个人。在地理学家的指点下，孤单的小王子来到人类居住的地球。
+小王子发现人类缺乏想象力，只知像鹦鹉那样重复别人讲过的话。小王子这时越来越思念自己星球上的那枝小玫瑰。后来，小王子遇到一只小狐狸，小王子用耐心征服了小狐狸，与它结成了亲密的朋友。小狐狸把自己心中的秘密——肉眼看不见事务的本质，只有用心灵才能洞察一切——作为礼物，送给小王子。用这个秘密，小王子在撒哈拉大沙漠与遇险的飞行员一...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>虽然我实在幼稚，但我并不怎么喜欢孩童般的纯净，我只爱风浪过后的平静，流水打磨出的清亮，大雪纷飞时的安宁，沧桑看透的纯真，我爱眼冷心热的庄子，人究竟无所逃于天地之间，各适其性，做自己认为有意义的事就好了，无论是统治宇宙还是喝酒点灯，对他们来说，都比爱一朵玫瑰重要，这不是很好的么</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1084336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>鲁迅如果不被赋予那么多政治色彩，单看作品也是一个优秀的毒舌家的</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>看他的文章还无法醒悟的人是该有多么可悲</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>一个特立独行的人需要金钱来保持他的尊严，否则就只有被毁灭的份，人们是不能容忍一个穷光蛋的异类的。就象一个老姑娘要用钱保持她的高傲，否则就是耻辱。</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>这部小说，大体上是描写了辛亥革命前后乡村发生的一系列的故事，其中以鞭子、革命、秀才、假洋鬼子，扮演出一幅中国传统社会的浮世绘。在这里，我们不妨感慨，鲁迅笔下人物的生命力。鲁迅是描写了辛亥革命前后，我们已经革命胜利六十多年，但是假洋鬼子、赵老太爷难道就绝迹了吗？咸与维新，却一切照旧。</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>呐喊</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>《呐喊》收录作者1918年至1922年所作小说十四篇。1923年8月由北京新潮社出版，原收十五篇，列为该社《文艺丛书》之一。1924年5月第三次印刷时起，改由北京北新书局出版，列为作者所编的《乌合丛书》之一。1930年1 月第十三次印刷时，由作者抽去其中的《不周山》一篇(后改名为《补天》，收入《故事新编》)。作者生前共印行二十二版次。</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>狂人在望着赵家的狗，孔乙己在讲茴字的四种写法，华老栓在拿夏瑜的血馒头，九斤老太在感叹一代不如一代，闰土在隔着厚障壁叫我老爷，圆规杨二嫂在捡东西，阿Q在逗尼姑，耍无赖，闹革命，要困觉，精神胜利法，迅哥在怀念那夜似的豆，那夜似的戏。我们在铁屋子里装睡，想着年轻时做过的许多的梦。</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1449351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>比格林好，而且寒假过后的几个月，经常在里面翻出压岁钱</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>《海的女儿》是爱情的启蒙。</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>如果不是叶君健译的就不要看，书者与译者相得益彰，擦出的精致纯美，无人可及</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>写给成人的悲伤童话</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>安徒生童话故事集</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>9787020017713</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>安徒生是丹麦19世纪著名童话作家，世界文学童话创始人。他生于欧登塞城一个贫苦鞋匠家庭，早年在慈善学校读过书，当过学徒工。受父亲和民间口头文学影响，他自幼酷爱文学。
+“为了争取未来的一代”，安徒生决定给孩子写童话，出版了《讲给孩子们听的故事》。此后数年，每年圣诞节都出版一本这样的童话集。其后又不断发表新作，直到1872年因患癌症才逐渐搁笔。近40年间，共计写了童话168篇。
+安徒生的创作可分早、中、晚三个时期。早期童话多充满绮丽的幻想、乐观的精神，体现现实主义和浪漫主义相结合的特点。代表作有《打火匣》、《小意达的花儿》、《拇指姑娘》、《海的女儿》、《野天鹅》、《丑小鸭》等。中期童话，幻想成分减弱，现实成分相对增强。在鞭挞丑恶、歌颂善良中，表现了对美好生活的执着追求，也流露了缺乏信心的忧郁情绪。代表作有《卖火柴的小女孩》、《白雪皇后》、《影子》、《一滴水...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>小时候看是童话 现在再看的话才发现都是悲剧</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1046209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>三毛的文字其实没有特别出挑的地方，但是合成一篇，整个却显得真实、清爽。她很好地遵循了白话文“有什么说什么，该怎么说就怎么说”的宗旨，而且她聪明在不在散文中论理，不作生硬的哲思，单纯就事论事，从而反倒能让人身临其境~~印象最深的是她和荷西去偷看别人洗澡灌肠，再如三毛考驾照的那几个考题，好笑极了~~而读到他们遇到三个疯子袭击则心提至喉~~看散文，以前喜欢过余秋雨的辞藻，现在越来越喜欢三毛这类的平淡，平淡是真，写文常常有自炫的诱惑，能抵住诱惑是不容易的。。。【题外】三毛与荷西是般配的一对，如果荷西没有去世地那么早，三毛可能也不会弃世了吧。。。“人”果然是两个人互相支撑在一起才能不倒下的。。。</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>自你之后，再无真正流浪自由的灵魂。</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>再看到 荒山之夜 仍然还是以前的震惊！他们那么随便就经历了一场出生入死，而且完全不在意，人生多么的洒脱啊</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>读过三毛全集，最好的还是这一册。</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>撒哈拉的故事</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>9787806398791</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>三毛作品中最脍炙人口的《撒哈拉的故事》，由12篇精彩动人的散文结合而成，其中《沙漠中的饭店》，是三毛适应荒凉单调的沙漠生活后，重新拾笔的第一篇文字，自此之后，三毛便写出一系列以沙漠为背景的故事，倾倒了全世界的中文读者。</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>你伤害了我的骄傲！</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1060068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>经典武学起于春秋，到北宋达到极盛，南宋有所衰落，元末因明教兴盛中兴。明代更有了东方不败等大师。但期间伽利略的出现已预示其衰落。康熙年间出现牛顿，梯云纵灭绝。道光年间出现卡诺，玄冰掌灭绝。尤其是力学定理建立后，内力和轻功全部消失，梯云纵这种只需吐纳练便可自带反重力系统的轻功彻底消失</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>慕容复是没落皇族子孙，毕生追求皇位，对王语嫣视如草介，段誉是正牌皇帝继承人，却爱美人宁弃江山。你所追的，正是我所弃的，尽道人生的可笑荒谬。</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>因为众生皆苦，便觉得自己也不是很苦。</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>金圣叹评《水浒》论武松为天人，萧峰何尝不是天人。看他有阔处，有毒处，有正处，有良处，有快处，有真处，有捷处，有雅处，有大处，有警处，实是金大侠小说中之第一人。</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>天龙八部</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>9787108006721</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>天龙八部乃金笔下的一部长篇小说，与《射雕》，《神雕》等 几部长篇小说一起被称为可读性最高的金庸小说。《天龙》的故事情节曲折，内容丰富，也曾多次被改编为电视作品。是金庸作品中集大成的一部。故事以北宋末年动荡的社会环境为背景，展开波澜壮阔的历史画卷，塑造了乔峰、段誉、 虚竹、慕容复等形象鲜明的人物，成为武侠史上的经典之作。故事精彩纷呈，人物命运悲壮多变，是可读性很强的作品，具有震撼人心的力量</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>偌大一本书，数百豪杰人物，萧峰一出，全归背景</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1255625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>理性的培养、逻辑的思维、高雅的阅读等不能让别人爱你，但却能让你坦然接受不被爱。</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>我一度以为二十多岁是一个人最难熬的一段时间，在这段时间里要实现从少年到青年的转换。看了这四本书之后发现人一辈子都在挣扎，只是每个时期面临的困难不同罢了，我们一直都经历着角色的转换。</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>会让你在读完最后一行后想要重新翻开《我的天才女友》的第一页。</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>也许莉拉吸引尼诺的地方，就是尼诺在她身上，开始看到了以为自己也有的东西，但对比之下他发现自己并没有。她拥有才智，但她没有利用它为自己谋福利，而像贵妇一样在挥霍着自己的才智，就好像对她来说，整个世界的财富都是庸俗的。莉拉的才智是免费的，这就是她让尼诺入迷的原因。“她和其他女人不一样，因为她天生就那么桀骜不驯，不会为任何事儿弯腰。”我们所有人都做出让步了，经过考验、失败和成功，这种让步重新塑造了我们。只有莉拉，没有任何人、任何事可以改变她。不仅如此，随着年龄的增长，她和任何人一样变得顽固和难相处，但她的那些品质一直都原封未动，甚至更加坚固。我们恨她的同时，也害怕她，会对她充满敬意。</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>失踪的孩子 : 那不勒斯四部曲4</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>9787020139927</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>“我的整个生命，只是一场为了提升社会地位的低俗斗争。”
+全球畅销近千万册被翻译成40多种语言
+《我的天才女友》《新名字的故事》《离开的，留下的》——
+那不勒斯四部曲NO.4令人欲罢不能的大结局
+穷尽友谊对一个人最极致的塑造
+《失踪的孩子》是“那不勒斯四部曲”的第四部，小说聚焦了莉拉和埃莱娜（“我”）的壮年和晚年，为她们持续了五十多年的友谊划上了一个令人心碎的句号。
+“我”为了爱情和写作，离开丈夫带着两个女儿回到了那不勒斯，不可避免地与莉拉，还有我曾想要逃离的城区再度变得亲密。“我”和莉拉甚至在同一年怀孕、生子，并经历了恐怖残暴的那不勒斯大地震，一切都分崩离析，一切又将被重建。
+“我”在不自觉中卷入莉拉秘密的企图——她希望利用我的名声和写作技巧来对抗城区陈腐而猖獗的恶势力。但在经历了生命最恐怖的打击之后，莉拉选择以一种怪异夸张的方式在城区彻底将自己流放...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>读完那不勒斯四部曲的雨夜，人生几十年，像是一场玩笑，像是一次为了记录而存在的表演。</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/30172069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>洪荒巨兽，太巨大了。老陀的体量感真不是盖的，契诃夫、布尔加科夫、《百年孤独》、《悉达多》，简直都好像只是从他身上抽下来一根骨头。一边读一边也遗憾：涅朵奇卡没有写完，卡拉马佐夫没有写完，契诃夫死得那么早...</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>这是一个缺失信仰的年代。这是一个焦虑爆棚的年代。当大家都在忙着读心灵鸡汤，来寻找到人生真谛的时候，推荐你读一读这本《卡拉马佐夫兄弟》，一本被无数大师封神的小说。 这本小说，在文学史上的地位已经毋庸置疑，它极其真实的写出了人性中种种的崇高与丑恶，它像一面镜子，在其中你会看到一个你都不想承认的自己。这本书，是完美的将哲学、神学、心理学融为一体的杰作。 就连最狂傲的，自命为天才的尼采，读完此书也不得不承认：“陀思妥耶夫斯基是我生命中最美好的际遇，他是一个思想深刻的人，他有充分的权利，蔑视我们这些浅薄的德国人。”</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>那时候我太轻狂，只觉得他太多话，没察觉那是另一种沉默，或者说那是沉默的尽头。</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>《宗教大法官》一章另添一星，翻译再添一星，这书至少该打七星！</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>卡拉马佐夫兄弟</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>9787532763696</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>本书系俄国大作家陀思妥耶夫斯基代表作之一。小说通过一桩真实的弑父案，描写老卡拉马佐夫同三个儿子即两代人之间的尖锐冲突。老卡拉马佐夫贪婪好色，独占妻子留给儿子们的遗产，并与长子德米特里为一个风流女子争风吃醋。一天黑夜，德米特里疑心自己的情人去跟老头儿幽会，便闯入家园，一怒之下，差点儿把老头儿砸死。他仓皇逃离后，躲在暗中装病的老卡拉马佐夫的私生子斯乜尔加科夫，悄然杀死老爷，造成了一桩震惊全俄的扑朔迷离的血案，从而引发了一连串惊心动魄的事件。作品展示一个错综复杂的社会家庭、道德和人性的悲剧主题，体现了作家一生的最高艺术成就。</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>不知是陀氏自身还是荣如德功劳，语言意蕴丰满，两本大部头看起来很愉快。上海译文这版版式不错，插画精美，如果有精装版就更好了。当时的俄罗斯刚刚破除农奴制，新思潮涌入，宗教却依然占据主导。陀氏虽然拥有一定的倾向性，但理性的光芒已锐不可当。感觉“宗教大法官”和“魔鬼。伊万·费奥多罗维奇的梦魇”两节最为精彩，其中“宗”一节直接逼问上帝，毫不留情揭露宗教，大快人心。相比之下，想到《我的个神啊》这种幼稚的意淫如此为人追捧，只得耻笑。</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/25887924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>我很真诚的讲：作者用极其扎实的故事告诉了女人们，为什么不能太早结婚以及为什么要坚持上学读书……（一本真正的女性主义小说</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>你以为那不勒斯很远，但是那种女性才懂的绝望和迷茫是全世界通用的。</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>这套小说有一种奇怪的魔力，完全手不释卷，停不下来，会想一口气看掉，沉迷在人物波澜壮阔的情感和命运里。有一种看情节剧的错觉，而且一点也不累人，翻起来又快又兴奋。莉拉的命运啊，真的，最后在工厂里那一幕，哭死了，为她心碎，她的疯狂和大胆，她的天才和倔强。而莱农的心理描写也非常好看，直接而无任何保留，以后她会袒露自己，还是把自己写成故事呢。现在配角的人物形象都开始丰满起来，但是尼诺反倒有点让人爱不起来，在莉拉的光芒下，他显得迟疑而孱弱，反倒是恩佐和莉拉一起学习的画面又一次激动了人心。继续等第三部第四部，想知道莉拉如何继续把控她的命运。</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>好吧我也没忍住把这本看完了。我现在最大的困惑其实是：这个作者为什么什么都懂！不光是女人们，男人们的歇斯底里，在她笔下也能驾轻就熟。生活就是如此无望，彼此桎梏，每个人都想要挣脱，可都没有结果，只留下了故事。</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>新名字的故事 : 那不勒斯四部曲2</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>9787020125265</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>只有你身为女人 才会知道这些丑陋的秘密
+两个女人 50年的友谊和战争
+如何成为那个更强大的她，又不被她战胜
+那不勒斯四部曲NO.2
+《我的天才女友》后续， 意大利最神秘的作家费兰特
+探索青年时代的激情、困惑、挣扎、背叛和失去
+全球畅销近千万册 被翻译成40多种语言
+-------------------------
+《新名字的故事》是埃莱娜·费兰特的“那不勒斯四部曲”的第二部，描述了埃莱娜和莉拉的青年时代。在她们的人生以最快的速度急遽分化的那些年里，她们共同体验了爱、失去、困惑、挣扎、嫉妒和隐蔽的破坏。
+莉拉在结婚当天就发现婚姻根本不是她想象的那样，她的初夜几乎是一场强奸。她带着一种强大的破坏欲介入了斯特凡诺的家族生意，似乎成为了她和埃莱娜小时候都想成为的那种女人。久未有身孕的莉拉，和埃莱娜去海边度假休养。而在伊斯基亚岛的那个夏天，改变了所有人的一生...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>读到一半要气死了，读完了反而释然了，莉拉和莱侬就像两株并生的植物，互相依赖，互相索取，互相想要摆脱对方，又都做不到。不过非常反感作者喜欢在每本书末尾扔炸弹这种做法。</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/26986954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>很感人的书，尤其是最后几页。我想以后我要是有孩子了，我要让TA在10岁的时候读这本书，让TA看到人与人的温暖和理解，学会对于“少数人”的包容和同理。这世上很多的罪恶，都来源于多数人对“少数人”的暴力。</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>她死得无怨无悔，不欠任何人，也不依赖任何东西。她是我见过最勇敢的人。</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>没有读过这本书的人生跟读过之后的人生，真的很不一样。</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>偏见不仅会消灭肉体（黑人汤姆之死）也会扼杀灵魂（怪人阿瑟·拉德利一生避世）</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>杀死一只知更鸟</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>9787544722766</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>成长总是个让人烦恼的命题。成长有时会很缓慢，如小溪般唱着叮咚的歌曲趟过，有时却如此突如其来，如暴雨般劈头盖脸……三个孩子因为小镇上的几桩冤案经历了猝不及防的成长——痛苦与迷惑，悲伤与愤怒，也有温情与感动。这是爱与真知的成长经典。
+《杀死一只知更鸟》获1961年普利策奖。
+美国图书馆借阅率最高的书，英国青少年最喜爱的小说之一。
+美国中学推荐课外读物。
+由小说改编的电影获第25届奥斯卡三项大奖。
+美国电影协会评选的“100名银幕英雄与恶人”中，派克主演的芬奇律师名列英雄第一位。
+作为史上最受喜爱的小说之一，《杀死一只知更鸟》已获得显赫声誉。它赢得过普利策奖，被翻译成四十多种语言，在世界范围内售出超过三千万册，并曾被拍成，备受欢迎的电影。
+——哈珀•柯林斯出版集团
+斯塔尔六月对北卡罗来纳州律师协会发表演说时，自比为《杀死一只知更鸟》中勇敢的南方白人律师阿蒂...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>“除非你穿上一个人的鞋子，像他那样走来走去，否则你永远无法真正了解一个人。”</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/6781808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>第一次看，还是06年第一本的电子书。后来家里有了本盗版全集，大16开800多页，板砖一样。这两天住院期间带了那本“板砖”重温了一遍，印象最深的是胡宗宪打海盗那段，最大的体会是，人可以没有良心但不能没有理想，没有良心的人未必不能做好事，但没有理想的人，只是苟活世间尔。</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>能勾起你读其他书的书，就是好书。</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>入门佳作，但是作者为了趣味性而牺牲了严谨性。</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>一个寒假看完，不拘一格拆解历史，虽不无主观，但的确很好看；最喜欢2、3集，万国来朝，文治武功，宫闱权斗，兄弟反目，于谦、王阳明伟立光明；中期妖孽盛行，流派林立，皇帝老儿冷眼旁观群臣斗；后期党同伐异，万象争流，妖人牛人猛人一锅粥，270多年的帝国灰飞烟灭，浪滔滔千古风流人物，尽成烟云；官场如职场，厚黑学从来没消失过！</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>明朝那些事儿（1-9） : 限量版</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>9787801656087</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>《明朝那些事儿》讲述从1344年到1644年，明朝三百年间的历史。作品以史料为基础，以年代和具体人物为主线，运用小说的笔法，对明朝十七帝和其他王公权贵和小人物的命运进行全景展示，尤其对官场政治、战争、帝王心术着墨最多。作品也是一部明朝政治经济制度、人伦道德的演义。</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>一部关于厚黑学的血泪史</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/3674537/</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>当我沉默的时候,我觉得充实;我将开口,同时感到空虚。</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>似乎鲁迅经常做噩梦...</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>我不愿彷徨于明暗之间，我不如在黑暗里沉没。</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>修行134th，彼时大先生白话文已臻绝顶。这本书是我爹私人藏书中唯一一本鲁迅，我六七岁的时候读过一次，不过必然是有读没有懂，今天读时受到了极大的震撼和感动，昨晚读到手心出汗心绪波动，另外这绝对不是肾虚的表现，我的损友们。最喜欢的是大先生借以自况的复仇者I，于是只剩下广漠的旷野，而他们俩在其间裸着全身，捏着利刃，干枯地立着；以死人似的眼光，赏鉴这路人们的干枯，无血的大戮，而永远沉浸于生命的飞扬的极致的大欢喜中。其次是立论，寥寥几笔白描，爽快淋漓，还有相当几篇感觉没有理解或者没有理解到位，大先生的书，也不是只读一次就可以的</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>野草</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>本书所收散文诗23篇〔包括一首打油诗和一出诗剧〕，最初都曾陆续发表于1924年12月至1926年1月的《语丝》周刊上，《题辞》最初也曾发表于1927年7月2日出版的《语丝》第138期，发表时署名均为鲁迅。
+本书于于年1927年4月由作者亲自编定，同年7月由上海北新书局初版印行列为作者所编的《乌合丛书》之一。此后印行的版本，除个别字和标点有所不同外，各篇文字大都和初版相同。《题辞》在本书最初的几次印刷都曾印入；后来被国民党政府书报检查机关抽去〔鲁迅在1935年11月23日致邱遇信和1936年2月19日致夏传经信中，均提及此事〕，至1941年上海鲁迅全集出版社出版《鲁迅三十年集》时才重新收入。《野草》的封面画系孙福熙所作，初版封面题字署“鲁迅先生”，后按鲁迅意思改为“鲁迅著”，鲁迅在1927年12月9日夜致章廷谦信中曾提及此事。
+鲁迅写作《野草》时，适值...
+(展开全部)</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>初读，重读，长时间读，掰开揉碎了读，半明半暗地读，不管怎么读都那么有味道，仅是这点有几部散文诗集能做到？</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1915958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>我对自己的要求很低：我活在世上，无非想要明白些道理，遇见些有趣的事。倘能如我所愿，我的一生就算成功。为此也要去论是非，否则道理不给你明白，有趣的事也不让你遇到。我开始得太晚了，很可能做不成什么，但我总得申明我的态度，所以就有了这本书——为我自己，也代表沉默的大多数。 ——王小波</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>我看现在是冷漠的大多数了</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>与其别人让我闭嘴，不如我自己赶快沉默了去。你的理又不是我的，我跟你辩个五六七八没意思。</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>我们是沉默的大多数，或在内心挣扎，或在脸上写满愤怒，然而结局终究是平庸与顺从。</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>沉默的大多数 : 王小波杂文随笔全编</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>9787500627098</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>这本杂文随笔集包括思想文化方面的文章，涉及知识分子的处境及思考，社会道德伦理，文化论争，国学与新儒家，民族主义等问题；包括从日常生活中发掘出来的各种真知灼见，涉及科学与邪道，女权主义等；包括对社会科学研究的评论，涉及性问题，生育问题，同性恋问题，社会研究的伦理问题和方法问题等；包括创作谈和文论，如写作的动机，作者的师承，作者对小说艺术的看法，作者对文体格调的看法，对影视的看法等；包括少量的书评，其中既有对文学经典的评论，也有对当代作家作品的一些看法；最后，还包括一些域外生活的杂感以及对某些社会现象的评点。</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>看了一半，难以为继。语言风格是揣着聪明装糊涂，可能是时代需要。关键是这聪明在我看来还不够聪明，不过想想，在那个时代，这应当也是冒险了。庆幸自己生在了现在。唯一的收获是，书中说，看杂文看评论的人，永远不能真正了解一门艺术。算是对自己一记警钟。想要广泛涉猎，高谈阔论，却又不曾自己真正深入过什么，算是一种对艺术的亵渎吧。希望自己多一点沉淀。</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>https://book.douban.com/subject/1054685/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
